--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3CDB4B-0E47-4E0D-8F21-93BC35BA8C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC1C4A0-2E3E-4DC0-9BA0-0E33594ACD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="17520" tabRatio="783" activeTab="2" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="2" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="2052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="2055">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -8526,6 +8526,15 @@
   </si>
   <si>
     <t>Malacca</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>194</t>
   </si>
 </sst>
 </file>
@@ -13339,28 +13348,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
   <dimension ref="A1:Y374"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="10" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="14" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="9.140625" style="5" collapsed="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="28.140625" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="60.140625" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="43.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="28.140625" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="11.140625" customWidth="1"/>
-    <col min="22" max="23" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="5" collapsed="1"/>
+    <col min="16" max="16" width="14.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="28.109375" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="60.109375" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="43.33203125" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="28.109375" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="11.109375" customWidth="1"/>
+    <col min="22" max="23" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="11.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -13437,7 +13446,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>568</v>
       </c>
@@ -13525,7 +13534,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>564</v>
       </c>
@@ -13615,7 +13624,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>621</v>
       </c>
@@ -13698,7 +13707,7 @@
         <v>Legacy of Saint George</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>619</v>
       </c>
@@ -13788,7 +13797,7 @@
         <v>From Frankfurt to the Andes</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>239</v>
       </c>
@@ -13873,7 +13882,7 @@
         <v>Timurizz</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>561</v>
       </c>
@@ -13963,7 +13972,7 @@
         <v>Ultimate Military</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>531</v>
       </c>
@@ -14051,7 +14060,7 @@
         <v>Triple the Rome</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>566</v>
       </c>
@@ -14134,7 +14143,7 @@
         <v>The Zoro-Austrians</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>522</v>
       </c>
@@ -14219,7 +14228,7 @@
         <v>The Freest Man in the World</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>569</v>
       </c>
@@ -14302,7 +14311,7 @@
         <v>Baborg</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>456</v>
       </c>
@@ -14387,7 +14396,7 @@
         <v>Australia-Hungary</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>633</v>
       </c>
@@ -14470,7 +14479,7 @@
         <v>Mehmet's Ambition</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>432</v>
       </c>
@@ -14560,7 +14569,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>426</v>
       </c>
@@ -14648,7 +14657,7 @@
         <v>It's all coming together</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>291</v>
       </c>
@@ -14738,7 +14747,7 @@
         <v>Hanukkah Mutapa</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>622</v>
       </c>
@@ -14826,7 +14835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>599</v>
       </c>
@@ -14916,7 +14925,7 @@
         <v>Quizquiz Pro Quo</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>620</v>
       </c>
@@ -15006,7 +15015,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>585</v>
       </c>
@@ -15096,7 +15105,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>618</v>
       </c>
@@ -15186,7 +15195,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -15276,7 +15285,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -15364,7 +15373,7 @@
         <v>Breadbasket of the World</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>567</v>
       </c>
@@ -15454,7 +15463,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>433</v>
       </c>
@@ -15544,7 +15553,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>496</v>
       </c>
@@ -15627,7 +15636,7 @@
         <v>One nation to rule them all</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>553</v>
       </c>
@@ -15712,7 +15721,7 @@
         <v>New, New Deli</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>483</v>
       </c>
@@ -15802,7 +15811,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>440</v>
       </c>
@@ -15892,7 +15901,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>451</v>
       </c>
@@ -15975,7 +15984,7 @@
         <v>Almost Prussian Blue</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>383</v>
       </c>
@@ -16060,7 +16069,7 @@
         <v>Where are the penguins?</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>430</v>
       </c>
@@ -16148,7 +16157,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>413</v>
       </c>
@@ -16231,7 +16240,7 @@
         <v>Stardust Crusaders</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>288</v>
       </c>
@@ -16321,7 +16330,7 @@
         <v>Golden Wind</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>387</v>
       </c>
@@ -16411,7 +16420,7 @@
         <v>Copium Wars</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>592</v>
       </c>
@@ -16496,7 +16505,7 @@
         <v>Inner Turmoil</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>574</v>
       </c>
@@ -16581,7 +16590,7 @@
         <v>I don't like sand</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>200</v>
       </c>
@@ -16664,7 +16673,7 @@
         <v>To the Bone</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -16749,7 +16758,7 @@
         <v>Surfing USA</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>557</v>
       </c>
@@ -16834,7 +16843,7 @@
         <v>The Pheasant Strut</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>624</v>
       </c>
@@ -16919,7 +16928,7 @@
         <v>Eat your Greens</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>390</v>
       </c>
@@ -17009,7 +17018,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>338</v>
       </c>
@@ -17099,7 +17108,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>389</v>
       </c>
@@ -17187,7 +17196,7 @@
         <v>No Country for Old Tercios</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>431</v>
       </c>
@@ -17275,7 +17284,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>428</v>
       </c>
@@ -17358,7 +17367,7 @@
         <v>Doge Coins</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>208</v>
       </c>
@@ -17445,7 +17454,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>528</v>
       </c>
@@ -17528,7 +17537,7 @@
         <v>Why is the Rûm gone!?</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>555</v>
       </c>
@@ -17613,7 +17622,7 @@
         <v>The Fezzan Corridors</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>513</v>
       </c>
@@ -17698,7 +17707,7 @@
         <v>Stiff Upper Lippe</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>511</v>
       </c>
@@ -17783,7 +17792,7 @@
         <v>Stern des Südens</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>503</v>
       </c>
@@ -17868,7 +17877,7 @@
         <v>Pick Your Poison</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>499</v>
       </c>
@@ -17951,7 +17960,7 @@
         <v>Pandya Empire</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>491</v>
       </c>
@@ -18036,7 +18045,7 @@
         <v>Mass Production</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>468</v>
       </c>
@@ -18126,7 +18135,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>463</v>
       </c>
@@ -18209,7 +18218,7 @@
         <v>Dovmont's Own</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>348</v>
       </c>
@@ -18299,7 +18308,7 @@
         <v>That's No Mon</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>412</v>
       </c>
@@ -18382,7 +18391,7 @@
         <v>Sun Invasion</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>253</v>
       </c>
@@ -18470,7 +18479,7 @@
         <v>Shemot is Not</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -18560,7 +18569,7 @@
         <v>Mansa Musa</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>424</v>
       </c>
@@ -18646,7 +18655,7 @@
         <v>King of Kings</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>265</v>
       </c>
@@ -18734,7 +18743,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
@@ -18819,7 +18828,7 @@
         <v>Imposter Syndrome</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>586</v>
       </c>
@@ -18902,7 +18911,7 @@
         <v>Empire of Mann</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>583</v>
       </c>
@@ -18994,7 +19003,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>530</v>
       </c>
@@ -19079,7 +19088,7 @@
         <v>With a little help..</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>525</v>
       </c>
@@ -19164,7 +19173,7 @@
         <v>Turkish Delight</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>523</v>
       </c>
@@ -19249,7 +19258,7 @@
         <v>Tiger of Mysore</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>520</v>
       </c>
@@ -19332,7 +19341,7 @@
         <v>The 52 Garhs</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>515</v>
       </c>
@@ -19422,7 +19431,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>506</v>
       </c>
@@ -19507,7 +19516,7 @@
         <v>Protect the Secret</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>543</v>
       </c>
@@ -19590,7 +19599,7 @@
         <v>Foremost Servitor of Jagannath</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>437</v>
       </c>
@@ -19673,7 +19682,7 @@
         <v>Core-fu</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>461</v>
       </c>
@@ -19758,7 +19767,7 @@
         <v>Bunte Kuh</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>535</v>
       </c>
@@ -19841,7 +19850,7 @@
         <v>Avar Khaganate</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>355</v>
       </c>
@@ -19931,7 +19940,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>309</v>
       </c>
@@ -20016,7 +20025,7 @@
         <v>Kuban Cigars</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>283</v>
       </c>
@@ -20101,7 +20110,7 @@
         <v>Ganges Khan</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>386</v>
       </c>
@@ -20189,7 +20198,7 @@
         <v>Brentry!</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>397</v>
       </c>
@@ -20277,7 +20286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>103</v>
       </c>
@@ -20362,7 +20371,7 @@
         <v>Truly Good Maaaaa-tch</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>614</v>
       </c>
@@ -20452,7 +20461,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>608</v>
       </c>
@@ -20537,7 +20546,7 @@
         <v>Spanish Fly</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>591</v>
       </c>
@@ -20620,7 +20629,7 @@
         <v>Great Perm</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>584</v>
       </c>
@@ -20708,7 +20717,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>139</v>
       </c>
@@ -20793,7 +20802,7 @@
         <v>Forgive me, for I have Sindh</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>509</v>
       </c>
@@ -20883,7 +20892,7 @@
         <v>Spaghetti Western</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>501</v>
       </c>
@@ -20964,7 +20973,7 @@
         <v>Philippine Tiger</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>551</v>
       </c>
@@ -21052,7 +21061,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>549</v>
       </c>
@@ -21137,7 +21146,7 @@
         <v>Meissner Porcelain</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>443</v>
       </c>
@@ -21222,7 +21231,7 @@
         <v>Kushite Restoration</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>477</v>
       </c>
@@ -21310,7 +21319,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>475</v>
       </c>
@@ -21395,7 +21404,7 @@
         <v>Holy Horder</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>541</v>
       </c>
@@ -21485,7 +21494,7 @@
         <v>Cotton Kandy</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>435</v>
       </c>
@@ -21573,7 +21582,7 @@
         <v>Breaking the Yoke</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>380</v>
       </c>
@@ -21658,7 +21667,7 @@
         <v>Victorian Three</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>337</v>
       </c>
@@ -21748,7 +21757,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>319</v>
       </c>
@@ -21838,7 +21847,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>297</v>
       </c>
@@ -21921,7 +21930,7 @@
         <v>Home and Away</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>277</v>
       </c>
@@ -22006,7 +22015,7 @@
         <v>Don’t be Cilli</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>248</v>
       </c>
@@ -22096,7 +22105,7 @@
         <v>Disciples of Enlightenment</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>613</v>
       </c>
@@ -22186,7 +22195,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>575</v>
       </c>
@@ -22271,7 +22280,7 @@
         <v>The Animal Kingdom</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>602</v>
       </c>
@@ -22356,7 +22365,7 @@
         <v>Raja of the Rajput Reich</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>597</v>
       </c>
@@ -22441,7 +22450,7 @@
         <v>Norwegian Wood</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>581</v>
       </c>
@@ -22531,7 +22540,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>577</v>
       </c>
@@ -22614,7 +22623,7 @@
         <v>Academical</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>186</v>
       </c>
@@ -22704,7 +22713,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>507</v>
       </c>
@@ -22794,7 +22803,7 @@
         <v>Sailor Mon</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>488</v>
       </c>
@@ -22879,7 +22888,7 @@
         <v>Lucky Lucca</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>547</v>
       </c>
@@ -22969,7 +22978,7 @@
         <v>Komnenoi Empire</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
@@ -23057,7 +23066,7 @@
         <v>Kinslayer</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>631</v>
       </c>
@@ -23142,7 +23151,7 @@
         <v>True Heir of Timur</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>629</v>
       </c>
@@ -23232,7 +23241,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>295</v>
       </c>
@@ -23317,7 +23326,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>404</v>
       </c>
@@ -23405,7 +23414,7 @@
         <v>For the Emperor!</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>571</v>
       </c>
@@ -23493,7 +23502,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>601</v>
       </c>
@@ -23578,7 +23587,7 @@
         <v>Rags and Riches</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>589</v>
       </c>
@@ -23663,7 +23672,7 @@
         <v>Gothic Invasion</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>170</v>
       </c>
@@ -23753,7 +23762,7 @@
         <v>On the Edge of Madness</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>215</v>
       </c>
@@ -23840,7 +23849,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>495</v>
       </c>
@@ -23928,7 +23937,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>420</v>
       </c>
@@ -24020,7 +24029,7 @@
         <v>Yarr Harr a Pirate's Life For Me</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>346</v>
       </c>
@@ -24108,7 +24117,7 @@
         <v>Tatarstan</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>334</v>
       </c>
@@ -24196,7 +24205,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -24283,7 +24292,7 @@
         <v>Rekindling the Flames</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>327</v>
       </c>
@@ -24366,7 +24375,7 @@
         <v>No Trail of Tears</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>423</v>
       </c>
@@ -24456,7 +24465,7 @@
         <v>First Come, First Serve</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>99</v>
       </c>
@@ -24543,7 +24552,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>611</v>
       </c>
@@ -24633,7 +24642,7 @@
         <v>The Buddhists Strike Back</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>595</v>
       </c>
@@ -24719,7 +24728,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>593</v>
       </c>
@@ -24809,7 +24818,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>588</v>
       </c>
@@ -24899,7 +24908,7 @@
         <v>Frozen Assets</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>579</v>
       </c>
@@ -24987,7 +24996,7 @@
         <v>Albania or Iberia</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>199</v>
       </c>
@@ -25072,7 +25081,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>235</v>
       </c>
@@ -25164,7 +25173,7 @@
         <v>Østindisk Kompagni Te</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>128</v>
       </c>
@@ -25249,7 +25258,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>119</v>
       </c>
@@ -25337,7 +25346,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>527</v>
       </c>
@@ -25427,7 +25436,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>466</v>
       </c>
@@ -25517,7 +25526,7 @@
         <v>Emperor of Hindustan</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>540</v>
       </c>
@@ -25602,7 +25611,7 @@
         <v>Choson One</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>458</v>
       </c>
@@ -25690,7 +25699,7 @@
         <v>Back to the Piast</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>258</v>
       </c>
@@ -25773,7 +25782,7 @@
         <v>Turn the Table</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>366</v>
       </c>
@@ -25863,7 +25872,7 @@
         <v>The Sudanese Expedition</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>610</v>
       </c>
@@ -25953,7 +25962,7 @@
         <v>Sunset Invasion</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>604</v>
       </c>
@@ -26043,7 +26052,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>126</v>
       </c>
@@ -26135,7 +26144,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>121</v>
       </c>
@@ -26225,7 +26234,7 @@
         <v>Brick by Brick</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>565</v>
       </c>
@@ -26315,7 +26324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>516</v>
       </c>
@@ -26403,7 +26412,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>445</v>
       </c>
@@ -26488,7 +26497,7 @@
         <v>Rise of the White Sheep</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>563</v>
       </c>
@@ -26576,7 +26585,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>444</v>
       </c>
@@ -26664,7 +26673,7 @@
         <v>Lessons of Hemmingstedt</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>484</v>
       </c>
@@ -26747,7 +26756,7 @@
         <v>Lazarus</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>479</v>
       </c>
@@ -26835,7 +26844,7 @@
         <v>Keep the Flame Burning</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -26923,7 +26932,7 @@
         <v>Auld Alliance Reversed</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>378</v>
       </c>
@@ -27013,7 +27022,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>362</v>
       </c>
@@ -27103,7 +27112,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>321</v>
       </c>
@@ -27191,7 +27200,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>289</v>
       </c>
@@ -27274,7 +27283,7 @@
         <v>Great Moravia</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>287</v>
       </c>
@@ -27359,7 +27368,7 @@
         <v>Golden Horn</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>83</v>
       </c>
@@ -27442,7 +27451,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>184</v>
       </c>
@@ -27527,7 +27536,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -27617,7 +27626,7 @@
         <v>Holy Trinity</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>471</v>
       </c>
@@ -27707,7 +27716,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>439</v>
       </c>
@@ -27799,7 +27808,7 @@
         <v>For Odin!</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>465</v>
       </c>
@@ -27889,7 +27898,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>533</v>
       </c>
@@ -27979,7 +27988,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>449</v>
       </c>
@@ -28064,7 +28073,7 @@
         <v>A Hero’s Welcome</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>627</v>
       </c>
@@ -28147,7 +28156,7 @@
         <v>One Faith</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>372</v>
       </c>
@@ -28230,7 +28239,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>418</v>
       </c>
@@ -28320,7 +28329,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>328</v>
       </c>
@@ -28403,7 +28412,7 @@
         <v>Parisian Pasha</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>317</v>
       </c>
@@ -28493,7 +28502,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>293</v>
       </c>
@@ -28576,7 +28585,7 @@
         <v>Hessian Mercenaries</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>267</v>
       </c>
@@ -28666,7 +28675,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>24</v>
       </c>
@@ -28753,7 +28762,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -28838,7 +28847,7 @@
         <v>Rozwi Empire</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
@@ -28928,7 +28937,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>154</v>
       </c>
@@ -29018,7 +29027,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>556</v>
       </c>
@@ -29108,7 +29117,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>419</v>
       </c>
@@ -29200,7 +29209,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>350</v>
       </c>
@@ -29288,7 +29297,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>336</v>
       </c>
@@ -29371,7 +29380,7 @@
         <v>Sons of Carthage</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>243</v>
       </c>
@@ -29461,7 +29470,7 @@
         <v>Abu Bakr II’s Ambition</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>214</v>
       </c>
@@ -29551,7 +29560,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -29636,7 +29645,7 @@
         <v>The Uncommonwealth</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>361</v>
       </c>
@@ -29726,7 +29735,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>357</v>
       </c>
@@ -29816,7 +29825,7 @@
         <v>The Levant Turnabout</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>352</v>
       </c>
@@ -29904,7 +29913,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>254</v>
       </c>
@@ -29987,7 +29996,7 @@
         <v>Sweet Home Qaraqorum</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>405</v>
       </c>
@@ -30077,7 +30086,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>299</v>
       </c>
@@ -30169,7 +30178,7 @@
         <v>Ideas Guy</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>269</v>
       </c>
@@ -30252,7 +30261,7 @@
         <v>Bengal Tiger</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>260</v>
       </c>
@@ -30344,7 +30353,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>161</v>
       </c>
@@ -30434,7 +30443,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>152</v>
       </c>
@@ -30524,7 +30533,7 @@
         <v>Kow-Tow</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>370</v>
       </c>
@@ -30612,7 +30621,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>422</v>
       </c>
@@ -30702,7 +30711,7 @@
         <v>A Sun God</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>469</v>
       </c>
@@ -30794,7 +30803,7 @@
         <v>Forever Golden</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>344</v>
       </c>
@@ -30884,7 +30893,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>342</v>
       </c>
@@ -30974,7 +30983,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>308</v>
       </c>
@@ -31064,7 +31073,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>398</v>
       </c>
@@ -31152,7 +31161,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>59</v>
       </c>
@@ -31237,7 +31246,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>221</v>
       </c>
@@ -31327,7 +31336,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>176</v>
       </c>
@@ -31410,7 +31419,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>157</v>
       </c>
@@ -31500,7 +31509,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>147</v>
       </c>
@@ -31590,7 +31599,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>117</v>
       </c>
@@ -31675,7 +31684,7 @@
         <v>Baa Baa Black Sheep</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>558</v>
       </c>
@@ -31765,7 +31774,7 @@
         <v>The Re-Reconquista</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>480</v>
       </c>
@@ -31855,7 +31864,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>545</v>
       </c>
@@ -31943,7 +31952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>452</v>
       </c>
@@ -32035,7 +32044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>359</v>
       </c>
@@ -32125,7 +32134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>353</v>
       </c>
@@ -32213,7 +32222,7 @@
         <v>The Iron Price</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>36</v>
       </c>
@@ -32296,7 +32305,7 @@
         <v>Krabater</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>146</v>
       </c>
@@ -32386,7 +32395,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>560</v>
       </c>
@@ -32474,7 +32483,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>505</v>
       </c>
@@ -32564,7 +32573,7 @@
         <v>Prester John</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>460</v>
       </c>
@@ -32654,7 +32663,7 @@
         <v>Baltic Crusader</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>411</v>
       </c>
@@ -32739,7 +32748,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>333</v>
       </c>
@@ -32827,7 +32836,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>330</v>
       </c>
@@ -32917,7 +32926,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>402</v>
       </c>
@@ -33007,7 +33016,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>486</v>
       </c>
@@ -33092,7 +33101,7 @@
         <v>Luck of the Irish</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>441</v>
       </c>
@@ -33180,7 +33189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>538</v>
       </c>
@@ -33270,7 +33279,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>93</v>
       </c>
@@ -33360,7 +33369,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>616</v>
       </c>
@@ -33450,7 +33459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
@@ -33536,7 +33545,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>400</v>
       </c>
@@ -33624,7 +33633,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -33712,7 +33721,7 @@
         <v>A Blessed Nation</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>240</v>
       </c>
@@ -33802,7 +33811,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>279</v>
       </c>
@@ -33885,7 +33894,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>164</v>
       </c>
@@ -33973,7 +33982,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>312</v>
       </c>
@@ -34058,7 +34067,7 @@
         <v>Lion of the North</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>518</v>
       </c>
@@ -34146,7 +34155,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>310</v>
       </c>
@@ -34234,7 +34243,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>606</v>
       </c>
@@ -34324,7 +34333,7 @@
         <v>Shahanshah</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>473</v>
       </c>
@@ -34407,7 +34416,7 @@
         <v>Guarantor of Peace</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>409</v>
       </c>
@@ -34497,7 +34506,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>251</v>
       </c>
@@ -34587,7 +34596,7 @@
         <v>Relentless Push East</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>306</v>
       </c>
@@ -34675,7 +34684,7 @@
         <v>Kingdom of God</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>273</v>
       </c>
@@ -34763,7 +34772,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>97</v>
       </c>
@@ -34846,7 +34855,7 @@
         <v>Poland can into space</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>22</v>
       </c>
@@ -34938,7 +34947,7 @@
         <v>Foul Mouthed</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>143</v>
       </c>
@@ -35028,7 +35037,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>104</v>
       </c>
@@ -35118,7 +35127,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>263</v>
       </c>
@@ -35206,7 +35215,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>166</v>
       </c>
@@ -35294,7 +35303,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>112</v>
       </c>
@@ -35380,7 +35389,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>285</v>
       </c>
@@ -35470,7 +35479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>168</v>
       </c>
@@ -35560,7 +35569,7 @@
         <v>Nobody wants to die</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>493</v>
       </c>
@@ -35645,7 +35654,7 @@
         <v>Master of India</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>231</v>
       </c>
@@ -35731,7 +35740,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>340</v>
       </c>
@@ -35819,7 +35828,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>202</v>
       </c>
@@ -35909,7 +35918,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>196</v>
       </c>
@@ -35997,7 +36006,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>364</v>
       </c>
@@ -36087,7 +36096,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>275</v>
       </c>
@@ -36170,7 +36179,7 @@
         <v>Definitely the Sultan of Rum</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>48</v>
       </c>
@@ -36258,7 +36267,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>497</v>
       </c>
@@ -36346,7 +36355,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>209</v>
       </c>
@@ -36429,7 +36438,7 @@
         <v>Winged Hussars</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>173</v>
       </c>
@@ -36512,7 +36521,7 @@
         <v>One King to Rule!</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>490</v>
       </c>
@@ -36602,7 +36611,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>256</v>
       </c>
@@ -36685,7 +36694,7 @@
         <v>The Spice Must Flow</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>259</v>
       </c>
@@ -36768,7 +36777,7 @@
         <v>A tale of two Families</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>129</v>
       </c>
@@ -36856,7 +36865,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>416</v>
       </c>
@@ -36944,7 +36953,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>393</v>
       </c>
@@ -37034,7 +37043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>34</v>
       </c>
@@ -37119,7 +37128,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>373</v>
       </c>
@@ -37207,7 +37216,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>325</v>
       </c>
@@ -37295,7 +37304,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>247</v>
       </c>
@@ -37383,7 +37392,7 @@
         <v>Black Jack</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>1677</v>
       </c>
@@ -37473,7 +37482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>210</v>
       </c>
@@ -37563,7 +37572,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>190</v>
       </c>
@@ -37655,7 +37664,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>106</v>
       </c>
@@ -37745,7 +37754,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>130</v>
       </c>
@@ -37828,7 +37837,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>537</v>
       </c>
@@ -37916,7 +37925,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>381</v>
       </c>
@@ -38004,7 +38013,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>13</v>
       </c>
@@ -38094,7 +38103,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>38</v>
       </c>
@@ -38182,7 +38191,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>148</v>
       </c>
@@ -38270,7 +38279,7 @@
         <v>Imperio español</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>384</v>
       </c>
@@ -38360,7 +38369,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>204</v>
       </c>
@@ -38448,7 +38457,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>300</v>
       </c>
@@ -38538,7 +38547,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>89</v>
       </c>
@@ -38626,7 +38635,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>376</v>
       </c>
@@ -38711,7 +38720,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>124</v>
       </c>
@@ -38799,7 +38808,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>144</v>
       </c>
@@ -38887,7 +38896,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>233</v>
       </c>
@@ -38975,7 +38984,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>229</v>
       </c>
@@ -39063,7 +39072,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>414</v>
       </c>
@@ -39153,7 +39162,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>391</v>
       </c>
@@ -39238,7 +39247,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>3</v>
       </c>
@@ -39326,7 +39335,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>63</v>
       </c>
@@ -39413,7 +39422,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>304</v>
       </c>
@@ -39503,7 +39512,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>281</v>
       </c>
@@ -39595,7 +39604,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>101</v>
       </c>
@@ -39680,7 +39689,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>25</v>
       </c>
@@ -39768,7 +39777,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>141</v>
       </c>
@@ -39856,7 +39865,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>133</v>
       </c>
@@ -39943,7 +39952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>395</v>
       </c>
@@ -40029,7 +40038,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>40</v>
       </c>
@@ -40119,7 +40128,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>212</v>
       </c>
@@ -40207,7 +40216,7 @@
         <v>A Fine Goosestep</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>323</v>
       </c>
@@ -40297,7 +40306,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>137</v>
       </c>
@@ -40387,7 +40396,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>250</v>
       </c>
@@ -40477,7 +40486,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>108</v>
       </c>
@@ -40565,7 +40574,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>223</v>
       </c>
@@ -40655,7 +40664,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>159</v>
       </c>
@@ -40743,7 +40752,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>175</v>
       </c>
@@ -40831,7 +40840,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>163</v>
       </c>
@@ -40921,7 +40930,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>262</v>
       </c>
@@ -41009,7 +41018,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>95</v>
       </c>
@@ -41097,7 +41106,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>49</v>
       </c>
@@ -41187,7 +41196,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>5</v>
       </c>
@@ -41277,7 +41286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>313</v>
       </c>
@@ -41362,7 +41371,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>85</v>
       </c>
@@ -41450,7 +41459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>271</v>
       </c>
@@ -41538,7 +41547,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>172</v>
       </c>
@@ -41626,7 +41635,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>75</v>
       </c>
@@ -41711,7 +41720,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>227</v>
       </c>
@@ -41801,7 +41810,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>42</v>
       </c>
@@ -41891,7 +41900,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>206</v>
       </c>
@@ -41979,7 +41988,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>203</v>
       </c>
@@ -42069,7 +42078,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>302</v>
       </c>
@@ -42157,7 +42166,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>135</v>
       </c>
@@ -42244,7 +42253,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>219</v>
       </c>
@@ -42332,7 +42341,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>57</v>
       </c>
@@ -42420,7 +42429,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>110</v>
       </c>
@@ -42510,7 +42519,7 @@
         <v>All belongs to Mother Russia</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>87</v>
       </c>
@@ -42596,7 +42605,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>113</v>
       </c>
@@ -42686,7 +42695,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>18</v>
       </c>
@@ -42769,7 +42778,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>65</v>
       </c>
@@ -42857,7 +42866,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>315</v>
       </c>
@@ -42945,7 +42954,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>192</v>
       </c>
@@ -43035,7 +43044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>30</v>
       </c>
@@ -43125,7 +43134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>61</v>
       </c>
@@ -43213,7 +43222,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>122</v>
       </c>
@@ -43302,7 +43311,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>194</v>
       </c>
@@ -43388,7 +43397,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>0</v>
       </c>
@@ -43475,7 +43484,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>81</v>
       </c>
@@ -43563,7 +43572,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>131</v>
       </c>
@@ -43651,7 +43660,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>225</v>
       </c>
@@ -43736,7 +43745,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>115</v>
       </c>
@@ -43826,7 +43835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>245</v>
       </c>
@@ -43911,7 +43920,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>7</v>
       </c>
@@ -43996,7 +44005,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>217</v>
       </c>
@@ -44081,7 +44090,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>374</v>
       </c>
@@ -44164,7 +44173,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>180</v>
       </c>
@@ -44249,7 +44258,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>16</v>
       </c>
@@ -44339,7 +44348,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>44</v>
       </c>
@@ -44422,7 +44431,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>27</v>
       </c>
@@ -44509,7 +44518,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>77</v>
       </c>
@@ -44594,7 +44603,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>69</v>
       </c>
@@ -44681,7 +44690,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -44768,7 +44777,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>150</v>
       </c>
@@ -44853,7 +44862,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>91</v>
       </c>
@@ -44938,7 +44947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>198</v>
       </c>
@@ -45028,7 +45037,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>14</v>
       </c>
@@ -45115,7 +45124,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>32</v>
       </c>
@@ -45200,7 +45209,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>67</v>
       </c>
@@ -45287,7 +45296,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -45372,7 +45381,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>20</v>
       </c>
@@ -45457,7 +45466,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>55</v>
       </c>
@@ -45542,7 +45551,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>46</v>
       </c>
@@ -45625,7 +45634,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>79</v>
       </c>
@@ -45708,7 +45717,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>51</v>
       </c>
@@ -45791,7 +45800,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>53</v>
       </c>
@@ -45878,7 +45887,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>73</v>
       </c>
@@ -45963,7 +45972,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>71</v>
       </c>
@@ -46130,17 +46139,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16ACCB4E-C812-42E5-BA87-3FBA0B83A629}">
   <dimension ref="A1:F116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="125.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.44140625" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="125.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1747</v>
       </c>
@@ -46160,7 +46169,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>1713</v>
       </c>
@@ -46169,7 +46178,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>1714</v>
       </c>
@@ -46183,7 +46192,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
         <v>1715</v>
       </c>
@@ -46191,7 +46200,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
         <v>1748</v>
       </c>
@@ -46199,7 +46208,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
         <v>1716</v>
       </c>
@@ -46207,7 +46216,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
         <v>1749</v>
       </c>
@@ -46215,7 +46224,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
         <v>1717</v>
       </c>
@@ -46229,7 +46238,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
         <v>1675</v>
       </c>
@@ -46243,7 +46252,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="35" t="s">
         <v>1750</v>
       </c>
@@ -46257,7 +46266,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
         <v>1718</v>
       </c>
@@ -46265,7 +46274,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="35" t="s">
         <v>1719</v>
       </c>
@@ -46273,7 +46282,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
         <v>1751</v>
       </c>
@@ -46281,7 +46290,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
         <v>1752</v>
       </c>
@@ -46289,7 +46298,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
         <v>1689</v>
       </c>
@@ -46297,7 +46306,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>1720</v>
       </c>
@@ -46305,7 +46314,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="s">
         <v>1721</v>
       </c>
@@ -46319,7 +46328,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="35" t="s">
         <v>1753</v>
       </c>
@@ -46333,7 +46342,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="35" t="s">
         <v>1754</v>
       </c>
@@ -46347,7 +46356,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
         <v>1755</v>
       </c>
@@ -46355,7 +46364,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
         <v>1756</v>
       </c>
@@ -46363,7 +46372,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="35" t="s">
         <v>1757</v>
       </c>
@@ -46377,7 +46386,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
         <v>1758</v>
       </c>
@@ -46391,7 +46400,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>1759</v>
       </c>
@@ -46399,7 +46408,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
         <v>1684</v>
       </c>
@@ -46413,7 +46422,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="35" t="s">
         <v>1722</v>
       </c>
@@ -46427,7 +46436,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
         <v>1826</v>
       </c>
@@ -46441,7 +46450,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
         <v>1676</v>
       </c>
@@ -46449,7 +46458,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="35" t="s">
         <v>1760</v>
       </c>
@@ -46457,7 +46466,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>756</v>
       </c>
@@ -46471,7 +46480,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
         <v>1723</v>
       </c>
@@ -46485,7 +46494,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="35" t="s">
         <v>1761</v>
       </c>
@@ -46493,7 +46502,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
         <v>1724</v>
       </c>
@@ -46501,7 +46510,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
         <v>289</v>
       </c>
@@ -46515,7 +46524,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="35" t="s">
         <v>1762</v>
       </c>
@@ -46523,7 +46532,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="35" t="s">
         <v>1763</v>
       </c>
@@ -46531,7 +46540,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
         <v>1764</v>
       </c>
@@ -46539,7 +46548,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>1765</v>
       </c>
@@ -46547,7 +46556,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
         <v>1725</v>
       </c>
@@ -46555,7 +46564,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="35" t="s">
         <v>1726</v>
       </c>
@@ -46563,7 +46572,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="35" t="s">
         <v>1710</v>
       </c>
@@ -46571,7 +46580,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
         <v>1766</v>
       </c>
@@ -46579,7 +46588,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
         <v>1767</v>
       </c>
@@ -46587,7 +46596,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
         <v>1768</v>
       </c>
@@ -46607,7 +46616,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
         <v>1769</v>
       </c>
@@ -46615,7 +46624,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
         <v>1770</v>
       </c>
@@ -46623,7 +46632,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>1727</v>
       </c>
@@ -46631,7 +46640,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
         <v>1728</v>
       </c>
@@ -46645,7 +46654,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
         <v>1771</v>
       </c>
@@ -46653,7 +46662,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="35" t="s">
         <v>1772</v>
       </c>
@@ -46661,7 +46670,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="35" t="s">
         <v>765</v>
       </c>
@@ -46669,7 +46678,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="35" t="s">
         <v>1773</v>
       </c>
@@ -46677,7 +46686,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
         <v>1777</v>
       </c>
@@ -46685,7 +46694,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
         <v>1774</v>
       </c>
@@ -46693,7 +46702,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
         <v>1775</v>
       </c>
@@ -46701,7 +46710,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>1776</v>
       </c>
@@ -46715,7 +46724,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>1729</v>
       </c>
@@ -46723,7 +46732,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="35" t="s">
         <v>1778</v>
       </c>
@@ -46731,7 +46740,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="35" t="s">
         <v>1779</v>
       </c>
@@ -46739,7 +46748,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="35" t="s">
         <v>1780</v>
       </c>
@@ -46753,7 +46762,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A61" s="35" t="s">
         <v>1781</v>
       </c>
@@ -46767,7 +46776,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="35" t="s">
         <v>1782</v>
       </c>
@@ -46787,7 +46796,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="35" t="s">
         <v>1783</v>
       </c>
@@ -46795,7 +46804,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="35" t="s">
         <v>1784</v>
       </c>
@@ -46803,7 +46812,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="35" t="s">
         <v>1785</v>
       </c>
@@ -46811,7 +46820,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="35" t="s">
         <v>1730</v>
       </c>
@@ -46825,7 +46834,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="35" t="s">
         <v>1731</v>
       </c>
@@ -46833,7 +46842,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="35" t="s">
         <v>1732</v>
       </c>
@@ -46847,7 +46856,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="35" t="s">
         <v>1786</v>
       </c>
@@ -46861,7 +46870,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="35" t="s">
         <v>1787</v>
       </c>
@@ -46869,7 +46878,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A71" s="35" t="s">
         <v>1733</v>
       </c>
@@ -46889,7 +46898,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="35" t="s">
         <v>1788</v>
       </c>
@@ -46897,7 +46906,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="35" t="s">
         <v>1789</v>
       </c>
@@ -46911,7 +46920,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="35" t="s">
         <v>1790</v>
       </c>
@@ -46919,7 +46928,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="35" t="s">
         <v>1791</v>
       </c>
@@ -46927,7 +46936,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="35" t="s">
         <v>1792</v>
       </c>
@@ -46935,7 +46944,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
         <v>1734</v>
       </c>
@@ -46955,7 +46964,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="35" t="s">
         <v>1735</v>
       </c>
@@ -46975,7 +46984,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A79" s="35" t="s">
         <v>1793</v>
       </c>
@@ -46989,7 +46998,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="35" t="s">
         <v>1794</v>
       </c>
@@ -46997,7 +47006,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A81" s="35" t="s">
         <v>1795</v>
       </c>
@@ -47011,7 +47020,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="35" t="s">
         <v>1796</v>
       </c>
@@ -47025,7 +47034,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="35" t="s">
         <v>1736</v>
       </c>
@@ -47033,7 +47042,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="35" t="s">
         <v>1797</v>
       </c>
@@ -47041,7 +47050,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="35" t="s">
         <v>1737</v>
       </c>
@@ -47049,7 +47058,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="35" t="s">
         <v>1798</v>
       </c>
@@ -47057,7 +47066,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="35" t="s">
         <v>182</v>
       </c>
@@ -47065,7 +47074,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A88" s="35" t="s">
         <v>1738</v>
       </c>
@@ -47085,7 +47094,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="35" t="s">
         <v>1739</v>
       </c>
@@ -47105,7 +47114,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="35" t="s">
         <v>1799</v>
       </c>
@@ -47113,7 +47122,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="35" t="s">
         <v>1800</v>
       </c>
@@ -47121,7 +47130,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="35" t="s">
         <v>1801</v>
       </c>
@@ -47129,7 +47138,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="35" t="s">
         <v>1740</v>
       </c>
@@ -47137,7 +47146,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="35" t="s">
         <v>1802</v>
       </c>
@@ -47151,7 +47160,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="35" t="s">
         <v>1803</v>
       </c>
@@ -47159,7 +47168,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="35" t="s">
         <v>1804</v>
       </c>
@@ -47167,7 +47176,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="35" t="s">
         <v>1805</v>
       </c>
@@ -47175,7 +47184,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
         <v>1806</v>
       </c>
@@ -47183,7 +47192,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="35" t="s">
         <v>1807</v>
       </c>
@@ -47191,7 +47200,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
         <v>1741</v>
       </c>
@@ -47205,7 +47214,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="35" t="s">
         <v>1808</v>
       </c>
@@ -47213,7 +47222,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="35" t="s">
         <v>764</v>
       </c>
@@ -47221,7 +47230,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="35" t="s">
         <v>1742</v>
       </c>
@@ -47229,7 +47238,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A104" s="35" t="s">
         <v>1743</v>
       </c>
@@ -47243,7 +47252,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="35" t="s">
         <v>1809</v>
       </c>
@@ -47251,7 +47260,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="35" t="s">
         <v>1810</v>
       </c>
@@ -47265,7 +47274,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="35" t="s">
         <v>1811</v>
       </c>
@@ -47273,7 +47282,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="35" t="s">
         <v>1812</v>
       </c>
@@ -47287,7 +47296,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="35" t="s">
         <v>1813</v>
       </c>
@@ -47295,7 +47304,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="35" t="s">
         <v>1814</v>
       </c>
@@ -47303,7 +47312,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="35" t="s">
         <v>1744</v>
       </c>
@@ -47319,7 +47328,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="35" t="s">
         <v>1815</v>
       </c>
@@ -47327,7 +47336,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="35" t="s">
         <v>1816</v>
       </c>
@@ -47335,7 +47344,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="35" t="s">
         <v>1817</v>
       </c>
@@ -47349,7 +47358,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="35" t="s">
         <v>1745</v>
       </c>
@@ -47357,7 +47366,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="35" t="s">
         <v>1746</v>
       </c>
@@ -47722,26 +47731,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB4F934-B5CD-4C00-8D57-A5021FDDF4F5}">
   <dimension ref="A1:P153"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" style="66" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="31.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="58" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="28.140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="34.42578125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="60.140625" customWidth="1"/>
-    <col min="16" max="16" width="63.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="58" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="28.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="34.44140625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="60.109375" customWidth="1"/>
+    <col min="16" max="16" width="63.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="37" t="s">
         <v>1856</v>
       </c>
@@ -47791,7 +47800,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
         <v>2044</v>
       </c>
@@ -47845,7 +47854,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>2031</v>
       </c>
@@ -47911,7 +47920,7 @@
 mission Ratify the Kalmar Union while having the reform Kalmar Union.</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="39" t="s">
         <v>2031</v>
       </c>
@@ -47974,7 +47983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48038,7 +48047,7 @@
 Asia. Then form a claim in Ayutthaya or wait for Mingsplosion.</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48113,7 +48122,7 @@
 - Switching to play as a released vassal will invalidate the achievement.</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48214,7 +48223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48284,7 +48293,7 @@
 pretty easy without it.</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48355,7 +48364,7 @@
 the Siberian ports has already been cored or fully colonized.</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48416,7 +48425,7 @@
         <v>Easiest to do as Muscovy.</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48489,7 +48498,7 @@
 Sea ̦; it can be counterbalanced by building lots of light ships.</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48557,7 +48566,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48619,7 +48628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48683,7 +48692,7 @@
 modifier. This will deter nearby attackers as you expand opportunistically.</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48745,7 +48754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48819,7 +48828,7 @@
 Rekindling the Flames.</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="39" t="s">
         <v>2036</v>
       </c>
@@ -48891,7 +48900,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
         <v>2036</v>
       </c>
@@ -48962,7 +48971,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45" t="s">
         <v>2036</v>
       </c>
@@ -49029,7 +49038,7 @@
 scornfully insult 10 of Lithuania's 11 neighbours.</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49096,7 +49105,7 @@
 to that number later.</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49168,7 +49177,7 @@
 aspect.</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49241,7 +49250,7 @@
 colonize yourself.</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49308,7 +49317,7 @@
 possible to get the achievement without that DLC.</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49371,7 +49380,7 @@
 colonizing the NA lands may result in their capital being in NA.</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49435,7 +49444,7 @@
 partnered with The Buddhists Strike Back.</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49502,7 +49511,7 @@
 playing as Kandy, you'll likely also get the achievement Cotton Kandy.</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>2040</v>
       </c>
@@ -49566,7 +49575,7 @@
 be achieved even without the DLC.</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>2041</v>
       </c>
@@ -49631,7 +49640,7 @@
 these will immediately make you an empire.</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>2043</v>
       </c>
@@ -49696,7 +49705,7 @@
 Philippine islands are an excellent place to start forcing conversions.</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="39" t="s">
         <v>2042</v>
       </c>
@@ -49778,7 +49787,7 @@
 Emperor.</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="39" t="s">
         <v>1920</v>
       </c>
@@ -49790,11 +49799,11 @@
       </c>
       <c r="D31" s="27">
         <f t="shared" si="0"/>
-        <v>438.5</v>
+        <v>290</v>
       </c>
       <c r="E31" s="31">
         <f>D31/'Top 10 Hard'!$J$2</f>
-        <v>1.1862219709409441E-2</v>
+        <v>7.8450255774885711E-3</v>
       </c>
       <c r="F31" s="31">
         <f>IF(NOT(ISNUMBER(F30)),0,F30)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -49841,7 +49850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="45" t="s">
         <v>1921</v>
       </c>
@@ -49913,7 +49922,7 @@
 Secretive personality which gives *+20%* foreign spy detection.</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39" t="s">
         <v>1922</v>
       </c>
@@ -49980,7 +49989,7 @@
 provinces by calling them to war as ally before subjugating them.</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="39" t="s">
         <v>1922</v>
       </c>
@@ -50045,7 +50054,7 @@
 the province sooner.</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50110,7 +50119,7 @@
 map which can't be earned by playing that custom nation.</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50178,7 +50187,7 @@
 to protect them while you improve relations.</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50244,7 +50253,7 @@
 releasing client states.</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50313,7 +50322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50375,7 +50384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50442,7 +50451,7 @@
 Aragon.</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50512,7 +50521,7 @@
 does not change your missions).</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50575,7 +50584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50645,7 +50654,7 @@
 animist) after hitting 95 doom will also not prevent the achievement.</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50717,7 +50726,7 @@
 take capitals without the need of conquering a lot of adjacent provinces.</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50788,7 +50797,7 @@
 you can finish, it may be easier to allow a colonial nation to form.</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50868,7 +50877,7 @@
 rapidly across the continent at the cost of diplomatic power.</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="45" t="s">
         <v>2047</v>
       </c>
@@ -50934,7 +50943,7 @@
 economy of Spain.</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="39" t="s">
         <v>1928</v>
       </c>
@@ -51006,7 +51015,7 @@
 country will count for the achievement.</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="45" t="s">
         <v>1929</v>
       </c>
@@ -51078,7 +51087,7 @@
 Ethiopia and nations lying in the way to the jewish provinces.</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51147,7 +51156,7 @@
 can culture convert their original provinces to a new culture.</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51212,7 +51221,7 @@
 in this way.</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="45" t="s">
         <v>1931</v>
       </c>
@@ -51278,9 +51287,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="39" t="s">
-        <v>1932</v>
+        <v>2053</v>
       </c>
       <c r="B53" s="60" t="s">
         <v>1875</v>
@@ -51290,11 +51299,11 @@
       </c>
       <c r="D53" s="27">
         <f t="shared" si="1"/>
-        <v>382.85</v>
+        <v>146</v>
       </c>
       <c r="E53" s="31">
         <f>D53/'Top 10 Hard'!$J$2</f>
-        <v>1.0356786352901722E-2</v>
+        <v>3.9495646010804528E-3</v>
       </c>
       <c r="F53" s="31">
         <f>IF(NOT(ISNUMBER(F52)),0,F52)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -51345,7 +51354,7 @@
 due to the unique government reform.</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51357,11 +51366,11 @@
       </c>
       <c r="D54" s="27">
         <f t="shared" si="1"/>
-        <v>382.85</v>
+        <v>236.85</v>
       </c>
       <c r="E54" s="31">
         <f>D54/'Top 10 Hard'!$J$2</f>
-        <v>1.0356786352901722E-2</v>
+        <v>6.4072217518212687E-3</v>
       </c>
       <c r="F54" s="31">
         <f>IF(NOT(ISNUMBER(F53)),0,F53)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -51409,7 +51418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51421,11 +51430,11 @@
       </c>
       <c r="D55" s="27">
         <f t="shared" si="1"/>
-        <v>382.85</v>
+        <v>236.85</v>
       </c>
       <c r="E55" s="31">
         <f>D55/'Top 10 Hard'!$J$2</f>
-        <v>1.0356786352901722E-2</v>
+        <v>6.4072217518212687E-3</v>
       </c>
       <c r="F55" s="31">
         <f>IF(NOT(ISNUMBER(F54)),0,F54)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -51482,7 +51491,7 @@
 Sacraments” (*+2.5%*)</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51494,11 +51503,11 @@
       </c>
       <c r="D56" s="27">
         <f t="shared" si="1"/>
-        <v>382.85</v>
+        <v>236.85</v>
       </c>
       <c r="E56" s="31">
         <f>D56/'Top 10 Hard'!$J$2</f>
-        <v>1.0356786352901722E-2</v>
+        <v>6.4072217518212687E-3</v>
       </c>
       <c r="F56" s="31">
         <f>IF(NOT(ISNUMBER(F55)),0,F55)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -51552,7 +51561,7 @@
 declines the PU is also a viable strategy.</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="45" t="s">
         <v>1933</v>
       </c>
@@ -51617,7 +51626,7 @@
 suffice.</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="39" t="s">
         <v>1934</v>
       </c>
@@ -51687,7 +51696,7 @@
 new capital.</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="45" t="s">
         <v>1935</v>
       </c>
@@ -51764,7 +51773,7 @@
 two are owned by Mali and one by Kong.</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51830,7 +51839,7 @@
 European majors for fighting the Turks.</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51893,7 +51902,7 @@
 religion by rebels.</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="45" t="s">
         <v>1937</v>
       </c>
@@ -51966,7 +51975,7 @@
 Africa. The provinces do not need to be cored.</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="39" t="s">
         <v>1938</v>
       </c>
@@ -52031,7 +52040,7 @@
 Valencia.</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="45" t="s">
         <v>1939</v>
       </c>
@@ -52097,7 +52106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="39" t="s">
         <v>1940</v>
       </c>
@@ -52109,11 +52118,11 @@
       </c>
       <c r="D65" s="27">
         <f t="shared" si="1"/>
-        <v>292.5</v>
+        <v>144</v>
       </c>
       <c r="E65" s="31">
         <f>D65/'Top 10 Hard'!$J$2</f>
-        <v>7.9126551083289892E-3</v>
+        <v>3.8954609764081179E-3</v>
       </c>
       <c r="F65" s="31">
         <f>IF(NOT(ISNUMBER(F64)),0,F64)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -52159,9 +52168,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="39" t="s">
-        <v>1940</v>
+        <v>2052</v>
       </c>
       <c r="B66" s="60" t="s">
         <v>1802</v>
@@ -52171,11 +52180,11 @@
       </c>
       <c r="D66" s="27">
         <f t="shared" ref="D66:D97" si="2">SUMIFS($L:$L,$A:$A,$A66)</f>
-        <v>292.5</v>
+        <v>148.5</v>
       </c>
       <c r="E66" s="31">
         <f>D66/'Top 10 Hard'!$J$2</f>
-        <v>7.9126551083289892E-3</v>
+        <v>4.0171941319208718E-3</v>
       </c>
       <c r="F66" s="31">
         <f>IF(NOT(ISNUMBER(F65)),0,F65)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -52239,7 +52248,7 @@
 gaining Azov early in the game.</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="45" t="s">
         <v>1941</v>
       </c>
@@ -52306,7 +52315,7 @@
 provinces with the correct trade goods.</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="39" t="s">
         <v>1942</v>
       </c>
@@ -52368,7 +52377,7 @@
         <v>Easiest as Malacca or Pasai.</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="45" t="s">
         <v>1943</v>
       </c>
@@ -52429,7 +52438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="39" t="s">
         <v>1944</v>
       </c>
@@ -52493,7 +52502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="45" t="s">
         <v>1945</v>
       </c>
@@ -52563,7 +52572,7 @@
 a quarter of HRE provinces under Anglican control.</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="39" t="s">
         <v>1946</v>
       </c>
@@ -52629,7 +52638,7 @@
 vassals in your home islands to achieve this.</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52692,7 +52701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52759,7 +52768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52828,7 +52837,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="39" t="s">
         <v>1948</v>
       </c>
@@ -52909,7 +52918,7 @@
 coast, and finally down to Werder.</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="45" t="s">
         <v>1949</v>
       </c>
@@ -52973,7 +52982,7 @@
 annexed all of Livonian Order and Riga</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="39" t="s">
         <v>1950</v>
       </c>
@@ -53047,7 +53056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="45" t="s">
         <v>1951</v>
       </c>
@@ -53114,7 +53123,7 @@
 necessary.</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="39" t="s">
         <v>1952</v>
       </c>
@@ -53177,7 +53186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="45" t="s">
         <v>1953</v>
       </c>
@@ -53239,7 +53248,7 @@
         <v>Caffa is in the Pontic Steppe region, initially owned by Genoa.</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="39" t="s">
         <v>1954</v>
       </c>
@@ -53311,7 +53320,7 @@
 a lot of troops and declaring war on them once they form Prussia.</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="45" t="s">
         <v>1955</v>
       </c>
@@ -53373,7 +53382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="39" t="s">
         <v>1956</v>
       </c>
@@ -53435,7 +53444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="45" t="s">
         <v>1957</v>
       </c>
@@ -53500,7 +53509,7 @@
 this.</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="39" t="s">
         <v>1958</v>
       </c>
@@ -53564,7 +53573,7 @@
 southeast Asia</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="45" t="s">
         <v>1959</v>
       </c>
@@ -53627,7 +53636,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="39" t="s">
         <v>1960</v>
       </c>
@@ -53689,7 +53698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="45" t="s">
         <v>1961</v>
       </c>
@@ -53765,7 +53774,7 @@
 ideas are all helpful.</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="39" t="s">
         <v>1962</v>
       </c>
@@ -53829,7 +53838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="45" t="s">
         <v>1963</v>
       </c>
@@ -53892,7 +53901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="39" t="s">
         <v>1964</v>
       </c>
@@ -53957,7 +53966,7 @@
 - Making the leading tobacco producer a tributary would count.</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="45" t="s">
         <v>1965</v>
       </c>
@@ -54030,7 +54039,7 @@
 (requires having the Emperor DLC activated and the Domination not active).</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="39" t="s">
         <v>1966</v>
       </c>
@@ -54101,7 +54110,7 @@
 province, this will convert you to Coptic and grant the achievement.</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="45" t="s">
         <v>1967</v>
       </c>
@@ -54165,7 +54174,7 @@
         <v>Chinaware appears in China, Japan, Korea and the East Indies.</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54231,7 +54240,7 @@
 and/or Bohemia to defeat Hungary for the important provinces.</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54297,7 +54306,7 @@
 then sail up next to Stockholm and move your cavalry onto it.</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="45" t="s">
         <v>1969</v>
       </c>
@@ -54360,7 +54369,7 @@
         <v>Lucknow is in northern India, initially owned by Jaunpur.</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="39" t="s">
         <v>1970</v>
       </c>
@@ -54428,9 +54437,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="45" t="s">
-        <v>1920</v>
+        <v>2054</v>
       </c>
       <c r="B100" s="59" t="s">
         <v>2021</v>
@@ -54440,11 +54449,11 @@
       </c>
       <c r="D100" s="27">
         <f t="shared" si="3"/>
-        <v>438.5</v>
+        <v>148.5</v>
       </c>
       <c r="E100" s="31">
         <f>D100/'Top 10 Hard'!$J$2</f>
-        <v>1.1862219709409441E-2</v>
+        <v>4.0171941319208718E-3</v>
       </c>
       <c r="F100" s="31">
         <f>IF(NOT(ISNUMBER(F99)),0,F99)+Table1[[#This Row],[Points]]/'Top 10 Hard'!$J$2</f>
@@ -54525,7 +54534,7 @@
 a horde in this way is only possible as a migratory tribe.</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="39" t="s">
         <v>1971</v>
       </c>
@@ -54592,7 +54601,7 @@
 due to the event which spawns Kalmyk.</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54659,7 +54668,7 @@
 within a few days.</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54725,7 +54734,7 @@
 nations that can be released from Qara Qoyunlu's provinces.</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="39" t="s">
         <v>1973</v>
       </c>
@@ -54788,7 +54797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="45" t="s">
         <v>1974</v>
       </c>
@@ -54854,7 +54863,7 @@
 they produce wool.</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="39" t="s">
         <v>1975</v>
       </c>
@@ -54917,7 +54926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="45" t="s">
         <v>1976</v>
       </c>
@@ -54981,7 +54990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="39" t="s">
         <v>1977</v>
       </c>
@@ -55049,7 +55058,7 @@
 an army when Mutapa has started integrating you.</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="45" t="s">
         <v>1978</v>
       </c>
@@ -55110,7 +55119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="39" t="s">
         <v>2029</v>
       </c>
@@ -55172,7 +55181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="45" t="s">
         <v>1979</v>
       </c>
@@ -55235,7 +55244,7 @@
         <v>Has to be Protestant and lead the League.</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="39" t="s">
         <v>1980</v>
       </c>
@@ -55300,7 +55309,7 @@
 England until the time is right.</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="45" t="s">
         <v>1981</v>
       </c>
@@ -55370,7 +55379,7 @@
 then release and play as Lippe, earning you the achievement.</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55431,7 +55440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55496,7 +55505,7 @@
 Corfu will not count.</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="45" t="s">
         <v>1983</v>
       </c>
@@ -55571,7 +55580,7 @@
 which will increase your gold income, requiring less development.</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="39" t="s">
         <v>1984</v>
       </c>
@@ -55638,7 +55647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="45" t="s">
         <v>1985</v>
       </c>
@@ -55704,7 +55713,7 @@
 get the open outcome in the incident Spread of Christianity.</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="39" t="s">
         <v>1986</v>
       </c>
@@ -55767,7 +55776,7 @@
         <v>Possible starts are Dongola, Alodia, and Makuria.</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="45" t="s">
         <v>1987</v>
       </c>
@@ -55832,7 +55841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="39" t="s">
         <v>1988</v>
       </c>
@@ -55902,7 +55911,7 @@
 Flame Burning.</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="45" t="s">
         <v>1989</v>
       </c>
@@ -55981,7 +55990,7 @@
 Moravia, which can be done by Bohemia.</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="39" t="s">
         <v>1990</v>
       </c>
@@ -56049,7 +56058,7 @@
 your former overlord.</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="45" t="s">
         <v>1991</v>
       </c>
@@ -56119,7 +56128,7 @@
 ahead-of-time penalty in 1820.</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="39" t="s">
         <v>1992</v>
       </c>
@@ -56198,7 +56207,7 @@
 Simply annexing a vassal in the region won't fire the achievement.</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="45" t="s">
         <v>1993</v>
       </c>
@@ -56308,7 +56317,7 @@
 is needed to complete it.</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="39" t="s">
         <v>1994</v>
       </c>
@@ -56371,7 +56380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="45" t="s">
         <v>1995</v>
       </c>
@@ -56442,7 +56451,7 @@
 to Germany.</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="39" t="s">
         <v>1996</v>
       </c>
@@ -56515,7 +56524,7 @@
 nation doesn't work, because it counts as playing as a released vassal.</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56589,7 +56598,7 @@
 more easily if necessary.</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56652,7 +56661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56723,7 +56732,7 @@
 use their bonuses and permanent claim on the mongol region.</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="39" t="s">
         <v>1998</v>
       </c>
@@ -56792,7 +56801,7 @@
 trust with allies grows slowly over time.</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="45" t="s">
         <v>1999</v>
       </c>
@@ -56865,7 +56874,7 @@
 especially for Trier which is not the primary tag of its culture.</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="39" t="s">
         <v>2000</v>
       </c>
@@ -56934,7 +56943,7 @@
 which stacks with "Hydraulic Rights"</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="45" t="s">
         <v>2001</v>
       </c>
@@ -57016,7 +57025,7 @@
 capital provinces.</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57080,7 +57089,7 @@
 still get the achievement without having to get Norway back on the map.</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57174,7 +57183,7 @@
 tick, you had the highest income.</v>
       </c>
     </row>
-    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57250,7 +57259,7 @@
 make conversions faster, especially against Islamic provinces.</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57336,7 +57345,7 @@
 - Tripura</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="39" t="s">
         <v>2012</v>
       </c>
@@ -57432,7 +57441,7 @@
 support from a rival.</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="45" t="s">
         <v>2007</v>
       </c>
@@ -57500,7 +57509,7 @@
 galley navy and block the straits.</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57564,7 +57573,7 @@
 Ottoman Government and Sultanate of Rûm</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57626,7 +57635,7 @@
         <v>Make sure to attack Muscovy ASAP to remove a future potential threat.</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57691,7 +57700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57762,7 +57771,7 @@
 provinces needed.</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57831,7 +57840,7 @@
 Coffee achievement. Do not form Arabia</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="45" t="s">
         <v>2009</v>
       </c>
@@ -57907,7 +57916,7 @@
 Sussex, and Kent in your first war and you should be off to a great start.</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="45" t="s">
         <v>2009</v>
       </c>
@@ -57972,7 +57981,7 @@
 Dulyn(373), Lleuddiniawn(248), Rhufain(118), Paris(183) and Llundain(236)</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58037,7 +58046,7 @@
 easily after unifying the HRE.</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58106,7 +58115,7 @@
 India.</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58182,7 +58191,7 @@
 with Jihad.</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
@@ -58311,19 +58320,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06764ED-1FD3-4368-8455-971DCC0423D8}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" customWidth="1"/>
-    <col min="8" max="8" width="60.140625" customWidth="1"/>
-    <col min="9" max="9" width="43.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="7" max="7" width="28.109375" customWidth="1"/>
+    <col min="8" max="8" width="60.109375" customWidth="1"/>
+    <col min="9" max="9" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -58352,7 +58361,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>531</v>
       </c>
@@ -58411,7 +58420,7 @@
       </c>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>251</v>
       </c>
@@ -58459,7 +58468,7 @@
       </c>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -58497,7 +58506,7 @@
       </c>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>482</v>
       </c>
@@ -58545,7 +58554,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
         <v>1702</v>
       </c>
@@ -58559,7 +58568,7 @@
       <c r="I6" s="75"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>435</v>
       </c>
@@ -58598,7 +58607,7 @@
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="76" t="s">
         <v>1703</v>
       </c>
@@ -58612,7 +58621,7 @@
       <c r="I8" s="76"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>463</v>
       </c>
@@ -58649,7 +58658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="77" t="s">
         <v>1704</v>
       </c>
@@ -58663,7 +58672,7 @@
       <c r="I10" s="77"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>491</v>
       </c>
@@ -58706,7 +58715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
         <v>1705</v>
       </c>
@@ -58720,7 +58729,7 @@
       <c r="I12" s="75"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>591</v>
       </c>
@@ -58765,7 +58774,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="78" t="s">
         <v>1706</v>
       </c>
@@ -58779,7 +58788,7 @@
       <c r="I14" s="78"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" ht="216.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>588</v>
       </c>
@@ -58828,30 +58837,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" s="2"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C22" s="2"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C26" s="2"/>
     </row>
   </sheetData>
@@ -59068,19 +59077,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5325864E-31AE-48F9-AD21-970E551229EF}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" customWidth="1"/>
-    <col min="7" max="7" width="60.140625" customWidth="1"/>
-    <col min="8" max="8" width="63.140625" customWidth="1"/>
+    <col min="6" max="6" width="28.109375" customWidth="1"/>
+    <col min="7" max="7" width="60.109375" customWidth="1"/>
+    <col min="8" max="8" width="63.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="C1" s="30" t="s">
         <v>1680</v>
       </c>
@@ -59093,7 +59102,7 @@
         <v>214.75</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>634</v>
       </c>
@@ -59119,7 +59128,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>299</v>
       </c>
@@ -59163,7 +59172,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="93" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>439</v>
       </c>
@@ -59206,7 +59215,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>601</v>
       </c>
@@ -59319,9 +59328,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1BBC31-09BA-43B6-86CD-7C2F847C46AC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>434</v>
       </c>
@@ -59332,7 +59341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>242</v>
       </c>
@@ -59343,7 +59352,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
@@ -59354,7 +59363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -59365,7 +59374,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>573</v>
       </c>
@@ -59376,7 +59385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>626</v>
       </c>
@@ -59387,7 +59396,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>1669</v>
       </c>
@@ -59420,30 +59429,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFB87DA-EA4E-493C-8327-11283D76496B}">
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="55.5703125" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="8" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-    <col min="12" max="12" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.42578125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="20" width="9.140625" style="1"/>
-    <col min="21" max="21" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.5703125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="55.5546875" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="8" max="9" width="9.109375" style="1"/>
+    <col min="10" max="10" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" style="1"/>
+    <col min="12" max="12" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="20" width="9.109375" style="1"/>
+    <col min="21" max="21" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.5546875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="I1" s="1" t="s">
         <v>1672</v>
       </c>
@@ -59457,7 +59466,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.3">
       <c r="I2" s="29">
         <f>K2/J2</f>
         <v>0.59265110466075721</v>
@@ -59475,13 +59484,13 @@
         <v>267</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="J3" s="67"/>
       <c r="L3" s="1">
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="79" t="s">
         <v>1638</v>
       </c>
@@ -59515,7 +59524,7 @@
       <c r="AA4" s="82"/>
       <c r="AB4" s="21"/>
     </row>
-    <row r="5" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>1640</v>
       </c>
@@ -59595,7 +59604,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -59714,7 +59723,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -59827,7 +59836,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -59970,7 +59979,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -60083,7 +60092,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -60197,7 +60206,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -60320,7 +60329,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -60426,7 +60435,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -60551,7 +60560,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -60658,7 +60667,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -60769,7 +60778,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="80" t="s">
         <v>1652</v>
       </c>
@@ -60803,7 +60812,7 @@
       <c r="AA17" s="84"/>
       <c r="AB17" s="22"/>
     </row>
-    <row r="18" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>1640</v>
       </c>
@@ -60883,7 +60892,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -60999,7 +61008,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>2</v>
       </c>
@@ -61117,7 +61126,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -61233,7 +61242,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>4</v>
       </c>
@@ -61352,7 +61361,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>5</v>
       </c>
@@ -61457,7 +61466,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>6</v>
       </c>
@@ -61601,7 +61610,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>7</v>
       </c>
@@ -61730,7 +61739,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>8</v>
       </c>
@@ -61846,7 +61855,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>9</v>
       </c>
@@ -61952,7 +61961,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>10</v>
       </c>
@@ -62554,21 +62563,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70671CC-FD1D-40C3-A5F7-A316733B30A0}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="9.109375" style="1"/>
+    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.44140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="86" t="s">
         <v>1658</v>
       </c>
@@ -62588,7 +62597,7 @@
       <c r="N1" s="88"/>
       <c r="O1" s="88"/>
     </row>
-    <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>1640</v>
       </c>
@@ -62632,7 +62641,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -62690,7 +62699,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20">
         <v>2</v>
       </c>
@@ -62746,7 +62755,7 @@
         <v>13.15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -62804,7 +62813,7 @@
         <v>66.25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20">
         <v>4</v>
       </c>
@@ -62860,7 +62869,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -62916,7 +62925,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>6</v>
       </c>
@@ -62973,7 +62982,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -63029,7 +63038,7 @@
         <v>67.25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20">
         <v>8</v>
       </c>
@@ -63086,7 +63095,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -63143,7 +63152,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20">
         <v>10</v>
       </c>
@@ -63199,7 +63208,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="87" t="s">
         <v>1659</v>
       </c>
@@ -63219,7 +63228,7 @@
       <c r="N14" s="89"/>
       <c r="O14" s="89"/>
     </row>
-    <row r="15" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63263,7 +63272,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>1</v>
       </c>
@@ -63320,7 +63329,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20">
         <v>2</v>
       </c>
@@ -63376,7 +63385,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
         <v>3</v>
       </c>
@@ -63432,7 +63441,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>4</v>
       </c>
@@ -63489,7 +63498,7 @@
         <v>143.5</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
         <v>5</v>
       </c>
@@ -63545,7 +63554,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>6</v>
       </c>
@@ -63602,7 +63611,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
         <v>7</v>
       </c>
@@ -63659,7 +63668,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
         <v>8</v>
       </c>
@@ -63715,7 +63724,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
         <v>9</v>
       </c>
@@ -63771,7 +63780,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20">
         <v>10</v>
       </c>
@@ -63828,7 +63837,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="85" t="s">
         <v>1673</v>
       </c>
@@ -63840,7 +63849,7 @@
       <c r="G27" s="85"/>
       <c r="H27" s="85"/>
     </row>
-    <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63866,7 +63875,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
         <v>1</v>
       </c>
@@ -63899,7 +63908,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20">
         <v>2</v>
       </c>
@@ -63932,7 +63941,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
         <v>3</v>
       </c>
@@ -63965,7 +63974,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
         <v>4</v>
       </c>
@@ -63998,7 +64007,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
         <v>5</v>
       </c>
@@ -64032,7 +64041,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>6</v>
       </c>
@@ -64065,7 +64074,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
         <v>7</v>
       </c>
@@ -64098,7 +64107,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>8</v>
       </c>
@@ -64132,7 +64141,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
         <v>9</v>
       </c>
@@ -64166,7 +64175,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20">
         <v>10</v>
       </c>

--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC1C4A0-2E3E-4DC0-9BA0-0E33594ACD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D024875-7CC4-40D1-BDB1-50CCDFFBEDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="2" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
+    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="17520" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="2055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3849" uniqueCount="2055">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -13347,29 +13347,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y374"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="10" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="14" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="9.109375" style="5" collapsed="1"/>
-    <col min="16" max="16" width="14.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="28.109375" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="60.109375" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="43.33203125" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="28.109375" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="11.109375" customWidth="1"/>
-    <col min="22" max="23" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="5" collapsed="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="28.140625" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="60.140625" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="43.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="28.140625" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="11.140625" customWidth="1"/>
+    <col min="22" max="23" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -13446,7 +13447,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>568</v>
       </c>
@@ -13534,7 +13535,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>564</v>
       </c>
@@ -13624,7 +13625,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>621</v>
       </c>
@@ -13707,7 +13708,7 @@
         <v>Legacy of Saint George</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>619</v>
       </c>
@@ -13797,7 +13798,7 @@
         <v>From Frankfurt to the Andes</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>239</v>
       </c>
@@ -13882,7 +13883,7 @@
         <v>Timurizz</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>561</v>
       </c>
@@ -13972,7 +13973,7 @@
         <v>Ultimate Military</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>531</v>
       </c>
@@ -14060,7 +14061,7 @@
         <v>Triple the Rome</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>566</v>
       </c>
@@ -14143,7 +14144,7 @@
         <v>The Zoro-Austrians</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>522</v>
       </c>
@@ -14228,7 +14229,7 @@
         <v>The Freest Man in the World</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>569</v>
       </c>
@@ -14311,7 +14312,7 @@
         <v>Baborg</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>456</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>Australia-Hungary</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>633</v>
       </c>
@@ -14479,7 +14480,7 @@
         <v>Mehmet's Ambition</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>432</v>
       </c>
@@ -14569,7 +14570,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>426</v>
       </c>
@@ -14657,7 +14658,7 @@
         <v>It's all coming together</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>291</v>
       </c>
@@ -14747,7 +14748,7 @@
         <v>Hanukkah Mutapa</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>622</v>
       </c>
@@ -14835,7 +14836,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>599</v>
       </c>
@@ -14925,7 +14926,7 @@
         <v>Quizquiz Pro Quo</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>620</v>
       </c>
@@ -15015,7 +15016,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>585</v>
       </c>
@@ -15105,7 +15106,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>618</v>
       </c>
@@ -15195,7 +15196,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -15285,7 +15286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -15373,7 +15374,7 @@
         <v>Breadbasket of the World</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>567</v>
       </c>
@@ -15463,7 +15464,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>433</v>
       </c>
@@ -15553,7 +15554,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>496</v>
       </c>
@@ -15636,7 +15637,7 @@
         <v>One nation to rule them all</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>553</v>
       </c>
@@ -15721,7 +15722,7 @@
         <v>New, New Deli</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>483</v>
       </c>
@@ -15811,7 +15812,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>440</v>
       </c>
@@ -15901,7 +15902,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>451</v>
       </c>
@@ -15984,7 +15985,7 @@
         <v>Almost Prussian Blue</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>383</v>
       </c>
@@ -16069,7 +16070,7 @@
         <v>Where are the penguins?</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>430</v>
       </c>
@@ -16157,7 +16158,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>413</v>
       </c>
@@ -16240,7 +16241,7 @@
         <v>Stardust Crusaders</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>288</v>
       </c>
@@ -16330,7 +16331,7 @@
         <v>Golden Wind</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>387</v>
       </c>
@@ -16420,7 +16421,7 @@
         <v>Copium Wars</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>592</v>
       </c>
@@ -16453,27 +16454,32 @@
         <f t="shared" si="2"/>
         <v>4.5069000000000003E-3</v>
       </c>
-      <c r="J36" s="10" t="str">
+      <c r="J36" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K36" s="10">
+        <v>4.5069000000000003E-3</v>
+      </c>
+      <c r="K36" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>4.5069000000000003E-3</v>
+        <v/>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="5"/>
         <v>4.9954931</v>
       </c>
-      <c r="M36" s="9" t="str">
+      <c r="M36" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N36" s="9">
+        <v>4.9954931</v>
+      </c>
+      <c r="N36" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>4.9954931</v>
-      </c>
-      <c r="O36" s="4"/>
+        <v/>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>1883</v>
+      </c>
       <c r="Q36" s="7" t="s">
         <v>1508</v>
       </c>
@@ -16505,7 +16511,7 @@
         <v>Inner Turmoil</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>574</v>
       </c>
@@ -16590,7 +16596,7 @@
         <v>I don't like sand</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>200</v>
       </c>
@@ -16673,7 +16679,7 @@
         <v>To the Bone</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -16758,7 +16764,7 @@
         <v>Surfing USA</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>557</v>
       </c>
@@ -16843,7 +16849,7 @@
         <v>The Pheasant Strut</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>624</v>
       </c>
@@ -16928,7 +16934,7 @@
         <v>Eat your Greens</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>390</v>
       </c>
@@ -17018,7 +17024,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>338</v>
       </c>
@@ -17108,7 +17114,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>389</v>
       </c>
@@ -17196,7 +17202,7 @@
         <v>No Country for Old Tercios</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>431</v>
       </c>
@@ -17284,7 +17290,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>428</v>
       </c>
@@ -17367,7 +17373,7 @@
         <v>Doge Coins</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>208</v>
       </c>
@@ -17454,7 +17460,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>528</v>
       </c>
@@ -17537,7 +17543,7 @@
         <v>Why is the Rûm gone!?</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>555</v>
       </c>
@@ -17622,7 +17628,7 @@
         <v>The Fezzan Corridors</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>513</v>
       </c>
@@ -17707,7 +17713,7 @@
         <v>Stiff Upper Lippe</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>511</v>
       </c>
@@ -17792,7 +17798,7 @@
         <v>Stern des Südens</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>503</v>
       </c>
@@ -17877,7 +17883,7 @@
         <v>Pick Your Poison</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>499</v>
       </c>
@@ -17960,7 +17966,7 @@
         <v>Pandya Empire</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>491</v>
       </c>
@@ -18045,7 +18051,7 @@
         <v>Mass Production</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>468</v>
       </c>
@@ -18135,7 +18141,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>463</v>
       </c>
@@ -18218,7 +18224,7 @@
         <v>Dovmont's Own</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>348</v>
       </c>
@@ -18308,7 +18314,7 @@
         <v>That's No Mon</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>412</v>
       </c>
@@ -18391,7 +18397,7 @@
         <v>Sun Invasion</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>253</v>
       </c>
@@ -18479,7 +18485,7 @@
         <v>Shemot is Not</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -18569,7 +18575,7 @@
         <v>Mansa Musa</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>424</v>
       </c>
@@ -18655,7 +18661,7 @@
         <v>King of Kings</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>265</v>
       </c>
@@ -18743,7 +18749,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
@@ -18828,7 +18834,7 @@
         <v>Imposter Syndrome</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>586</v>
       </c>
@@ -18911,7 +18917,7 @@
         <v>Empire of Mann</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>583</v>
       </c>
@@ -19003,7 +19009,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>530</v>
       </c>
@@ -19088,7 +19094,7 @@
         <v>With a little help..</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>525</v>
       </c>
@@ -19173,7 +19179,7 @@
         <v>Turkish Delight</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>523</v>
       </c>
@@ -19258,7 +19264,7 @@
         <v>Tiger of Mysore</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>520</v>
       </c>
@@ -19341,7 +19347,7 @@
         <v>The 52 Garhs</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>515</v>
       </c>
@@ -19431,7 +19437,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>506</v>
       </c>
@@ -19516,7 +19522,7 @@
         <v>Protect the Secret</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>543</v>
       </c>
@@ -19599,7 +19605,7 @@
         <v>Foremost Servitor of Jagannath</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>437</v>
       </c>
@@ -19682,7 +19688,7 @@
         <v>Core-fu</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>461</v>
       </c>
@@ -19767,7 +19773,7 @@
         <v>Bunte Kuh</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>535</v>
       </c>
@@ -19850,7 +19856,7 @@
         <v>Avar Khaganate</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>355</v>
       </c>
@@ -19940,7 +19946,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>309</v>
       </c>
@@ -20025,7 +20031,7 @@
         <v>Kuban Cigars</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>283</v>
       </c>
@@ -20110,7 +20116,7 @@
         <v>Ganges Khan</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>386</v>
       </c>
@@ -20198,7 +20204,7 @@
         <v>Brentry!</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>397</v>
       </c>
@@ -20286,7 +20292,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>103</v>
       </c>
@@ -20371,7 +20377,7 @@
         <v>Truly Good Maaaaa-tch</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>614</v>
       </c>
@@ -20461,7 +20467,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>608</v>
       </c>
@@ -20546,7 +20552,7 @@
         <v>Spanish Fly</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>591</v>
       </c>
@@ -20629,7 +20635,7 @@
         <v>Great Perm</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>584</v>
       </c>
@@ -20717,7 +20723,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>139</v>
       </c>
@@ -20802,7 +20808,7 @@
         <v>Forgive me, for I have Sindh</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>509</v>
       </c>
@@ -20892,7 +20898,7 @@
         <v>Spaghetti Western</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>501</v>
       </c>
@@ -20973,7 +20979,7 @@
         <v>Philippine Tiger</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>551</v>
       </c>
@@ -21061,7 +21067,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>549</v>
       </c>
@@ -21146,7 +21152,7 @@
         <v>Meissner Porcelain</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>443</v>
       </c>
@@ -21231,7 +21237,7 @@
         <v>Kushite Restoration</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>477</v>
       </c>
@@ -21319,7 +21325,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>475</v>
       </c>
@@ -21404,7 +21410,7 @@
         <v>Holy Horder</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>541</v>
       </c>
@@ -21494,7 +21500,7 @@
         <v>Cotton Kandy</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>435</v>
       </c>
@@ -21582,7 +21588,7 @@
         <v>Breaking the Yoke</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>380</v>
       </c>
@@ -21667,7 +21673,7 @@
         <v>Victorian Three</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>337</v>
       </c>
@@ -21757,7 +21763,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>319</v>
       </c>
@@ -21847,7 +21853,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>297</v>
       </c>
@@ -21930,7 +21936,7 @@
         <v>Home and Away</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>277</v>
       </c>
@@ -22015,7 +22021,7 @@
         <v>Don’t be Cilli</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>248</v>
       </c>
@@ -22105,7 +22111,7 @@
         <v>Disciples of Enlightenment</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>613</v>
       </c>
@@ -22195,7 +22201,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>575</v>
       </c>
@@ -22280,7 +22286,7 @@
         <v>The Animal Kingdom</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>602</v>
       </c>
@@ -22365,7 +22371,7 @@
         <v>Raja of the Rajput Reich</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>597</v>
       </c>
@@ -22450,7 +22456,7 @@
         <v>Norwegian Wood</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>581</v>
       </c>
@@ -22540,7 +22546,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>577</v>
       </c>
@@ -22623,7 +22629,7 @@
         <v>Academical</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>186</v>
       </c>
@@ -22713,7 +22719,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>507</v>
       </c>
@@ -22803,7 +22809,7 @@
         <v>Sailor Mon</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>488</v>
       </c>
@@ -22888,7 +22894,7 @@
         <v>Lucky Lucca</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>547</v>
       </c>
@@ -22978,7 +22984,7 @@
         <v>Komnenoi Empire</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
@@ -23066,7 +23072,7 @@
         <v>Kinslayer</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>631</v>
       </c>
@@ -23151,7 +23157,7 @@
         <v>True Heir of Timur</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>629</v>
       </c>
@@ -23241,7 +23247,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>295</v>
       </c>
@@ -23326,7 +23332,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>404</v>
       </c>
@@ -23414,7 +23420,7 @@
         <v>For the Emperor!</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>571</v>
       </c>
@@ -23502,7 +23508,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>601</v>
       </c>
@@ -23587,7 +23593,7 @@
         <v>Rags and Riches</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>589</v>
       </c>
@@ -23672,7 +23678,7 @@
         <v>Gothic Invasion</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>170</v>
       </c>
@@ -23762,7 +23768,7 @@
         <v>On the Edge of Madness</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>215</v>
       </c>
@@ -23849,7 +23855,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>495</v>
       </c>
@@ -23937,7 +23943,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>420</v>
       </c>
@@ -24029,7 +24035,7 @@
         <v>Yarr Harr a Pirate's Life For Me</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>346</v>
       </c>
@@ -24117,7 +24123,7 @@
         <v>Tatarstan</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>334</v>
       </c>
@@ -24205,7 +24211,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -24292,7 +24298,7 @@
         <v>Rekindling the Flames</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>327</v>
       </c>
@@ -24375,7 +24381,7 @@
         <v>No Trail of Tears</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>423</v>
       </c>
@@ -24465,7 +24471,7 @@
         <v>First Come, First Serve</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>99</v>
       </c>
@@ -24552,7 +24558,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>611</v>
       </c>
@@ -24642,7 +24648,7 @@
         <v>The Buddhists Strike Back</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>595</v>
       </c>
@@ -24728,7 +24734,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>593</v>
       </c>
@@ -24818,7 +24824,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>588</v>
       </c>
@@ -24908,7 +24914,7 @@
         <v>Frozen Assets</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>579</v>
       </c>
@@ -24996,7 +25002,7 @@
         <v>Albania or Iberia</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>199</v>
       </c>
@@ -25081,7 +25087,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>235</v>
       </c>
@@ -25173,7 +25179,7 @@
         <v>Østindisk Kompagni Te</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>128</v>
       </c>
@@ -25258,7 +25264,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>119</v>
       </c>
@@ -25346,7 +25352,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>527</v>
       </c>
@@ -25436,7 +25442,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>466</v>
       </c>
@@ -25526,7 +25532,7 @@
         <v>Emperor of Hindustan</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>540</v>
       </c>
@@ -25611,7 +25617,7 @@
         <v>Choson One</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>458</v>
       </c>
@@ -25699,7 +25705,7 @@
         <v>Back to the Piast</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>258</v>
       </c>
@@ -25782,7 +25788,7 @@
         <v>Turn the Table</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>366</v>
       </c>
@@ -25872,7 +25878,7 @@
         <v>The Sudanese Expedition</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>610</v>
       </c>
@@ -25962,7 +25968,7 @@
         <v>Sunset Invasion</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>604</v>
       </c>
@@ -26052,7 +26058,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>126</v>
       </c>
@@ -26144,7 +26150,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>121</v>
       </c>
@@ -26234,7 +26240,7 @@
         <v>Brick by Brick</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>565</v>
       </c>
@@ -26324,7 +26330,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>516</v>
       </c>
@@ -26412,7 +26418,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>445</v>
       </c>
@@ -26497,7 +26503,7 @@
         <v>Rise of the White Sheep</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>563</v>
       </c>
@@ -26585,7 +26591,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>444</v>
       </c>
@@ -26673,7 +26679,7 @@
         <v>Lessons of Hemmingstedt</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>484</v>
       </c>
@@ -26756,7 +26762,7 @@
         <v>Lazarus</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>479</v>
       </c>
@@ -26844,7 +26850,7 @@
         <v>Keep the Flame Burning</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -26932,7 +26938,7 @@
         <v>Auld Alliance Reversed</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>378</v>
       </c>
@@ -27022,7 +27028,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>362</v>
       </c>
@@ -27112,7 +27118,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>321</v>
       </c>
@@ -27200,7 +27206,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>289</v>
       </c>
@@ -27283,7 +27289,7 @@
         <v>Great Moravia</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>287</v>
       </c>
@@ -27368,7 +27374,7 @@
         <v>Golden Horn</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>83</v>
       </c>
@@ -27451,7 +27457,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>184</v>
       </c>
@@ -27536,7 +27542,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -27626,7 +27632,7 @@
         <v>Holy Trinity</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>471</v>
       </c>
@@ -27716,7 +27722,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>439</v>
       </c>
@@ -27808,7 +27814,7 @@
         <v>For Odin!</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>465</v>
       </c>
@@ -27898,7 +27904,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>533</v>
       </c>
@@ -27988,7 +27994,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>449</v>
       </c>
@@ -28073,7 +28079,7 @@
         <v>A Hero’s Welcome</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>627</v>
       </c>
@@ -28156,7 +28162,7 @@
         <v>One Faith</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>372</v>
       </c>
@@ -28239,7 +28245,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>418</v>
       </c>
@@ -28329,7 +28335,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>328</v>
       </c>
@@ -28412,7 +28418,7 @@
         <v>Parisian Pasha</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>317</v>
       </c>
@@ -28502,7 +28508,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>293</v>
       </c>
@@ -28585,7 +28591,7 @@
         <v>Hessian Mercenaries</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>267</v>
       </c>
@@ -28675,7 +28681,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>24</v>
       </c>
@@ -28762,7 +28768,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -28847,7 +28853,7 @@
         <v>Rozwi Empire</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
@@ -28937,7 +28943,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>154</v>
       </c>
@@ -29027,7 +29033,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>556</v>
       </c>
@@ -29117,7 +29123,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>419</v>
       </c>
@@ -29209,7 +29215,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>350</v>
       </c>
@@ -29297,7 +29303,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>336</v>
       </c>
@@ -29380,7 +29386,7 @@
         <v>Sons of Carthage</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>243</v>
       </c>
@@ -29470,7 +29476,7 @@
         <v>Abu Bakr II’s Ambition</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>214</v>
       </c>
@@ -29560,7 +29566,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -29645,7 +29651,7 @@
         <v>The Uncommonwealth</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>361</v>
       </c>
@@ -29735,7 +29741,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>357</v>
       </c>
@@ -29825,7 +29831,7 @@
         <v>The Levant Turnabout</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>352</v>
       </c>
@@ -29913,7 +29919,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>254</v>
       </c>
@@ -29996,7 +30002,7 @@
         <v>Sweet Home Qaraqorum</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>405</v>
       </c>
@@ -30086,7 +30092,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>299</v>
       </c>
@@ -30178,7 +30184,7 @@
         <v>Ideas Guy</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>269</v>
       </c>
@@ -30261,7 +30267,7 @@
         <v>Bengal Tiger</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>260</v>
       </c>
@@ -30353,7 +30359,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>161</v>
       </c>
@@ -30443,7 +30449,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>152</v>
       </c>
@@ -30533,7 +30539,7 @@
         <v>Kow-Tow</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>370</v>
       </c>
@@ -30621,7 +30627,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>422</v>
       </c>
@@ -30711,7 +30717,7 @@
         <v>A Sun God</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>469</v>
       </c>
@@ -30803,7 +30809,7 @@
         <v>Forever Golden</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>344</v>
       </c>
@@ -30893,7 +30899,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>342</v>
       </c>
@@ -30983,7 +30989,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>308</v>
       </c>
@@ -31073,7 +31079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>398</v>
       </c>
@@ -31161,7 +31167,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>59</v>
       </c>
@@ -31246,7 +31252,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>221</v>
       </c>
@@ -31336,7 +31342,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>176</v>
       </c>
@@ -31419,7 +31425,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>157</v>
       </c>
@@ -31509,7 +31515,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>147</v>
       </c>
@@ -31599,7 +31605,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>117</v>
       </c>
@@ -31684,7 +31690,7 @@
         <v>Baa Baa Black Sheep</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>558</v>
       </c>
@@ -31774,7 +31780,7 @@
         <v>The Re-Reconquista</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>480</v>
       </c>
@@ -31864,7 +31870,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>545</v>
       </c>
@@ -31952,7 +31958,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>452</v>
       </c>
@@ -32044,7 +32050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>359</v>
       </c>
@@ -32134,7 +32140,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>353</v>
       </c>
@@ -32222,7 +32228,7 @@
         <v>The Iron Price</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>36</v>
       </c>
@@ -32305,7 +32311,7 @@
         <v>Krabater</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>146</v>
       </c>
@@ -32395,7 +32401,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>560</v>
       </c>
@@ -32483,7 +32489,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>505</v>
       </c>
@@ -32573,7 +32579,7 @@
         <v>Prester John</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>460</v>
       </c>
@@ -32663,7 +32669,7 @@
         <v>Baltic Crusader</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>411</v>
       </c>
@@ -32748,7 +32754,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>333</v>
       </c>
@@ -32836,7 +32842,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>330</v>
       </c>
@@ -32926,7 +32932,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>402</v>
       </c>
@@ -33016,7 +33022,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>486</v>
       </c>
@@ -33101,7 +33107,7 @@
         <v>Luck of the Irish</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>441</v>
       </c>
@@ -33189,7 +33195,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>538</v>
       </c>
@@ -33279,7 +33285,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>93</v>
       </c>
@@ -33369,7 +33375,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>616</v>
       </c>
@@ -33459,7 +33465,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
@@ -33545,7 +33551,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>400</v>
       </c>
@@ -33633,7 +33639,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -33721,7 +33727,7 @@
         <v>A Blessed Nation</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>240</v>
       </c>
@@ -33811,7 +33817,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>279</v>
       </c>
@@ -33894,7 +33900,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>164</v>
       </c>
@@ -33982,7 +33988,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>312</v>
       </c>
@@ -34067,7 +34073,7 @@
         <v>Lion of the North</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>518</v>
       </c>
@@ -34155,7 +34161,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>310</v>
       </c>
@@ -34243,7 +34249,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>606</v>
       </c>
@@ -34333,7 +34339,7 @@
         <v>Shahanshah</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>473</v>
       </c>
@@ -34416,7 +34422,7 @@
         <v>Guarantor of Peace</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>409</v>
       </c>
@@ -34506,7 +34512,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>251</v>
       </c>
@@ -34596,7 +34602,7 @@
         <v>Relentless Push East</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>306</v>
       </c>
@@ -34684,7 +34690,7 @@
         <v>Kingdom of God</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>273</v>
       </c>
@@ -34772,7 +34778,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>97</v>
       </c>
@@ -34855,7 +34861,7 @@
         <v>Poland can into space</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>22</v>
       </c>
@@ -34947,7 +34953,7 @@
         <v>Foul Mouthed</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>143</v>
       </c>
@@ -35037,7 +35043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>104</v>
       </c>
@@ -35127,7 +35133,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>263</v>
       </c>
@@ -35215,7 +35221,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>166</v>
       </c>
@@ -35303,7 +35309,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>112</v>
       </c>
@@ -35389,7 +35395,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>285</v>
       </c>
@@ -35479,7 +35485,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>168</v>
       </c>
@@ -35569,7 +35575,7 @@
         <v>Nobody wants to die</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>493</v>
       </c>
@@ -35654,7 +35660,7 @@
         <v>Master of India</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>231</v>
       </c>
@@ -35740,7 +35746,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>340</v>
       </c>
@@ -35828,7 +35834,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>202</v>
       </c>
@@ -35918,7 +35924,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>196</v>
       </c>
@@ -36006,7 +36012,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>364</v>
       </c>
@@ -36096,7 +36102,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>275</v>
       </c>
@@ -36179,7 +36185,7 @@
         <v>Definitely the Sultan of Rum</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>48</v>
       </c>
@@ -36267,7 +36273,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>497</v>
       </c>
@@ -36355,7 +36361,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>209</v>
       </c>
@@ -36438,7 +36444,7 @@
         <v>Winged Hussars</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>173</v>
       </c>
@@ -36521,7 +36527,7 @@
         <v>One King to Rule!</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>490</v>
       </c>
@@ -36611,7 +36617,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>256</v>
       </c>
@@ -36694,7 +36700,7 @@
         <v>The Spice Must Flow</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>259</v>
       </c>
@@ -36777,7 +36783,7 @@
         <v>A tale of two Families</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>129</v>
       </c>
@@ -36865,7 +36871,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>416</v>
       </c>
@@ -36953,7 +36959,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>393</v>
       </c>
@@ -37043,7 +37049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>34</v>
       </c>
@@ -37128,7 +37134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>373</v>
       </c>
@@ -37216,7 +37222,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>325</v>
       </c>
@@ -37304,7 +37310,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>247</v>
       </c>
@@ -37392,7 +37398,7 @@
         <v>Black Jack</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1677</v>
       </c>
@@ -37482,7 +37488,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>210</v>
       </c>
@@ -37572,7 +37578,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>190</v>
       </c>
@@ -37664,7 +37670,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>106</v>
       </c>
@@ -37754,7 +37760,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>130</v>
       </c>
@@ -37837,7 +37843,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>537</v>
       </c>
@@ -37925,7 +37931,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>381</v>
       </c>
@@ -38013,7 +38019,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>13</v>
       </c>
@@ -38103,7 +38109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>38</v>
       </c>
@@ -38191,7 +38197,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>148</v>
       </c>
@@ -38279,7 +38285,7 @@
         <v>Imperio español</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>384</v>
       </c>
@@ -38369,7 +38375,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>204</v>
       </c>
@@ -38457,7 +38463,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>300</v>
       </c>
@@ -38547,7 +38553,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>89</v>
       </c>
@@ -38635,7 +38641,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>376</v>
       </c>
@@ -38720,7 +38726,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>124</v>
       </c>
@@ -38808,7 +38814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>144</v>
       </c>
@@ -38896,7 +38902,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>233</v>
       </c>
@@ -38984,7 +38990,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>229</v>
       </c>
@@ -39072,7 +39078,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>414</v>
       </c>
@@ -39162,7 +39168,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>391</v>
       </c>
@@ -39247,7 +39253,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>3</v>
       </c>
@@ -39335,7 +39341,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>63</v>
       </c>
@@ -39422,7 +39428,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>304</v>
       </c>
@@ -39512,7 +39518,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>281</v>
       </c>
@@ -39604,7 +39610,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>101</v>
       </c>
@@ -39689,7 +39695,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>25</v>
       </c>
@@ -39777,7 +39783,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>141</v>
       </c>
@@ -39865,7 +39871,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>133</v>
       </c>
@@ -39952,7 +39958,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>395</v>
       </c>
@@ -40038,7 +40044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>40</v>
       </c>
@@ -40128,7 +40134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>212</v>
       </c>
@@ -40216,7 +40222,7 @@
         <v>A Fine Goosestep</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>323</v>
       </c>
@@ -40306,7 +40312,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>137</v>
       </c>
@@ -40396,7 +40402,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>250</v>
       </c>
@@ -40486,7 +40492,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>108</v>
       </c>
@@ -40574,7 +40580,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>223</v>
       </c>
@@ -40664,7 +40670,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>159</v>
       </c>
@@ -40752,7 +40758,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>175</v>
       </c>
@@ -40840,7 +40846,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>163</v>
       </c>
@@ -40930,7 +40936,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>262</v>
       </c>
@@ -41018,7 +41024,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>95</v>
       </c>
@@ -41106,7 +41112,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>49</v>
       </c>
@@ -41196,7 +41202,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>5</v>
       </c>
@@ -41286,7 +41292,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>313</v>
       </c>
@@ -41371,7 +41377,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>85</v>
       </c>
@@ -41459,7 +41465,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>271</v>
       </c>
@@ -41547,7 +41553,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>172</v>
       </c>
@@ -41635,7 +41641,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>75</v>
       </c>
@@ -41720,7 +41726,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>227</v>
       </c>
@@ -41810,7 +41816,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>42</v>
       </c>
@@ -41900,7 +41906,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>206</v>
       </c>
@@ -41988,7 +41994,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>203</v>
       </c>
@@ -42078,7 +42084,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>302</v>
       </c>
@@ -42166,7 +42172,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>135</v>
       </c>
@@ -42253,7 +42259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>219</v>
       </c>
@@ -42341,7 +42347,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>57</v>
       </c>
@@ -42429,7 +42435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>110</v>
       </c>
@@ -42519,7 +42525,7 @@
         <v>All belongs to Mother Russia</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>87</v>
       </c>
@@ -42605,7 +42611,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>113</v>
       </c>
@@ -42695,7 +42701,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>18</v>
       </c>
@@ -42778,7 +42784,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>65</v>
       </c>
@@ -42866,7 +42872,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>315</v>
       </c>
@@ -42954,7 +42960,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>192</v>
       </c>
@@ -43044,7 +43050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>30</v>
       </c>
@@ -43134,7 +43140,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>61</v>
       </c>
@@ -43222,7 +43228,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>122</v>
       </c>
@@ -43311,7 +43317,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>194</v>
       </c>
@@ -43397,7 +43403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>0</v>
       </c>
@@ -43484,7 +43490,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>81</v>
       </c>
@@ -43572,7 +43578,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>131</v>
       </c>
@@ -43660,7 +43666,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>225</v>
       </c>
@@ -43745,7 +43751,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>115</v>
       </c>
@@ -43835,7 +43841,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>245</v>
       </c>
@@ -43920,7 +43926,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>7</v>
       </c>
@@ -44005,7 +44011,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>217</v>
       </c>
@@ -44090,7 +44096,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>374</v>
       </c>
@@ -44173,7 +44179,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>180</v>
       </c>
@@ -44258,7 +44264,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>16</v>
       </c>
@@ -44348,7 +44354,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>44</v>
       </c>
@@ -44431,7 +44437,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>27</v>
       </c>
@@ -44518,7 +44524,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>77</v>
       </c>
@@ -44603,7 +44609,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>69</v>
       </c>
@@ -44690,7 +44696,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -44777,7 +44783,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>150</v>
       </c>
@@ -44862,7 +44868,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>91</v>
       </c>
@@ -44947,7 +44953,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>198</v>
       </c>
@@ -45037,7 +45043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>14</v>
       </c>
@@ -45124,7 +45130,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>32</v>
       </c>
@@ -45209,7 +45215,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>67</v>
       </c>
@@ -45296,7 +45302,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -45381,7 +45387,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>20</v>
       </c>
@@ -45466,7 +45472,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>55</v>
       </c>
@@ -45551,7 +45557,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>46</v>
       </c>
@@ -45634,7 +45640,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>79</v>
       </c>
@@ -45717,7 +45723,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>51</v>
       </c>
@@ -45800,7 +45806,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>53</v>
       </c>
@@ -45887,7 +45893,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>73</v>
       </c>
@@ -45972,7 +45978,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>71</v>
       </c>
@@ -46060,7 +46066,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y374" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}"/>
+  <autoFilter ref="A1:Y374" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Inner Turmoil"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="393" priority="379">
@@ -46139,17 +46151,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16ACCB4E-C812-42E5-BA87-3FBA0B83A629}">
   <dimension ref="A1:F116"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.44140625" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="6" width="125.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="125.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>1747</v>
       </c>
@@ -46169,7 +46181,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>1713</v>
       </c>
@@ -46178,7 +46190,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>1714</v>
       </c>
@@ -46192,7 +46204,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>1715</v>
       </c>
@@ -46200,7 +46212,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>1748</v>
       </c>
@@ -46208,7 +46220,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>1716</v>
       </c>
@@ -46216,7 +46228,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>1749</v>
       </c>
@@ -46224,7 +46236,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>1717</v>
       </c>
@@ -46238,7 +46250,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
         <v>1675</v>
       </c>
@@ -46252,7 +46264,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>1750</v>
       </c>
@@ -46266,7 +46278,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>1718</v>
       </c>
@@ -46274,7 +46286,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
         <v>1719</v>
       </c>
@@ -46282,7 +46294,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
         <v>1751</v>
       </c>
@@ -46290,7 +46302,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
         <v>1752</v>
       </c>
@@ -46298,7 +46310,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
         <v>1689</v>
       </c>
@@ -46306,7 +46318,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>1720</v>
       </c>
@@ -46314,7 +46326,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
         <v>1721</v>
       </c>
@@ -46328,7 +46340,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>1753</v>
       </c>
@@ -46342,7 +46354,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>1754</v>
       </c>
@@ -46356,7 +46368,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>1755</v>
       </c>
@@ -46364,7 +46376,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>1756</v>
       </c>
@@ -46372,7 +46384,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
         <v>1757</v>
       </c>
@@ -46386,7 +46398,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35" t="s">
         <v>1758</v>
       </c>
@@ -46400,7 +46412,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>1759</v>
       </c>
@@ -46408,7 +46420,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>1684</v>
       </c>
@@ -46422,7 +46434,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
         <v>1722</v>
       </c>
@@ -46436,7 +46448,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="35" t="s">
         <v>1826</v>
       </c>
@@ -46450,7 +46462,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
         <v>1676</v>
       </c>
@@ -46458,7 +46470,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
         <v>1760</v>
       </c>
@@ -46466,7 +46478,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
         <v>756</v>
       </c>
@@ -46480,7 +46492,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
         <v>1723</v>
       </c>
@@ -46494,7 +46506,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
         <v>1761</v>
       </c>
@@ -46502,7 +46514,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="35" t="s">
         <v>1724</v>
       </c>
@@ -46510,7 +46522,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
         <v>289</v>
       </c>
@@ -46524,7 +46536,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
         <v>1762</v>
       </c>
@@ -46532,7 +46544,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="35" t="s">
         <v>1763</v>
       </c>
@@ -46540,7 +46552,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="35" t="s">
         <v>1764</v>
       </c>
@@ -46548,7 +46560,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>1765</v>
       </c>
@@ -46556,7 +46568,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
         <v>1725</v>
       </c>
@@ -46564,7 +46576,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="35" t="s">
         <v>1726</v>
       </c>
@@ -46572,7 +46584,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="35" t="s">
         <v>1710</v>
       </c>
@@ -46580,7 +46592,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
         <v>1766</v>
       </c>
@@ -46588,7 +46600,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="35" t="s">
         <v>1767</v>
       </c>
@@ -46596,7 +46608,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="35" t="s">
         <v>1768</v>
       </c>
@@ -46616,7 +46628,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
         <v>1769</v>
       </c>
@@ -46624,7 +46636,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="35" t="s">
         <v>1770</v>
       </c>
@@ -46632,7 +46644,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="35" t="s">
         <v>1727</v>
       </c>
@@ -46640,7 +46652,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
         <v>1728</v>
       </c>
@@ -46654,7 +46666,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="35" t="s">
         <v>1771</v>
       </c>
@@ -46662,7 +46674,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="35" t="s">
         <v>1772</v>
       </c>
@@ -46670,7 +46682,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="35" t="s">
         <v>765</v>
       </c>
@@ -46678,7 +46690,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="35" t="s">
         <v>1773</v>
       </c>
@@ -46686,7 +46698,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="35" t="s">
         <v>1777</v>
       </c>
@@ -46694,7 +46706,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
         <v>1774</v>
       </c>
@@ -46702,7 +46714,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="35" t="s">
         <v>1775</v>
       </c>
@@ -46710,7 +46722,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="35" t="s">
         <v>1776</v>
       </c>
@@ -46724,7 +46736,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="35" t="s">
         <v>1729</v>
       </c>
@@ -46732,7 +46744,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
         <v>1778</v>
       </c>
@@ -46740,7 +46752,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="35" t="s">
         <v>1779</v>
       </c>
@@ -46748,7 +46760,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="35" t="s">
         <v>1780</v>
       </c>
@@ -46762,7 +46774,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A61" s="35" t="s">
         <v>1781</v>
       </c>
@@ -46776,7 +46788,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="35" t="s">
         <v>1782</v>
       </c>
@@ -46796,7 +46808,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="35" t="s">
         <v>1783</v>
       </c>
@@ -46804,7 +46816,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="35" t="s">
         <v>1784</v>
       </c>
@@ -46812,7 +46824,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="35" t="s">
         <v>1785</v>
       </c>
@@ -46820,7 +46832,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="35" t="s">
         <v>1730</v>
       </c>
@@ -46834,7 +46846,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="35" t="s">
         <v>1731</v>
       </c>
@@ -46842,7 +46854,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="35" t="s">
         <v>1732</v>
       </c>
@@ -46856,7 +46868,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="35" t="s">
         <v>1786</v>
       </c>
@@ -46870,7 +46882,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="35" t="s">
         <v>1787</v>
       </c>
@@ -46878,7 +46890,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A71" s="35" t="s">
         <v>1733</v>
       </c>
@@ -46898,7 +46910,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="35" t="s">
         <v>1788</v>
       </c>
@@ -46906,7 +46918,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
         <v>1789</v>
       </c>
@@ -46920,7 +46932,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
         <v>1790</v>
       </c>
@@ -46928,7 +46940,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
         <v>1791</v>
       </c>
@@ -46936,7 +46948,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
         <v>1792</v>
       </c>
@@ -46944,7 +46956,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>1734</v>
       </c>
@@ -46964,7 +46976,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
         <v>1735</v>
       </c>
@@ -46984,7 +46996,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
         <v>1793</v>
       </c>
@@ -46998,7 +47010,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
         <v>1794</v>
       </c>
@@ -47006,7 +47018,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
         <v>1795</v>
       </c>
@@ -47020,7 +47032,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
         <v>1796</v>
       </c>
@@ -47034,7 +47046,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
         <v>1736</v>
       </c>
@@ -47042,7 +47054,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
         <v>1797</v>
       </c>
@@ -47050,7 +47062,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="35" t="s">
         <v>1737</v>
       </c>
@@ -47058,7 +47070,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
         <v>1798</v>
       </c>
@@ -47066,7 +47078,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="35" t="s">
         <v>182</v>
       </c>
@@ -47074,7 +47086,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
         <v>1738</v>
       </c>
@@ -47094,7 +47106,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
         <v>1739</v>
       </c>
@@ -47114,7 +47126,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
         <v>1799</v>
       </c>
@@ -47122,7 +47134,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
         <v>1800</v>
       </c>
@@ -47130,7 +47142,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="35" t="s">
         <v>1801</v>
       </c>
@@ -47138,7 +47150,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
         <v>1740</v>
       </c>
@@ -47146,7 +47158,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="35" t="s">
         <v>1802</v>
       </c>
@@ -47160,7 +47172,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="35" t="s">
         <v>1803</v>
       </c>
@@ -47168,7 +47180,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="35" t="s">
         <v>1804</v>
       </c>
@@ -47176,7 +47188,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="35" t="s">
         <v>1805</v>
       </c>
@@ -47184,7 +47196,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="35" t="s">
         <v>1806</v>
       </c>
@@ -47192,7 +47204,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="35" t="s">
         <v>1807</v>
       </c>
@@ -47200,7 +47212,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="35" t="s">
         <v>1741</v>
       </c>
@@ -47214,7 +47226,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="35" t="s">
         <v>1808</v>
       </c>
@@ -47222,7 +47234,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="35" t="s">
         <v>764</v>
       </c>
@@ -47230,7 +47242,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="35" t="s">
         <v>1742</v>
       </c>
@@ -47238,7 +47250,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A104" s="35" t="s">
         <v>1743</v>
       </c>
@@ -47252,7 +47264,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="35" t="s">
         <v>1809</v>
       </c>
@@ -47260,7 +47272,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="35" t="s">
         <v>1810</v>
       </c>
@@ -47274,7 +47286,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="35" t="s">
         <v>1811</v>
       </c>
@@ -47282,7 +47294,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="35" t="s">
         <v>1812</v>
       </c>
@@ -47296,7 +47308,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="35" t="s">
         <v>1813</v>
       </c>
@@ -47304,7 +47316,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="35" t="s">
         <v>1814</v>
       </c>
@@ -47312,7 +47324,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="35" t="s">
         <v>1744</v>
       </c>
@@ -47328,7 +47340,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="35" t="s">
         <v>1815</v>
       </c>
@@ -47336,7 +47348,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="35" t="s">
         <v>1816</v>
       </c>
@@ -47344,7 +47356,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="35" t="s">
         <v>1817</v>
       </c>
@@ -47358,7 +47370,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="35" t="s">
         <v>1745</v>
       </c>
@@ -47366,7 +47378,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="35" t="s">
         <v>1746</v>
       </c>
@@ -47731,26 +47743,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB4F934-B5CD-4C00-8D57-A5021FDDF4F5}">
   <dimension ref="A1:P153"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="66" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="31.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="58" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="28.109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="34.44140625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="60.109375" customWidth="1"/>
-    <col min="16" max="16" width="63.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="66" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="58" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="28.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="34.42578125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="60.140625" customWidth="1"/>
+    <col min="16" max="16" width="63.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>1856</v>
       </c>
@@ -47800,7 +47812,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
         <v>2044</v>
       </c>
@@ -47854,7 +47866,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>2031</v>
       </c>
@@ -47920,7 +47932,7 @@
 mission Ratify the Kalmar Union while having the reform Kalmar Union.</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>2031</v>
       </c>
@@ -47983,7 +47995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48047,7 +48059,7 @@
 Asia. Then form a claim in Ayutthaya or wait for Mingsplosion.</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48122,7 +48134,7 @@
 - Switching to play as a released vassal will invalidate the achievement.</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48223,7 +48235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48293,7 +48305,7 @@
 pretty easy without it.</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48364,7 +48376,7 @@
 the Siberian ports has already been cored or fully colonized.</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48425,7 +48437,7 @@
         <v>Easiest to do as Muscovy.</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48498,7 +48510,7 @@
 Sea ̦; it can be counterbalanced by building lots of light ships.</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48566,7 +48578,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48628,7 +48640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48692,7 +48704,7 @@
 modifier. This will deter nearby attackers as you expand opportunistically.</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48754,7 +48766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48828,7 +48840,7 @@
 Rekindling the Flames.</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>2036</v>
       </c>
@@ -48900,7 +48912,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
         <v>2036</v>
       </c>
@@ -48971,7 +48983,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
         <v>2036</v>
       </c>
@@ -49038,7 +49050,7 @@
 scornfully insult 10 of Lithuania's 11 neighbours.</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49105,7 +49117,7 @@
 to that number later.</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49177,7 +49189,7 @@
 aspect.</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49250,7 +49262,7 @@
 colonize yourself.</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49317,7 +49329,7 @@
 possible to get the achievement without that DLC.</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49380,7 +49392,7 @@
 colonizing the NA lands may result in their capital being in NA.</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49444,7 +49456,7 @@
 partnered with The Buddhists Strike Back.</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49511,7 +49523,7 @@
 playing as Kandy, you'll likely also get the achievement Cotton Kandy.</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
         <v>2040</v>
       </c>
@@ -49575,7 +49587,7 @@
 be achieved even without the DLC.</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
         <v>2041</v>
       </c>
@@ -49640,7 +49652,7 @@
 these will immediately make you an empire.</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="39" t="s">
         <v>2043</v>
       </c>
@@ -49705,7 +49717,7 @@
 Philippine islands are an excellent place to start forcing conversions.</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="39" t="s">
         <v>2042</v>
       </c>
@@ -49787,7 +49799,7 @@
 Emperor.</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39" t="s">
         <v>1920</v>
       </c>
@@ -49850,7 +49862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="45" t="s">
         <v>1921</v>
       </c>
@@ -49922,7 +49934,7 @@
 Secretive personality which gives *+20%* foreign spy detection.</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="39" t="s">
         <v>1922</v>
       </c>
@@ -49989,7 +50001,7 @@
 provinces by calling them to war as ally before subjugating them.</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
         <v>1922</v>
       </c>
@@ -50054,7 +50066,7 @@
 the province sooner.</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50119,7 +50131,7 @@
 map which can't be earned by playing that custom nation.</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50187,7 +50199,7 @@
 to protect them while you improve relations.</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50253,7 +50265,7 @@
 releasing client states.</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50322,7 +50334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50384,7 +50396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50451,7 +50463,7 @@
 Aragon.</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50521,7 +50533,7 @@
 does not change your missions).</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50584,7 +50596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50654,7 +50666,7 @@
 animist) after hitting 95 doom will also not prevent the achievement.</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50726,7 +50738,7 @@
 take capitals without the need of conquering a lot of adjacent provinces.</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50797,7 +50809,7 @@
 you can finish, it may be easier to allow a colonial nation to form.</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50877,7 +50889,7 @@
 rapidly across the continent at the cost of diplomatic power.</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45" t="s">
         <v>2047</v>
       </c>
@@ -50943,7 +50955,7 @@
 economy of Spain.</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
         <v>1928</v>
       </c>
@@ -51015,7 +51027,7 @@
 country will count for the achievement.</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45" t="s">
         <v>1929</v>
       </c>
@@ -51087,7 +51099,7 @@
 Ethiopia and nations lying in the way to the jewish provinces.</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51156,7 +51168,7 @@
 can culture convert their original provinces to a new culture.</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51221,7 +51233,7 @@
 in this way.</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="45" t="s">
         <v>1931</v>
       </c>
@@ -51287,7 +51299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="39" t="s">
         <v>2053</v>
       </c>
@@ -51354,7 +51366,7 @@
 due to the unique government reform.</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51418,7 +51430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51491,7 +51503,7 @@
 Sacraments” (*+2.5%*)</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51561,7 +51573,7 @@
 declines the PU is also a viable strategy.</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="45" t="s">
         <v>1933</v>
       </c>
@@ -51626,7 +51638,7 @@
 suffice.</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39" t="s">
         <v>1934</v>
       </c>
@@ -51696,7 +51708,7 @@
 new capital.</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45" t="s">
         <v>1935</v>
       </c>
@@ -51773,7 +51785,7 @@
 two are owned by Mali and one by Kong.</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51839,7 +51851,7 @@
 European majors for fighting the Turks.</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51902,7 +51914,7 @@
 religion by rebels.</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45" t="s">
         <v>1937</v>
       </c>
@@ -51929,7 +51941,7 @@
       </c>
       <c r="H62" s="63" t="str">
         <f>IF(VLOOKUP($G62,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G62,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I62" s="47" t="str">
         <f>VLOOKUP($G62,List!$A:$U,2,FALSE)</f>
@@ -51975,7 +51987,7 @@
 Africa. The provinces do not need to be cored.</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="39" t="s">
         <v>1938</v>
       </c>
@@ -52040,7 +52052,7 @@
 Valencia.</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="45" t="s">
         <v>1939</v>
       </c>
@@ -52106,7 +52118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="39" t="s">
         <v>1940</v>
       </c>
@@ -52168,7 +52180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="39" t="s">
         <v>2052</v>
       </c>
@@ -52248,7 +52260,7 @@
 gaining Azov early in the game.</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45" t="s">
         <v>1941</v>
       </c>
@@ -52315,7 +52327,7 @@
 provinces with the correct trade goods.</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="39" t="s">
         <v>1942</v>
       </c>
@@ -52377,7 +52389,7 @@
         <v>Easiest as Malacca or Pasai.</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45" t="s">
         <v>1943</v>
       </c>
@@ -52438,7 +52450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="39" t="s">
         <v>1944</v>
       </c>
@@ -52502,7 +52514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45" t="s">
         <v>1945</v>
       </c>
@@ -52572,7 +52584,7 @@
 a quarter of HRE provinces under Anglican control.</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="39" t="s">
         <v>1946</v>
       </c>
@@ -52638,7 +52650,7 @@
 vassals in your home islands to achieve this.</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52701,7 +52713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52768,7 +52780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52837,7 +52849,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="39" t="s">
         <v>1948</v>
       </c>
@@ -52918,7 +52930,7 @@
 coast, and finally down to Werder.</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="45" t="s">
         <v>1949</v>
       </c>
@@ -52982,7 +52994,7 @@
 annexed all of Livonian Order and Riga</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="39" t="s">
         <v>1950</v>
       </c>
@@ -53056,7 +53068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="45" t="s">
         <v>1951</v>
       </c>
@@ -53123,7 +53135,7 @@
 necessary.</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="39" t="s">
         <v>1952</v>
       </c>
@@ -53186,7 +53198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="45" t="s">
         <v>1953</v>
       </c>
@@ -53248,7 +53260,7 @@
         <v>Caffa is in the Pontic Steppe region, initially owned by Genoa.</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="39" t="s">
         <v>1954</v>
       </c>
@@ -53320,7 +53332,7 @@
 a lot of troops and declaring war on them once they form Prussia.</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="45" t="s">
         <v>1955</v>
       </c>
@@ -53382,7 +53394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="39" t="s">
         <v>1956</v>
       </c>
@@ -53444,7 +53456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="45" t="s">
         <v>1957</v>
       </c>
@@ -53509,7 +53521,7 @@
 this.</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="39" t="s">
         <v>1958</v>
       </c>
@@ -53573,7 +53585,7 @@
 southeast Asia</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="45" t="s">
         <v>1959</v>
       </c>
@@ -53636,7 +53648,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="39" t="s">
         <v>1960</v>
       </c>
@@ -53698,7 +53710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="45" t="s">
         <v>1961</v>
       </c>
@@ -53774,7 +53786,7 @@
 ideas are all helpful.</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="39" t="s">
         <v>1962</v>
       </c>
@@ -53838,7 +53850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="45" t="s">
         <v>1963</v>
       </c>
@@ -53901,7 +53913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="39" t="s">
         <v>1964</v>
       </c>
@@ -53966,7 +53978,7 @@
 - Making the leading tobacco producer a tributary would count.</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="45" t="s">
         <v>1965</v>
       </c>
@@ -54039,7 +54051,7 @@
 (requires having the Emperor DLC activated and the Domination not active).</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="39" t="s">
         <v>1966</v>
       </c>
@@ -54110,7 +54122,7 @@
 province, this will convert you to Coptic and grant the achievement.</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="45" t="s">
         <v>1967</v>
       </c>
@@ -54174,7 +54186,7 @@
         <v>Chinaware appears in China, Japan, Korea and the East Indies.</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54240,7 +54252,7 @@
 and/or Bohemia to defeat Hungary for the important provinces.</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54306,7 +54318,7 @@
 then sail up next to Stockholm and move your cavalry onto it.</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="45" t="s">
         <v>1969</v>
       </c>
@@ -54369,7 +54381,7 @@
         <v>Lucknow is in northern India, initially owned by Jaunpur.</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="39" t="s">
         <v>1970</v>
       </c>
@@ -54437,7 +54449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="45" t="s">
         <v>2054</v>
       </c>
@@ -54534,7 +54546,7 @@
 a horde in this way is only possible as a migratory tribe.</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="39" t="s">
         <v>1971</v>
       </c>
@@ -54601,7 +54613,7 @@
 due to the event which spawns Kalmyk.</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54668,7 +54680,7 @@
 within a few days.</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54734,7 +54746,7 @@
 nations that can be released from Qara Qoyunlu's provinces.</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="39" t="s">
         <v>1973</v>
       </c>
@@ -54797,7 +54809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="45" t="s">
         <v>1974</v>
       </c>
@@ -54863,7 +54875,7 @@
 they produce wool.</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="39" t="s">
         <v>1975</v>
       </c>
@@ -54926,7 +54938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="45" t="s">
         <v>1976</v>
       </c>
@@ -54990,7 +55002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="39" t="s">
         <v>1977</v>
       </c>
@@ -55058,7 +55070,7 @@
 an army when Mutapa has started integrating you.</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="45" t="s">
         <v>1978</v>
       </c>
@@ -55119,7 +55131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="39" t="s">
         <v>2029</v>
       </c>
@@ -55181,7 +55193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="45" t="s">
         <v>1979</v>
       </c>
@@ -55244,7 +55256,7 @@
         <v>Has to be Protestant and lead the League.</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="39" t="s">
         <v>1980</v>
       </c>
@@ -55309,7 +55321,7 @@
 England until the time is right.</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="45" t="s">
         <v>1981</v>
       </c>
@@ -55379,7 +55391,7 @@
 then release and play as Lippe, earning you the achievement.</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55440,7 +55452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55505,7 +55517,7 @@
 Corfu will not count.</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="45" t="s">
         <v>1983</v>
       </c>
@@ -55580,7 +55592,7 @@
 which will increase your gold income, requiring less development.</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="39" t="s">
         <v>1984</v>
       </c>
@@ -55647,7 +55659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="45" t="s">
         <v>1985</v>
       </c>
@@ -55713,7 +55725,7 @@
 get the open outcome in the incident Spread of Christianity.</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="39" t="s">
         <v>1986</v>
       </c>
@@ -55776,7 +55788,7 @@
         <v>Possible starts are Dongola, Alodia, and Makuria.</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="45" t="s">
         <v>1987</v>
       </c>
@@ -55841,7 +55853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="39" t="s">
         <v>1988</v>
       </c>
@@ -55911,7 +55923,7 @@
 Flame Burning.</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="45" t="s">
         <v>1989</v>
       </c>
@@ -55990,7 +56002,7 @@
 Moravia, which can be done by Bohemia.</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="39" t="s">
         <v>1990</v>
       </c>
@@ -56058,7 +56070,7 @@
 your former overlord.</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="45" t="s">
         <v>1991</v>
       </c>
@@ -56128,7 +56140,7 @@
 ahead-of-time penalty in 1820.</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="39" t="s">
         <v>1992</v>
       </c>
@@ -56207,7 +56219,7 @@
 Simply annexing a vassal in the region won't fire the achievement.</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="45" t="s">
         <v>1993</v>
       </c>
@@ -56317,7 +56329,7 @@
 is needed to complete it.</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="39" t="s">
         <v>1994</v>
       </c>
@@ -56380,7 +56392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="45" t="s">
         <v>1995</v>
       </c>
@@ -56451,7 +56463,7 @@
 to Germany.</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="39" t="s">
         <v>1996</v>
       </c>
@@ -56524,7 +56536,7 @@
 nation doesn't work, because it counts as playing as a released vassal.</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56598,7 +56610,7 @@
 more easily if necessary.</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56661,7 +56673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56732,7 +56744,7 @@
 use their bonuses and permanent claim on the mongol region.</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="39" t="s">
         <v>1998</v>
       </c>
@@ -56801,7 +56813,7 @@
 trust with allies grows slowly over time.</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="45" t="s">
         <v>1999</v>
       </c>
@@ -56874,7 +56886,7 @@
 especially for Trier which is not the primary tag of its culture.</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="39" t="s">
         <v>2000</v>
       </c>
@@ -56943,7 +56955,7 @@
 which stacks with "Hydraulic Rights"</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="45" t="s">
         <v>2001</v>
       </c>
@@ -57025,7 +57037,7 @@
 capital provinces.</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57089,7 +57101,7 @@
 still get the achievement without having to get Norway back on the map.</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57183,7 +57195,7 @@
 tick, you had the highest income.</v>
       </c>
     </row>
-    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57259,7 +57271,7 @@
 make conversions faster, especially against Islamic provinces.</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57345,7 +57357,7 @@
 - Tripura</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="39" t="s">
         <v>2012</v>
       </c>
@@ -57441,7 +57453,7 @@
 support from a rival.</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="45" t="s">
         <v>2007</v>
       </c>
@@ -57509,7 +57521,7 @@
 galley navy and block the straits.</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57573,7 +57585,7 @@
 Ottoman Government and Sultanate of Rûm</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57635,7 +57647,7 @@
         <v>Make sure to attack Muscovy ASAP to remove a future potential threat.</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57700,7 +57712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57771,7 +57783,7 @@
 provinces needed.</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57840,7 +57852,7 @@
 Coffee achievement. Do not form Arabia</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="45" t="s">
         <v>2009</v>
       </c>
@@ -57916,7 +57928,7 @@
 Sussex, and Kent in your first war and you should be off to a great start.</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="45" t="s">
         <v>2009</v>
       </c>
@@ -57981,7 +57993,7 @@
 Dulyn(373), Lleuddiniawn(248), Rhufain(118), Paris(183) and Llundain(236)</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58046,7 +58058,7 @@
 easily after unifying the HRE.</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58115,7 +58127,7 @@
 India.</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58191,7 +58203,7 @@
 with Jihad.</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
@@ -58320,19 +58332,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06764ED-1FD3-4368-8455-971DCC0423D8}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
-    <col min="7" max="7" width="28.109375" customWidth="1"/>
-    <col min="8" max="8" width="60.109375" customWidth="1"/>
-    <col min="9" max="9" width="43.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" customWidth="1"/>
+    <col min="8" max="8" width="60.140625" customWidth="1"/>
+    <col min="9" max="9" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -58361,7 +58373,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>531</v>
       </c>
@@ -58420,7 +58432,7 @@
       </c>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>251</v>
       </c>
@@ -58468,7 +58480,7 @@
       </c>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -58506,7 +58518,7 @@
       </c>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>482</v>
       </c>
@@ -58554,7 +58566,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="75" t="s">
         <v>1702</v>
       </c>
@@ -58568,7 +58580,7 @@
       <c r="I6" s="75"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>435</v>
       </c>
@@ -58607,7 +58619,7 @@
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="76" t="s">
         <v>1703</v>
       </c>
@@ -58621,7 +58633,7 @@
       <c r="I8" s="76"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>463</v>
       </c>
@@ -58658,7 +58670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="77" t="s">
         <v>1704</v>
       </c>
@@ -58672,7 +58684,7 @@
       <c r="I10" s="77"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>491</v>
       </c>
@@ -58715,7 +58727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="75" t="s">
         <v>1705</v>
       </c>
@@ -58729,7 +58741,7 @@
       <c r="I12" s="75"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>591</v>
       </c>
@@ -58774,7 +58786,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="78" t="s">
         <v>1706</v>
       </c>
@@ -58788,7 +58800,7 @@
       <c r="I14" s="78"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" ht="224.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>588</v>
       </c>
@@ -58837,30 +58849,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C19" s="2"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C22" s="2"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
     </row>
   </sheetData>
@@ -59077,19 +59089,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5325864E-31AE-48F9-AD21-970E551229EF}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="28.109375" customWidth="1"/>
-    <col min="7" max="7" width="60.109375" customWidth="1"/>
-    <col min="8" max="8" width="63.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="60.140625" customWidth="1"/>
+    <col min="8" max="8" width="63.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="C1" s="30" t="s">
         <v>1680</v>
       </c>
@@ -59102,7 +59114,7 @@
         <v>214.75</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>634</v>
       </c>
@@ -59128,7 +59140,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>299</v>
       </c>
@@ -59172,7 +59184,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="93" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>439</v>
       </c>
@@ -59215,7 +59227,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>601</v>
       </c>
@@ -59328,9 +59340,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1BBC31-09BA-43B6-86CD-7C2F847C46AC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>434</v>
       </c>
@@ -59341,7 +59353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>242</v>
       </c>
@@ -59352,7 +59364,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
@@ -59363,7 +59375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -59374,7 +59386,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>573</v>
       </c>
@@ -59385,7 +59397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>626</v>
       </c>
@@ -59396,7 +59408,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>1669</v>
       </c>
@@ -59429,30 +59441,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFB87DA-EA4E-493C-8327-11283D76496B}">
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="55.5546875" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="8" max="9" width="9.109375" style="1"/>
-    <col min="10" max="10" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="1"/>
-    <col min="12" max="12" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.44140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="20" width="9.109375" style="1"/>
-    <col min="21" max="21" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.5546875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="55.5703125" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="8" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="20" width="9.140625" style="1"/>
+    <col min="21" max="21" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.5703125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
         <v>1672</v>
       </c>
@@ -59466,10 +59478,10 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
       <c r="I2" s="29">
         <f>K2/J2</f>
-        <v>0.59265110466075721</v>
+        <v>0.60065844111226274</v>
       </c>
       <c r="J2" s="28">
         <f>SUM(List!E:E)</f>
@@ -59477,20 +59489,20 @@
       </c>
       <c r="K2" s="27">
         <f>SUMIFS(List!$E:$E,List!$O:$O,"Y")</f>
-        <v>21908</v>
+        <v>22203.999999999996</v>
       </c>
       <c r="L2" s="1">
         <f>COUNTIFS(List!O:O,"Y")</f>
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="J3" s="67"/>
       <c r="L3" s="1">
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="79" t="s">
         <v>1638</v>
       </c>
@@ -59524,7 +59536,7 @@
       <c r="AA4" s="82"/>
       <c r="AB4" s="21"/>
     </row>
-    <row r="5" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>1640</v>
       </c>
@@ -59604,7 +59616,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -59723,7 +59735,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -59836,7 +59848,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -59979,7 +59991,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -60092,7 +60104,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -60206,7 +60218,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -60329,7 +60341,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -60435,7 +60447,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -60560,7 +60572,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -60667,7 +60679,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -60778,7 +60790,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="80" t="s">
         <v>1652</v>
       </c>
@@ -60812,7 +60824,7 @@
       <c r="AA17" s="84"/>
       <c r="AB17" s="22"/>
     </row>
-    <row r="18" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>1640</v>
       </c>
@@ -60892,7 +60904,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -61008,7 +61020,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>2</v>
       </c>
@@ -61126,7 +61138,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -61242,7 +61254,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>4</v>
       </c>
@@ -61361,7 +61373,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>5</v>
       </c>
@@ -61466,7 +61478,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>6</v>
       </c>
@@ -61590,16 +61602,15 @@
       </c>
       <c r="X24" s="1" t="str" cm="1">
         <f t="array" ref="X24">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(7:7)),List!N:N,0))</f>
-        <v>Inner Turmoil</v>
+        <v>Empire of Mann</v>
       </c>
       <c r="Y24" s="15" t="str">
         <f>VLOOKUP($X24,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as The Isles, own 20 provinces by 1500, none of which are on 
-Islands.</v>
+        <v>As Mann, conquer all Islands in the world.</v>
       </c>
       <c r="Z24" s="16">
         <f>VLOOKUP($X24,List!$A$1:$U$374,3,FALSE)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="AA24" s="17" t="str">
         <f>VLOOKUP($X24,List!$A$1:$U$374,4,FALSE)</f>
@@ -61610,7 +61621,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>7</v>
       </c>
@@ -61687,17 +61698,16 @@
       </c>
       <c r="O25" s="1" t="str" cm="1">
         <f t="array" ref="O25">INDEX(List!A:A,MATCH(LARGE(List!M:M,ROW(8:8)),List!M:M,0))</f>
-        <v>Around the World in 80 Years</v>
+        <v>Inner Turmoil</v>
       </c>
       <c r="P25" s="2" t="str">
         <f>VLOOKUP($O25,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as a Custom Nation of up to 400 points in the British Region, own 
-New York, San Francisco, Suez, Bombay, Calcutta, Hong Kong and Yokohama by 
-1524.11.11.</v>
+        <v>Starting as The Isles, own 20 provinces by 1500, none of which are on 
+Islands.</v>
       </c>
       <c r="Q25" s="3">
         <f>VLOOKUP($O25,List!$A$1:$U$374,3,FALSE)</f>
-        <v>6.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="R25" s="6" t="str">
         <f>VLOOKUP($O25,List!$A$1:$U$374,4,FALSE)</f>
@@ -61713,22 +61723,23 @@
       </c>
       <c r="U25" s="1" t="str">
         <f>IF(VLOOKUP($O25,List!$A$1:$U$374,16,FALSE)="","",VLOOKUP($O25,List!$A$1:$U$374,16,FALSE))</f>
-        <v>Custom</v>
+        <v>The Isles</v>
       </c>
       <c r="W25" s="1">
         <v>7</v>
       </c>
       <c r="X25" s="1" t="str" cm="1">
         <f t="array" ref="X25">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(8:8)),List!N:N,0))</f>
-        <v>Empire of Mann</v>
+        <v>Great Perm</v>
       </c>
       <c r="Y25" s="2" t="str">
         <f>VLOOKUP($X25,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Mann, conquer all Islands in the world.</v>
+        <v>As Perm, own or have a subject own the Russian, Siberian, Scandinavian, 
+Canadian, Hudson Bay and Cascadian Regions.</v>
       </c>
       <c r="Z25" s="3">
         <f>VLOOKUP($X25,List!$A$1:$U$374,3,FALSE)</f>
-        <v>6.0000000000000001E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="AA25" s="6" t="str">
         <f>VLOOKUP($X25,List!$A$1:$U$374,4,FALSE)</f>
@@ -61739,7 +61750,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>8</v>
       </c>
@@ -61803,16 +61814,17 @@
       </c>
       <c r="O26" s="14" t="str" cm="1">
         <f t="array" ref="O26">INDEX(List!A:A,MATCH(LARGE(List!M:M,ROW(9:9)),List!M:M,0))</f>
-        <v>Basque in Glory</v>
+        <v>Around the World in 80 Years</v>
       </c>
       <c r="P26" s="15" t="str">
         <f>VLOOKUP($O26,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as Navarra, ensure that most of Iberia is Basque culture before 
-the Age of Absolutism.</v>
+        <v>Starting as a Custom Nation of up to 400 points in the British Region, own 
+New York, San Francisco, Suez, Bombay, Calcutta, Hong Kong and Yokohama by 
+1524.11.11.</v>
       </c>
       <c r="Q26" s="16">
         <f>VLOOKUP($O26,List!$A$1:$U$374,3,FALSE)</f>
-        <v>7.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="R26" s="17" t="str">
         <f>VLOOKUP($O26,List!$A$1:$U$374,4,FALSE)</f>
@@ -61828,19 +61840,18 @@
       </c>
       <c r="U26" s="14" t="str">
         <f>IF(VLOOKUP($O26,List!$A$1:$U$374,16,FALSE)="","",VLOOKUP($O26,List!$A$1:$U$374,16,FALSE))</f>
-        <v>Navarra</v>
+        <v>Custom</v>
       </c>
       <c r="W26" s="14">
         <v>8</v>
       </c>
       <c r="X26" s="1" t="str" cm="1">
         <f t="array" ref="X26">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(9:9)),List!N:N,0))</f>
-        <v>Great Perm</v>
+        <v>Spanish Fly</v>
       </c>
       <c r="Y26" s="15" t="str">
         <f>VLOOKUP($X26,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Perm, own or have a subject own the Russian, Siberian, Scandinavian, 
-Canadian, Hudson Bay and Cascadian Regions.</v>
+        <v>Starting as Offaly, secure a Personal Union over an Iberian nation.</v>
       </c>
       <c r="Z26" s="16">
         <f>VLOOKUP($X26,List!$A$1:$U$374,3,FALSE)</f>
@@ -61855,7 +61866,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>9</v>
       </c>
@@ -61911,11 +61922,12 @@
       </c>
       <c r="O27" s="1" t="str" cm="1">
         <f t="array" ref="O27">INDEX(List!A:A,MATCH(LARGE(List!M:M,ROW(10:10)),List!M:M,0))</f>
-        <v>Where the heart is</v>
+        <v>Basque in Glory</v>
       </c>
       <c r="P27" s="2" t="str">
         <f>VLOOKUP($O27,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Dahomey, force all non-Fetishist nations out of Niger and Sahel by 1500.</v>
+        <v>Starting as Navarra, ensure that most of Iberia is Basque culture before 
+the Age of Absolutism.</v>
       </c>
       <c r="Q27" s="3">
         <f>VLOOKUP($O27,List!$A$1:$U$374,3,FALSE)</f>
@@ -61935,22 +61947,22 @@
       </c>
       <c r="U27" s="1" t="str">
         <f>IF(VLOOKUP($O27,List!$A$1:$U$374,16,FALSE)="","",VLOOKUP($O27,List!$A$1:$U$374,16,FALSE))</f>
-        <v>Dahomey</v>
+        <v>Navarra</v>
       </c>
       <c r="W27" s="1">
         <v>9</v>
       </c>
       <c r="X27" s="1" t="str" cm="1">
         <f t="array" ref="X27">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(10:10)),List!N:N,0))</f>
-        <v>Spanish Fly</v>
+        <v>Raja of the Rajput Reich</v>
       </c>
       <c r="Y27" s="2" t="str">
         <f>VLOOKUP($X27,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as Offaly, secure a Personal Union over an Iberian nation.</v>
+        <v>Conquer all of Germany as Nagaur.</v>
       </c>
       <c r="Z27" s="3">
         <f>VLOOKUP($X27,List!$A$1:$U$374,3,FALSE)</f>
-        <v>7.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AA27" s="6" t="str">
         <f>VLOOKUP($X27,List!$A$1:$U$374,4,FALSE)</f>
@@ -61961,7 +61973,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>10</v>
       </c>
@@ -62022,15 +62034,15 @@
       </c>
       <c r="O28" s="14" t="str" cm="1">
         <f t="array" ref="O28">INDEX(List!A:A,MATCH(LARGE(List!M:M,ROW(11:11)),List!M:M,0))</f>
-        <v>An Unlikely Candidate</v>
+        <v>Where the heart is</v>
       </c>
       <c r="P28" s="15" t="str">
         <f>VLOOKUP($O28,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as Mzab, Touggourt or Djerid, reform Al-Andalus.</v>
+        <v>As Dahomey, force all non-Fetishist nations out of Niger and Sahel by 1500.</v>
       </c>
       <c r="Q28" s="16">
         <f>VLOOKUP($O28,List!$A$1:$U$374,3,FALSE)</f>
-        <v>8.0000000000000002E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R28" s="17" t="str">
         <f>VLOOKUP($O28,List!$A$1:$U$374,4,FALSE)</f>
@@ -62046,18 +62058,18 @@
       </c>
       <c r="U28" s="14" t="str">
         <f>IF(VLOOKUP($O28,List!$A$1:$U$374,16,FALSE)="","",VLOOKUP($O28,List!$A$1:$U$374,16,FALSE))</f>
-        <v>Mzab</v>
+        <v>Dahomey</v>
       </c>
       <c r="W28" s="14">
         <v>10</v>
       </c>
       <c r="X28" s="1" t="str" cm="1">
         <f t="array" ref="X28">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(11:11)),List!N:N,0))</f>
-        <v>Raja of the Rajput Reich</v>
+        <v>The Animal Kingdom</v>
       </c>
       <c r="Y28" s="15" t="str">
         <f>VLOOKUP($X28,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Conquer all of Germany as Nagaur.</v>
+        <v>As Manipur, unite the Bengal region and convert it to Animism.</v>
       </c>
       <c r="Z28" s="16">
         <f>VLOOKUP($X28,List!$A$1:$U$374,3,FALSE)</f>
@@ -62563,21 +62575,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70671CC-FD1D-40C3-A5F7-A316733B30A0}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="9.109375" style="1"/>
-    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.42578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="11" max="11" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="86" t="s">
         <v>1658</v>
       </c>
@@ -62597,7 +62609,7 @@
       <c r="N1" s="88"/>
       <c r="O1" s="88"/>
     </row>
-    <row r="2" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>1640</v>
       </c>
@@ -62641,7 +62653,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -62699,7 +62711,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>2</v>
       </c>
@@ -62755,7 +62767,7 @@
         <v>13.15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -62813,7 +62825,7 @@
         <v>66.25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>4</v>
       </c>
@@ -62869,7 +62881,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -62925,7 +62937,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>6</v>
       </c>
@@ -62982,7 +62994,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -63038,7 +63050,7 @@
         <v>67.25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>8</v>
       </c>
@@ -63095,7 +63107,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -63152,7 +63164,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>10</v>
       </c>
@@ -63208,7 +63220,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="87" t="s">
         <v>1659</v>
       </c>
@@ -63228,7 +63240,7 @@
       <c r="N14" s="89"/>
       <c r="O14" s="89"/>
     </row>
-    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63272,7 +63284,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>1</v>
       </c>
@@ -63329,7 +63341,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>2</v>
       </c>
@@ -63385,7 +63397,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>3</v>
       </c>
@@ -63441,7 +63453,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>4</v>
       </c>
@@ -63498,7 +63510,7 @@
         <v>143.5</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>5</v>
       </c>
@@ -63554,7 +63566,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>6</v>
       </c>
@@ -63611,7 +63623,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>7</v>
       </c>
@@ -63668,7 +63680,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20">
         <v>8</v>
       </c>
@@ -63724,7 +63736,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9</v>
       </c>
@@ -63780,7 +63792,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20">
         <v>10</v>
       </c>
@@ -63837,7 +63849,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="85" t="s">
         <v>1673</v>
       </c>
@@ -63849,7 +63861,7 @@
       <c r="G27" s="85"/>
       <c r="H27" s="85"/>
     </row>
-    <row r="28" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63875,7 +63887,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>1</v>
       </c>
@@ -63908,7 +63920,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="20">
         <v>2</v>
       </c>
@@ -63941,7 +63953,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>3</v>
       </c>
@@ -63974,7 +63986,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>4</v>
       </c>
@@ -64007,7 +64019,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>5</v>
       </c>
@@ -64041,7 +64053,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>6</v>
       </c>
@@ -64074,7 +64086,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <v>7</v>
       </c>
@@ -64107,7 +64119,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>8</v>
       </c>
@@ -64141,7 +64153,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>9</v>
       </c>
@@ -64175,7 +64187,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>10</v>
       </c>

--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D024875-7CC4-40D1-BDB1-50CCDFFBEDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BB83F2-FA0E-4154-B38E-F4C55DE77D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="17520" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3849" uniqueCount="2055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3857" uniqueCount="2056">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -8535,6 +8535,9 @@
   </si>
   <si>
     <t>194</t>
+  </si>
+  <si>
+    <t>Imerina</t>
   </si>
 </sst>
 </file>
@@ -13347,7 +13350,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y374"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13447,7 +13449,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>568</v>
       </c>
@@ -13535,7 +13537,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>564</v>
       </c>
@@ -13625,7 +13627,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>621</v>
       </c>
@@ -13708,7 +13710,7 @@
         <v>Legacy of Saint George</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>619</v>
       </c>
@@ -13798,7 +13800,7 @@
         <v>From Frankfurt to the Andes</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>239</v>
       </c>
@@ -13883,7 +13885,7 @@
         <v>Timurizz</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>561</v>
       </c>
@@ -13973,7 +13975,7 @@
         <v>Ultimate Military</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>531</v>
       </c>
@@ -14061,7 +14063,7 @@
         <v>Triple the Rome</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>566</v>
       </c>
@@ -14144,7 +14146,7 @@
         <v>The Zoro-Austrians</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>522</v>
       </c>
@@ -14229,7 +14231,7 @@
         <v>The Freest Man in the World</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>569</v>
       </c>
@@ -14312,7 +14314,7 @@
         <v>Baborg</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>456</v>
       </c>
@@ -14397,7 +14399,7 @@
         <v>Australia-Hungary</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>633</v>
       </c>
@@ -14480,7 +14482,7 @@
         <v>Mehmet's Ambition</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>432</v>
       </c>
@@ -14570,7 +14572,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>426</v>
       </c>
@@ -14658,7 +14660,7 @@
         <v>It's all coming together</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>291</v>
       </c>
@@ -14748,7 +14750,7 @@
         <v>Hanukkah Mutapa</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>622</v>
       </c>
@@ -14836,7 +14838,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>599</v>
       </c>
@@ -14926,7 +14928,7 @@
         <v>Quizquiz Pro Quo</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>620</v>
       </c>
@@ -15016,7 +15018,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>585</v>
       </c>
@@ -15106,7 +15108,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>618</v>
       </c>
@@ -15196,7 +15198,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -15286,7 +15288,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -15374,7 +15376,7 @@
         <v>Breadbasket of the World</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>567</v>
       </c>
@@ -15464,7 +15466,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>433</v>
       </c>
@@ -15554,7 +15556,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>496</v>
       </c>
@@ -15637,7 +15639,7 @@
         <v>One nation to rule them all</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>553</v>
       </c>
@@ -15722,7 +15724,7 @@
         <v>New, New Deli</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>483</v>
       </c>
@@ -15812,7 +15814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>440</v>
       </c>
@@ -15902,7 +15904,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>451</v>
       </c>
@@ -15985,7 +15987,7 @@
         <v>Almost Prussian Blue</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>383</v>
       </c>
@@ -16018,27 +16020,32 @@
         <f t="shared" si="2"/>
         <v>4.3045999999999996E-3</v>
       </c>
-      <c r="J31" s="10" t="str">
+      <c r="J31" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K31" s="10">
+        <v>4.3045999999999996E-3</v>
+      </c>
+      <c r="K31" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>4.3045999999999996E-3</v>
+        <v/>
       </c>
       <c r="L31" s="9">
         <f t="shared" si="5"/>
         <v>2.9956953999999998</v>
       </c>
-      <c r="M31" s="9" t="str">
+      <c r="M31" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N31" s="9">
+        <v>2.9956953999999998</v>
+      </c>
+      <c r="N31" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>2.9956953999999998</v>
-      </c>
-      <c r="O31" s="4"/>
+        <v/>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>2055</v>
+      </c>
       <c r="Q31" s="7" t="s">
         <v>1267</v>
       </c>
@@ -16053,9 +16060,9 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="V31">
+      <c r="V31" t="str">
         <f t="shared" si="9"/>
-        <v>4.3045999999999996E-3</v>
+        <v/>
       </c>
       <c r="W31" t="str">
         <f t="shared" si="10"/>
@@ -16070,7 +16077,7 @@
         <v>Where are the penguins?</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>430</v>
       </c>
@@ -16158,7 +16165,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>413</v>
       </c>
@@ -16241,7 +16248,7 @@
         <v>Stardust Crusaders</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>288</v>
       </c>
@@ -16331,7 +16338,7 @@
         <v>Golden Wind</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>387</v>
       </c>
@@ -16511,7 +16518,7 @@
         <v>Inner Turmoil</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>574</v>
       </c>
@@ -16596,7 +16603,7 @@
         <v>I don't like sand</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>200</v>
       </c>
@@ -16679,7 +16686,7 @@
         <v>To the Bone</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -16764,7 +16771,7 @@
         <v>Surfing USA</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>557</v>
       </c>
@@ -16849,7 +16856,7 @@
         <v>The Pheasant Strut</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>624</v>
       </c>
@@ -16934,7 +16941,7 @@
         <v>Eat your Greens</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>390</v>
       </c>
@@ -17024,7 +17031,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>338</v>
       </c>
@@ -17114,7 +17121,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>389</v>
       </c>
@@ -17202,7 +17209,7 @@
         <v>No Country for Old Tercios</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>431</v>
       </c>
@@ -17290,7 +17297,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>428</v>
       </c>
@@ -17373,7 +17380,7 @@
         <v>Doge Coins</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>208</v>
       </c>
@@ -17460,7 +17467,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>528</v>
       </c>
@@ -17543,7 +17550,7 @@
         <v>Why is the Rûm gone!?</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>555</v>
       </c>
@@ -17628,7 +17635,7 @@
         <v>The Fezzan Corridors</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>513</v>
       </c>
@@ -17713,7 +17720,7 @@
         <v>Stiff Upper Lippe</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>511</v>
       </c>
@@ -17798,7 +17805,7 @@
         <v>Stern des Südens</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>503</v>
       </c>
@@ -17883,7 +17890,7 @@
         <v>Pick Your Poison</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>499</v>
       </c>
@@ -17966,7 +17973,7 @@
         <v>Pandya Empire</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>491</v>
       </c>
@@ -18051,7 +18058,7 @@
         <v>Mass Production</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>468</v>
       </c>
@@ -18141,7 +18148,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>463</v>
       </c>
@@ -18224,7 +18231,7 @@
         <v>Dovmont's Own</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>348</v>
       </c>
@@ -18314,7 +18321,7 @@
         <v>That's No Mon</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>412</v>
       </c>
@@ -18347,27 +18354,32 @@
         <f t="shared" si="2"/>
         <v>6.3068000000000004E-3</v>
       </c>
-      <c r="J58" s="10" t="str">
+      <c r="J58" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K58" s="10">
+        <v>6.3068000000000004E-3</v>
+      </c>
+      <c r="K58" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>6.3068000000000004E-3</v>
+        <v/>
       </c>
       <c r="L58" s="9">
         <f t="shared" si="5"/>
         <v>2.9936932000000001</v>
       </c>
-      <c r="M58" s="9" t="str">
+      <c r="M58" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N58" s="9">
+        <v>2.9936932000000001</v>
+      </c>
+      <c r="N58" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>2.9936932000000001</v>
-      </c>
-      <c r="O58" s="4"/>
+        <v/>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>2020</v>
+      </c>
       <c r="Q58" s="7"/>
       <c r="R58" s="7" t="s">
         <v>1417</v>
@@ -18380,9 +18392,9 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="V58">
+      <c r="V58" t="str">
         <f t="shared" si="9"/>
-        <v>6.3068000000000004E-3</v>
+        <v/>
       </c>
       <c r="W58" t="str">
         <f t="shared" si="10"/>
@@ -18397,7 +18409,7 @@
         <v>Sun Invasion</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>253</v>
       </c>
@@ -18485,7 +18497,7 @@
         <v>Shemot is Not</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -18575,7 +18587,7 @@
         <v>Mansa Musa</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>424</v>
       </c>
@@ -18661,7 +18673,7 @@
         <v>King of Kings</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>265</v>
       </c>
@@ -18749,7 +18761,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
@@ -18834,7 +18846,7 @@
         <v>Imposter Syndrome</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>586</v>
       </c>
@@ -18917,7 +18929,7 @@
         <v>Empire of Mann</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>583</v>
       </c>
@@ -19009,7 +19021,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>530</v>
       </c>
@@ -19094,7 +19106,7 @@
         <v>With a little help..</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>525</v>
       </c>
@@ -19179,7 +19191,7 @@
         <v>Turkish Delight</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>523</v>
       </c>
@@ -19264,7 +19276,7 @@
         <v>Tiger of Mysore</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>520</v>
       </c>
@@ -19347,7 +19359,7 @@
         <v>The 52 Garhs</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>515</v>
       </c>
@@ -19437,7 +19449,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>506</v>
       </c>
@@ -19522,7 +19534,7 @@
         <v>Protect the Secret</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>543</v>
       </c>
@@ -19605,7 +19617,7 @@
         <v>Foremost Servitor of Jagannath</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>437</v>
       </c>
@@ -19688,7 +19700,7 @@
         <v>Core-fu</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>461</v>
       </c>
@@ -19773,7 +19785,7 @@
         <v>Bunte Kuh</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>535</v>
       </c>
@@ -19856,7 +19868,7 @@
         <v>Avar Khaganate</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>355</v>
       </c>
@@ -19946,7 +19958,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>309</v>
       </c>
@@ -20031,7 +20043,7 @@
         <v>Kuban Cigars</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>283</v>
       </c>
@@ -20116,7 +20128,7 @@
         <v>Ganges Khan</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>386</v>
       </c>
@@ -20204,7 +20216,7 @@
         <v>Brentry!</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>397</v>
       </c>
@@ -20292,7 +20304,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>103</v>
       </c>
@@ -20377,7 +20389,7 @@
         <v>Truly Good Maaaaa-tch</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>614</v>
       </c>
@@ -20467,7 +20479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>608</v>
       </c>
@@ -20552,7 +20564,7 @@
         <v>Spanish Fly</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>591</v>
       </c>
@@ -20635,7 +20647,7 @@
         <v>Great Perm</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>584</v>
       </c>
@@ -20723,7 +20735,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>139</v>
       </c>
@@ -20808,7 +20820,7 @@
         <v>Forgive me, for I have Sindh</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>509</v>
       </c>
@@ -20898,7 +20910,7 @@
         <v>Spaghetti Western</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>501</v>
       </c>
@@ -20979,7 +20991,7 @@
         <v>Philippine Tiger</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>551</v>
       </c>
@@ -21067,7 +21079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>549</v>
       </c>
@@ -21152,7 +21164,7 @@
         <v>Meissner Porcelain</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>443</v>
       </c>
@@ -21237,7 +21249,7 @@
         <v>Kushite Restoration</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>477</v>
       </c>
@@ -21325,7 +21337,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>475</v>
       </c>
@@ -21410,7 +21422,7 @@
         <v>Holy Horder</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>541</v>
       </c>
@@ -21500,7 +21512,7 @@
         <v>Cotton Kandy</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>435</v>
       </c>
@@ -21588,7 +21600,7 @@
         <v>Breaking the Yoke</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>380</v>
       </c>
@@ -21673,7 +21685,7 @@
         <v>Victorian Three</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>337</v>
       </c>
@@ -21763,7 +21775,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>319</v>
       </c>
@@ -21853,7 +21865,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>297</v>
       </c>
@@ -21936,7 +21948,7 @@
         <v>Home and Away</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>277</v>
       </c>
@@ -21969,27 +21981,32 @@
         <f t="shared" si="14"/>
         <v>8.3110000000000007E-3</v>
       </c>
-      <c r="J100" s="10" t="str">
+      <c r="J100" s="10">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K100" s="10">
+        <v>8.3110000000000007E-3</v>
+      </c>
+      <c r="K100" s="10" t="str">
         <f t="shared" si="16"/>
-        <v>8.3110000000000007E-3</v>
+        <v/>
       </c>
       <c r="L100" s="9">
         <f t="shared" si="17"/>
         <v>2.991689</v>
       </c>
-      <c r="M100" s="9" t="str">
+      <c r="M100" s="9">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N100" s="9">
+        <v>2.991689</v>
+      </c>
+      <c r="N100" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>2.991689</v>
-      </c>
-      <c r="O100" s="4"/>
+        <v/>
+      </c>
+      <c r="O100" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P100" s="1" t="s">
+        <v>1900</v>
+      </c>
       <c r="Q100" s="7" t="s">
         <v>1088</v>
       </c>
@@ -22004,9 +22021,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="V100">
+      <c r="V100" t="str">
         <f t="shared" si="21"/>
-        <v>8.3110000000000007E-3</v>
+        <v/>
       </c>
       <c r="W100" t="str">
         <f t="shared" si="22"/>
@@ -22021,7 +22038,7 @@
         <v>Don’t be Cilli</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>248</v>
       </c>
@@ -22111,7 +22128,7 @@
         <v>Disciples of Enlightenment</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>613</v>
       </c>
@@ -22201,7 +22218,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>575</v>
       </c>
@@ -22286,7 +22303,7 @@
         <v>The Animal Kingdom</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>602</v>
       </c>
@@ -22371,7 +22388,7 @@
         <v>Raja of the Rajput Reich</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>597</v>
       </c>
@@ -22456,7 +22473,7 @@
         <v>Norwegian Wood</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>581</v>
       </c>
@@ -22546,7 +22563,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>577</v>
       </c>
@@ -22629,7 +22646,7 @@
         <v>Academical</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>186</v>
       </c>
@@ -22719,7 +22736,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>507</v>
       </c>
@@ -22809,7 +22826,7 @@
         <v>Sailor Mon</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>488</v>
       </c>
@@ -22894,7 +22911,7 @@
         <v>Lucky Lucca</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>547</v>
       </c>
@@ -22984,7 +23001,7 @@
         <v>Komnenoi Empire</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
@@ -23072,7 +23089,7 @@
         <v>Kinslayer</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>631</v>
       </c>
@@ -23157,7 +23174,7 @@
         <v>True Heir of Timur</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>629</v>
       </c>
@@ -23247,7 +23264,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>295</v>
       </c>
@@ -23332,7 +23349,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>404</v>
       </c>
@@ -23420,7 +23437,7 @@
         <v>For the Emperor!</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>571</v>
       </c>
@@ -23508,7 +23525,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>601</v>
       </c>
@@ -23593,7 +23610,7 @@
         <v>Rags and Riches</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>589</v>
       </c>
@@ -23678,7 +23695,7 @@
         <v>Gothic Invasion</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>170</v>
       </c>
@@ -23768,7 +23785,7 @@
         <v>On the Edge of Madness</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>215</v>
       </c>
@@ -23855,7 +23872,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>495</v>
       </c>
@@ -23943,7 +23960,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>420</v>
       </c>
@@ -24035,7 +24052,7 @@
         <v>Yarr Harr a Pirate's Life For Me</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>346</v>
       </c>
@@ -24123,7 +24140,7 @@
         <v>Tatarstan</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>334</v>
       </c>
@@ -24211,7 +24228,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -24298,7 +24315,7 @@
         <v>Rekindling the Flames</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>327</v>
       </c>
@@ -24381,7 +24398,7 @@
         <v>No Trail of Tears</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>423</v>
       </c>
@@ -24471,7 +24488,7 @@
         <v>First Come, First Serve</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>99</v>
       </c>
@@ -24558,7 +24575,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>611</v>
       </c>
@@ -24648,7 +24665,7 @@
         <v>The Buddhists Strike Back</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>595</v>
       </c>
@@ -24734,7 +24751,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>593</v>
       </c>
@@ -24824,7 +24841,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>588</v>
       </c>
@@ -24914,7 +24931,7 @@
         <v>Frozen Assets</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>579</v>
       </c>
@@ -25002,7 +25019,7 @@
         <v>Albania or Iberia</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>199</v>
       </c>
@@ -25087,7 +25104,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>235</v>
       </c>
@@ -25179,7 +25196,7 @@
         <v>Østindisk Kompagni Te</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>128</v>
       </c>
@@ -25264,7 +25281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>119</v>
       </c>
@@ -25352,7 +25369,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>527</v>
       </c>
@@ -25442,7 +25459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>466</v>
       </c>
@@ -25532,7 +25549,7 @@
         <v>Emperor of Hindustan</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>540</v>
       </c>
@@ -25617,7 +25634,7 @@
         <v>Choson One</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>458</v>
       </c>
@@ -25705,7 +25722,7 @@
         <v>Back to the Piast</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>258</v>
       </c>
@@ -25788,7 +25805,7 @@
         <v>Turn the Table</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>366</v>
       </c>
@@ -25878,7 +25895,7 @@
         <v>The Sudanese Expedition</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>610</v>
       </c>
@@ -25968,7 +25985,7 @@
         <v>Sunset Invasion</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>604</v>
       </c>
@@ -26058,7 +26075,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>126</v>
       </c>
@@ -26150,7 +26167,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>121</v>
       </c>
@@ -26240,7 +26257,7 @@
         <v>Brick by Brick</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>565</v>
       </c>
@@ -26330,7 +26347,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>516</v>
       </c>
@@ -26418,7 +26435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>445</v>
       </c>
@@ -26503,7 +26520,7 @@
         <v>Rise of the White Sheep</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>563</v>
       </c>
@@ -26591,7 +26608,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>444</v>
       </c>
@@ -26679,7 +26696,7 @@
         <v>Lessons of Hemmingstedt</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>484</v>
       </c>
@@ -26762,7 +26779,7 @@
         <v>Lazarus</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>479</v>
       </c>
@@ -26850,7 +26867,7 @@
         <v>Keep the Flame Burning</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -26938,7 +26955,7 @@
         <v>Auld Alliance Reversed</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>378</v>
       </c>
@@ -27028,7 +27045,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>362</v>
       </c>
@@ -27118,7 +27135,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>321</v>
       </c>
@@ -27206,7 +27223,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>289</v>
       </c>
@@ -27289,7 +27306,7 @@
         <v>Great Moravia</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>287</v>
       </c>
@@ -27374,7 +27391,7 @@
         <v>Golden Horn</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>83</v>
       </c>
@@ -27457,7 +27474,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>184</v>
       </c>
@@ -27542,7 +27559,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -27632,7 +27649,7 @@
         <v>Holy Trinity</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>471</v>
       </c>
@@ -27722,7 +27739,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>439</v>
       </c>
@@ -27814,7 +27831,7 @@
         <v>For Odin!</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>465</v>
       </c>
@@ -27904,7 +27921,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>533</v>
       </c>
@@ -27994,7 +28011,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>449</v>
       </c>
@@ -28079,7 +28096,7 @@
         <v>A Hero’s Welcome</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>627</v>
       </c>
@@ -28162,7 +28179,7 @@
         <v>One Faith</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>372</v>
       </c>
@@ -28245,7 +28262,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>418</v>
       </c>
@@ -28335,7 +28352,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>328</v>
       </c>
@@ -28418,7 +28435,7 @@
         <v>Parisian Pasha</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>317</v>
       </c>
@@ -28508,7 +28525,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>293</v>
       </c>
@@ -28591,7 +28608,7 @@
         <v>Hessian Mercenaries</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>267</v>
       </c>
@@ -28681,7 +28698,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>24</v>
       </c>
@@ -28768,7 +28785,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -28853,7 +28870,7 @@
         <v>Rozwi Empire</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
@@ -28943,7 +28960,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>154</v>
       </c>
@@ -29033,7 +29050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>556</v>
       </c>
@@ -29123,7 +29140,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>419</v>
       </c>
@@ -29215,7 +29232,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>350</v>
       </c>
@@ -29303,7 +29320,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>336</v>
       </c>
@@ -29386,7 +29403,7 @@
         <v>Sons of Carthage</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>243</v>
       </c>
@@ -29476,7 +29493,7 @@
         <v>Abu Bakr II’s Ambition</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>214</v>
       </c>
@@ -29566,7 +29583,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -29651,7 +29668,7 @@
         <v>The Uncommonwealth</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>361</v>
       </c>
@@ -29741,7 +29758,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>357</v>
       </c>
@@ -29831,7 +29848,7 @@
         <v>The Levant Turnabout</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>352</v>
       </c>
@@ -29919,7 +29936,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>254</v>
       </c>
@@ -30002,7 +30019,7 @@
         <v>Sweet Home Qaraqorum</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>405</v>
       </c>
@@ -30092,7 +30109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>299</v>
       </c>
@@ -30184,7 +30201,7 @@
         <v>Ideas Guy</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>269</v>
       </c>
@@ -30267,7 +30284,7 @@
         <v>Bengal Tiger</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>260</v>
       </c>
@@ -30359,7 +30376,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>161</v>
       </c>
@@ -30449,7 +30466,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>152</v>
       </c>
@@ -30539,7 +30556,7 @@
         <v>Kow-Tow</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>370</v>
       </c>
@@ -30627,7 +30644,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>422</v>
       </c>
@@ -30717,7 +30734,7 @@
         <v>A Sun God</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>469</v>
       </c>
@@ -30809,7 +30826,7 @@
         <v>Forever Golden</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>344</v>
       </c>
@@ -30899,7 +30916,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>342</v>
       </c>
@@ -30989,7 +31006,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>308</v>
       </c>
@@ -31079,7 +31096,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>398</v>
       </c>
@@ -31167,7 +31184,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>59</v>
       </c>
@@ -31252,7 +31269,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>221</v>
       </c>
@@ -31342,7 +31359,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>176</v>
       </c>
@@ -31425,7 +31442,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>157</v>
       </c>
@@ -31515,7 +31532,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>147</v>
       </c>
@@ -31605,7 +31622,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>117</v>
       </c>
@@ -31690,7 +31707,7 @@
         <v>Baa Baa Black Sheep</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>558</v>
       </c>
@@ -31780,7 +31797,7 @@
         <v>The Re-Reconquista</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>480</v>
       </c>
@@ -31870,7 +31887,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>545</v>
       </c>
@@ -31958,7 +31975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>452</v>
       </c>
@@ -32050,7 +32067,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>359</v>
       </c>
@@ -32140,7 +32157,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>353</v>
       </c>
@@ -32228,7 +32245,7 @@
         <v>The Iron Price</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>36</v>
       </c>
@@ -32261,27 +32278,32 @@
         <f t="shared" si="38"/>
         <v>1.8107599999999998E-2</v>
       </c>
-      <c r="J217" s="10" t="str">
+      <c r="J217" s="10">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="K217" s="10">
+        <v>1.8107599999999998E-2</v>
+      </c>
+      <c r="K217" s="10" t="str">
         <f t="shared" si="40"/>
-        <v>1.8107599999999998E-2</v>
+        <v/>
       </c>
       <c r="L217" s="9">
         <f t="shared" si="41"/>
         <v>0.9818924</v>
       </c>
-      <c r="M217" s="9" t="str">
+      <c r="M217" s="9">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="N217" s="9">
+        <v>0.9818924</v>
+      </c>
+      <c r="N217" s="9" t="str">
         <f t="shared" si="43"/>
-        <v>0.9818924</v>
-      </c>
-      <c r="O217" s="4"/>
+        <v/>
+      </c>
+      <c r="O217" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P217" s="1" t="s">
+        <v>1900</v>
+      </c>
       <c r="Q217" s="7"/>
       <c r="R217" s="7" t="s">
         <v>818</v>
@@ -32302,16 +32324,16 @@
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="X217">
+      <c r="X217" t="str">
         <f t="shared" si="47"/>
-        <v>1.8107599999999998E-2</v>
+        <v/>
       </c>
       <c r="Y217" t="str">
         <f>VLOOKUP($A217,Runs!$G:$G,1,FALSE)</f>
         <v>Krabater</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>146</v>
       </c>
@@ -32401,7 +32423,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>560</v>
       </c>
@@ -32489,7 +32511,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>505</v>
       </c>
@@ -32579,7 +32601,7 @@
         <v>Prester John</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>460</v>
       </c>
@@ -32669,7 +32691,7 @@
         <v>Baltic Crusader</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>411</v>
       </c>
@@ -32754,7 +32776,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>333</v>
       </c>
@@ -32842,7 +32864,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>330</v>
       </c>
@@ -32932,7 +32954,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>402</v>
       </c>
@@ -33022,7 +33044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>486</v>
       </c>
@@ -33107,7 +33129,7 @@
         <v>Luck of the Irish</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>441</v>
       </c>
@@ -33195,7 +33217,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>538</v>
       </c>
@@ -33285,7 +33307,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>93</v>
       </c>
@@ -33375,7 +33397,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>616</v>
       </c>
@@ -33465,7 +33487,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
@@ -33551,7 +33573,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>400</v>
       </c>
@@ -33639,7 +33661,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -33727,7 +33749,7 @@
         <v>A Blessed Nation</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>240</v>
       </c>
@@ -33817,7 +33839,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>279</v>
       </c>
@@ -33900,7 +33922,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>164</v>
       </c>
@@ -33988,7 +34010,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>312</v>
       </c>
@@ -34073,7 +34095,7 @@
         <v>Lion of the North</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>518</v>
       </c>
@@ -34161,7 +34183,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>310</v>
       </c>
@@ -34249,7 +34271,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>606</v>
       </c>
@@ -34339,7 +34361,7 @@
         <v>Shahanshah</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>473</v>
       </c>
@@ -34422,7 +34444,7 @@
         <v>Guarantor of Peace</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>409</v>
       </c>
@@ -34512,7 +34534,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>251</v>
       </c>
@@ -34602,7 +34624,7 @@
         <v>Relentless Push East</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>306</v>
       </c>
@@ -34690,7 +34712,7 @@
         <v>Kingdom of God</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>273</v>
       </c>
@@ -34778,7 +34800,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>97</v>
       </c>
@@ -34861,7 +34883,7 @@
         <v>Poland can into space</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>22</v>
       </c>
@@ -34953,7 +34975,7 @@
         <v>Foul Mouthed</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>143</v>
       </c>
@@ -35043,7 +35065,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>104</v>
       </c>
@@ -35133,7 +35155,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>263</v>
       </c>
@@ -35221,7 +35243,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>166</v>
       </c>
@@ -35309,7 +35331,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>112</v>
       </c>
@@ -35395,7 +35417,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>285</v>
       </c>
@@ -35485,7 +35507,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>168</v>
       </c>
@@ -35575,7 +35597,7 @@
         <v>Nobody wants to die</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>493</v>
       </c>
@@ -35660,7 +35682,7 @@
         <v>Master of India</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>231</v>
       </c>
@@ -35746,7 +35768,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>340</v>
       </c>
@@ -35834,7 +35856,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>202</v>
       </c>
@@ -35924,7 +35946,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>196</v>
       </c>
@@ -36012,7 +36034,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>364</v>
       </c>
@@ -36102,7 +36124,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>275</v>
       </c>
@@ -36185,7 +36207,7 @@
         <v>Definitely the Sultan of Rum</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>48</v>
       </c>
@@ -36273,7 +36295,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>497</v>
       </c>
@@ -36361,7 +36383,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>209</v>
       </c>
@@ -36444,7 +36466,7 @@
         <v>Winged Hussars</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>173</v>
       </c>
@@ -36527,7 +36549,7 @@
         <v>One King to Rule!</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>490</v>
       </c>
@@ -36617,7 +36639,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>256</v>
       </c>
@@ -36700,7 +36722,7 @@
         <v>The Spice Must Flow</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>259</v>
       </c>
@@ -36783,7 +36805,7 @@
         <v>A tale of two Families</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>129</v>
       </c>
@@ -36871,7 +36893,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>416</v>
       </c>
@@ -36959,7 +36981,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>393</v>
       </c>
@@ -37049,7 +37071,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>34</v>
       </c>
@@ -37134,7 +37156,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>373</v>
       </c>
@@ -37222,7 +37244,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>325</v>
       </c>
@@ -37310,7 +37332,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>247</v>
       </c>
@@ -37398,7 +37420,7 @@
         <v>Black Jack</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1677</v>
       </c>
@@ -37488,7 +37510,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>210</v>
       </c>
@@ -37578,7 +37600,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>190</v>
       </c>
@@ -37670,7 +37692,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>106</v>
       </c>
@@ -37760,7 +37782,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>130</v>
       </c>
@@ -37843,7 +37865,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>537</v>
       </c>
@@ -37931,7 +37953,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>381</v>
       </c>
@@ -38019,7 +38041,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>13</v>
       </c>
@@ -38109,7 +38131,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>38</v>
       </c>
@@ -38197,7 +38219,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>148</v>
       </c>
@@ -38285,7 +38307,7 @@
         <v>Imperio español</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>384</v>
       </c>
@@ -38375,7 +38397,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>204</v>
       </c>
@@ -38463,7 +38485,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>300</v>
       </c>
@@ -38553,7 +38575,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>89</v>
       </c>
@@ -38641,7 +38663,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>376</v>
       </c>
@@ -38726,7 +38748,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>124</v>
       </c>
@@ -38814,7 +38836,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>144</v>
       </c>
@@ -38902,7 +38924,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>233</v>
       </c>
@@ -38990,7 +39012,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>229</v>
       </c>
@@ -39078,7 +39100,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>414</v>
       </c>
@@ -39168,7 +39190,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>391</v>
       </c>
@@ -39253,7 +39275,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>3</v>
       </c>
@@ -39341,7 +39363,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>63</v>
       </c>
@@ -39428,7 +39450,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>304</v>
       </c>
@@ -39518,7 +39540,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>281</v>
       </c>
@@ -39610,7 +39632,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>101</v>
       </c>
@@ -39695,7 +39717,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>25</v>
       </c>
@@ -39783,7 +39805,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>141</v>
       </c>
@@ -39871,7 +39893,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>133</v>
       </c>
@@ -39958,7 +39980,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>395</v>
       </c>
@@ -40044,7 +40066,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>40</v>
       </c>
@@ -40134,7 +40156,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>212</v>
       </c>
@@ -40222,7 +40244,7 @@
         <v>A Fine Goosestep</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>323</v>
       </c>
@@ -40312,7 +40334,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>137</v>
       </c>
@@ -40402,7 +40424,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>250</v>
       </c>
@@ -40492,7 +40514,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>108</v>
       </c>
@@ -40580,7 +40602,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>223</v>
       </c>
@@ -40670,7 +40692,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>159</v>
       </c>
@@ -40758,7 +40780,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>175</v>
       </c>
@@ -40846,7 +40868,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>163</v>
       </c>
@@ -40936,7 +40958,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>262</v>
       </c>
@@ -41024,7 +41046,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>95</v>
       </c>
@@ -41112,7 +41134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>49</v>
       </c>
@@ -41202,7 +41224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>5</v>
       </c>
@@ -41292,7 +41314,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>313</v>
       </c>
@@ -41377,7 +41399,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>85</v>
       </c>
@@ -41465,7 +41487,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>271</v>
       </c>
@@ -41553,7 +41575,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>172</v>
       </c>
@@ -41641,7 +41663,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>75</v>
       </c>
@@ -41726,7 +41748,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>227</v>
       </c>
@@ -41816,7 +41838,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>42</v>
       </c>
@@ -41906,7 +41928,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>206</v>
       </c>
@@ -41994,7 +42016,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>203</v>
       </c>
@@ -42084,7 +42106,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>302</v>
       </c>
@@ -42172,7 +42194,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>135</v>
       </c>
@@ -42259,7 +42281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>219</v>
       </c>
@@ -42347,7 +42369,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>57</v>
       </c>
@@ -42435,7 +42457,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>110</v>
       </c>
@@ -42525,7 +42547,7 @@
         <v>All belongs to Mother Russia</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>87</v>
       </c>
@@ -42611,7 +42633,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>113</v>
       </c>
@@ -42701,7 +42723,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>18</v>
       </c>
@@ -42784,7 +42806,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>65</v>
       </c>
@@ -42872,7 +42894,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>315</v>
       </c>
@@ -42960,7 +42982,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>192</v>
       </c>
@@ -43050,7 +43072,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>30</v>
       </c>
@@ -43140,7 +43162,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>61</v>
       </c>
@@ -43228,7 +43250,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>122</v>
       </c>
@@ -43317,7 +43339,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>194</v>
       </c>
@@ -43403,7 +43425,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>0</v>
       </c>
@@ -43490,7 +43512,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>81</v>
       </c>
@@ -43578,7 +43600,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>131</v>
       </c>
@@ -43666,7 +43688,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>225</v>
       </c>
@@ -43751,7 +43773,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>115</v>
       </c>
@@ -43841,7 +43863,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>245</v>
       </c>
@@ -43926,7 +43948,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>7</v>
       </c>
@@ -44011,7 +44033,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>217</v>
       </c>
@@ -44096,7 +44118,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>374</v>
       </c>
@@ -44179,7 +44201,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>180</v>
       </c>
@@ -44264,7 +44286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>16</v>
       </c>
@@ -44354,7 +44376,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>44</v>
       </c>
@@ -44437,7 +44459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>27</v>
       </c>
@@ -44524,7 +44546,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>77</v>
       </c>
@@ -44609,7 +44631,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>69</v>
       </c>
@@ -44696,7 +44718,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -44783,7 +44805,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>150</v>
       </c>
@@ -44868,7 +44890,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>91</v>
       </c>
@@ -44953,7 +44975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>198</v>
       </c>
@@ -45043,7 +45065,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>14</v>
       </c>
@@ -45130,7 +45152,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>32</v>
       </c>
@@ -45215,7 +45237,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>67</v>
       </c>
@@ -45302,7 +45324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -45387,7 +45409,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>20</v>
       </c>
@@ -45472,7 +45494,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>55</v>
       </c>
@@ -45557,7 +45579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>46</v>
       </c>
@@ -45640,7 +45662,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>79</v>
       </c>
@@ -45723,7 +45745,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>51</v>
       </c>
@@ -45806,7 +45828,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>53</v>
       </c>
@@ -45893,7 +45915,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>73</v>
       </c>
@@ -45978,7 +46000,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>71</v>
       </c>
@@ -46066,13 +46088,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y374" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Inner Turmoil"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y374" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="393" priority="379">
@@ -54213,7 +54229,7 @@
       </c>
       <c r="H96" s="64" t="str">
         <f>IF(VLOOKUP($G96,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G96,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I96" s="42" t="str">
         <f>VLOOKUP($G96,List!$A:$U,2,FALSE)</f>
@@ -54279,7 +54295,7 @@
       </c>
       <c r="H97" s="64" t="str">
         <f>IF(VLOOKUP($G97,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G97,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I97" s="42" t="str">
         <f>VLOOKUP($G97,List!$A:$U,2,FALSE)</f>
@@ -56167,7 +56183,7 @@
       </c>
       <c r="H125" s="64" t="str">
         <f>IF(VLOOKUP($G125,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G125,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I125" s="42" t="str">
         <f>VLOOKUP($G125,List!$A:$U,2,FALSE)</f>
@@ -56246,7 +56262,7 @@
       </c>
       <c r="H126" s="63" t="str">
         <f>IF(VLOOKUP($G126,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G126,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I126" s="47" t="str">
         <f>VLOOKUP($G126,List!$A:$U,2,FALSE)</f>
@@ -59481,7 +59497,7 @@
     <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
       <c r="I2" s="29">
         <f>K2/J2</f>
-        <v>0.60065844111226274</v>
+        <v>0.60700479628632753</v>
       </c>
       <c r="J2" s="28">
         <f>SUM(List!E:E)</f>
@@ -59489,11 +59505,11 @@
       </c>
       <c r="K2" s="27">
         <f>SUMIFS(List!$E:$E,List!$O:$O,"Y")</f>
-        <v>22203.999999999996</v>
+        <v>22438.599999999995</v>
       </c>
       <c r="L2" s="1">
         <f>COUNTIFS(List!O:O,"Y")</f>
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -60427,12 +60443,12 @@
       </c>
       <c r="X12" s="1" t="str" cm="1">
         <f t="array" ref="X12">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(8:8)),List!K:K,0))</f>
-        <v>Where are the penguins?</v>
+        <v>Stardust Crusaders</v>
       </c>
       <c r="Y12" s="2" t="str">
         <f>VLOOKUP($X12,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As a Malagasy country, unite Madagascar and hold all the most southern 
-provinces of the world.</v>
+        <v>As Japan have the Land of the Christian Sun reform while Palestine and 
+Cairo are Christian under us.</v>
       </c>
       <c r="Z12" s="3">
         <f>VLOOKUP($X12,List!$A$1:$U$374,3,FALSE)</f>
@@ -60552,12 +60568,11 @@
       </c>
       <c r="X13" s="1" t="str" cm="1">
         <f t="array" ref="X13">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(9:9)),List!K:K,0))</f>
-        <v>Stardust Crusaders</v>
+        <v>New, New Deli</v>
       </c>
       <c r="Y13" s="15" t="str">
         <f>VLOOKUP($X13,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Japan have the Land of the Christian Sun reform while Palestine and 
-Cairo are Christian under us.</v>
+        <v>As Deli, have your capital in the Delhi province.</v>
       </c>
       <c r="Z13" s="16">
         <f>VLOOKUP($X13,List!$A$1:$U$374,3,FALSE)</f>
@@ -60565,7 +60580,7 @@
       </c>
       <c r="AA13" s="17" t="str">
         <f>VLOOKUP($X13,List!$A$1:$U$374,4,FALSE)</f>
-        <v>M</v>
+        <v>H</v>
       </c>
       <c r="AB13" s="25">
         <f>IF(VLOOKUP($X13,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B13,List!$A$1:$U$374,5,FALSE))</f>
@@ -60660,11 +60675,12 @@
       </c>
       <c r="X14" s="1" t="str" cm="1">
         <f t="array" ref="X14">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(10:10)),List!K:K,0))</f>
-        <v>New, New Deli</v>
+        <v>One nation to rule them all</v>
       </c>
       <c r="Y14" s="2" t="str">
         <f>VLOOKUP($X14,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Deli, have your capital in the Delhi province.</v>
+        <v>As Saruhan, have at least 9 loyal vassals with at least 100 development 
+each.</v>
       </c>
       <c r="Z14" s="3">
         <f>VLOOKUP($X14,List!$A$1:$U$374,3,FALSE)</f>
@@ -60770,12 +60786,12 @@
       </c>
       <c r="X15" s="1" t="str" cm="1">
         <f t="array" ref="X15">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(11:11)),List!K:K,0))</f>
-        <v>One nation to rule them all</v>
+        <v>Almost Prussian Blue</v>
       </c>
       <c r="Y15" s="15" t="str">
         <f>VLOOKUP($X15,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Saruhan, have at least 9 loyal vassals with at least 100 development 
-each.</v>
+        <v>Starting as the Livonian Order, form Livonia and own the territory of the 
+North German Confederation as core provinces.</v>
       </c>
       <c r="Z15" s="16">
         <f>VLOOKUP($X15,List!$A$1:$U$374,3,FALSE)</f>
@@ -63959,15 +63975,15 @@
       </c>
       <c r="B31" s="1" t="str" cm="1">
         <f t="array" ref="B31">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(3:3)),List!X:X,0))</f>
-        <v>Krabater</v>
+        <v>The Six Nations</v>
       </c>
       <c r="C31" s="2" t="str">
         <f>VLOOKUP($B31,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Form the nation of Croatia and station a unit of cavalry in Stockholm.</v>
+        <v>Form a Federation of at least six nations as the Iroquois.</v>
       </c>
       <c r="D31" s="3">
         <f>VLOOKUP($B31,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.7999999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="E31" s="6" t="str">
         <f>VLOOKUP($B31,List!$A$1:$U$374,4,FALSE)</f>
@@ -63975,7 +63991,7 @@
       </c>
       <c r="F31" s="26">
         <f>IF(VLOOKUP($B31,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B31,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.1</v>
+        <v>14.15</v>
       </c>
       <c r="G31" s="4" t="str">
         <f>IF(VLOOKUP($B31,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B31,List!$A$1:$U$374,15,FALSE))</f>
@@ -63992,15 +64008,16 @@
       </c>
       <c r="B32" s="14" t="str" cm="1">
         <f t="array" ref="B32">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(4:4)),List!X:X,0))</f>
-        <v>The Six Nations</v>
+        <v>From Humble Origins</v>
       </c>
       <c r="C32" s="15" t="str">
         <f>VLOOKUP($B32,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Form a Federation of at least six nations as the Iroquois.</v>
+        <v>Starting as a custom nation with no more than 50 points, have at least 
+2000 total development.</v>
       </c>
       <c r="D32" s="16">
         <f>VLOOKUP($B32,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.7000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="E32" s="17" t="str">
         <f>VLOOKUP($B32,List!$A$1:$U$374,4,FALSE)</f>
@@ -64008,7 +64025,7 @@
       </c>
       <c r="F32" s="25">
         <f>IF(VLOOKUP($B32,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B32,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.15</v>
+        <v>14.35</v>
       </c>
       <c r="G32" s="18" t="str">
         <f>IF(VLOOKUP($B32,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B32,List!$A$1:$U$374,15,FALSE))</f>
@@ -64025,16 +64042,15 @@
       </c>
       <c r="B33" s="1" t="str" cm="1">
         <f t="array" ref="B33">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(5:5)),List!X:X,0))</f>
-        <v>From Humble Origins</v>
+        <v>David the Builder</v>
       </c>
       <c r="C33" s="2" t="str">
         <f>VLOOKUP($B33,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as a custom nation with no more than 50 points, have at least 
-2000 total development.</v>
+        <v>As Georgia have no free building slots in any owned province.</v>
       </c>
       <c r="D33" s="3">
         <f>VLOOKUP($B33,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="E33" s="6" t="str">
         <f>VLOOKUP($B33,List!$A$1:$U$374,4,FALSE)</f>
@@ -64042,7 +64058,7 @@
       </c>
       <c r="F33" s="26">
         <f>IF(VLOOKUP($B33,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B33,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.35</v>
+        <v>14.4</v>
       </c>
       <c r="G33" s="4" t="str">
         <f>IF(VLOOKUP($B33,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B33,List!$A$1:$U$374,15,FALSE))</f>
@@ -64059,15 +64075,15 @@
       </c>
       <c r="B34" s="14" t="str" cm="1">
         <f t="array" ref="B34">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(6:6)),List!X:X,0))</f>
-        <v>David the Builder</v>
+        <v>Sakoku Law</v>
       </c>
       <c r="C34" s="15" t="str">
         <f>VLOOKUP($B34,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Georgia have no free building slots in any owned province.</v>
+        <v>Go full isolationist in 6 Incidents.</v>
       </c>
       <c r="D34" s="16">
         <f>VLOOKUP($B34,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.2E-2</v>
+        <v>0.01</v>
       </c>
       <c r="E34" s="17" t="str">
         <f>VLOOKUP($B34,List!$A$1:$U$374,4,FALSE)</f>
@@ -64075,7 +64091,7 @@
       </c>
       <c r="F34" s="25">
         <f>IF(VLOOKUP($B34,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B34,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G34" s="18" t="str">
         <f>IF(VLOOKUP($B34,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B34,List!$A$1:$U$374,15,FALSE))</f>
@@ -64092,15 +64108,16 @@
       </c>
       <c r="B35" s="1" t="str" cm="1">
         <f t="array" ref="B35">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(7:7)),List!X:X,0))</f>
-        <v>Sakoku Law</v>
+        <v>Truly Good Maaaaa-tch</v>
       </c>
       <c r="C35" s="2" t="str">
         <f>VLOOKUP($B35,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Go full isolationist in 6 Incidents.</v>
+        <v>Starting as either Aq Qoyunlu or Qara Qoyunlu, have a royal marriage and 
+an alliance with Ramazan.</v>
       </c>
       <c r="D35" s="3">
         <f>VLOOKUP($B35,List!$A$1:$U$374,3,FALSE)</f>
-        <v>0.01</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E35" s="6" t="str">
         <f>VLOOKUP($B35,List!$A$1:$U$374,4,FALSE)</f>
@@ -64108,7 +64125,7 @@
       </c>
       <c r="F35" s="26">
         <f>IF(VLOOKUP($B35,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B35,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.5</v>
+        <v>14.65</v>
       </c>
       <c r="G35" s="4" t="str">
         <f>IF(VLOOKUP($B35,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B35,List!$A$1:$U$374,15,FALSE))</f>
@@ -64125,16 +64142,16 @@
       </c>
       <c r="B36" s="14" t="str" cm="1">
         <f t="array" ref="B36">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(8:8)),List!X:X,0))</f>
-        <v>Truly Good Maaaaa-tch</v>
+        <v>Imposter Syndrome</v>
       </c>
       <c r="C36" s="15" t="str">
         <f>VLOOKUP($B36,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as either Aq Qoyunlu or Qara Qoyunlu, have a royal marriage and 
-an alliance with Ramazan.</v>
+        <v>As Sus, have three countries hostile to you (less than 0 opinion) after 
+they discovered your spy.</v>
       </c>
       <c r="D36" s="16">
         <f>VLOOKUP($B36,List!$A$1:$U$374,3,FALSE)</f>
-        <v>7.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E36" s="17" t="str">
         <f>VLOOKUP($B36,List!$A$1:$U$374,4,FALSE)</f>
@@ -64142,7 +64159,7 @@
       </c>
       <c r="F36" s="25">
         <f>IF(VLOOKUP($B36,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B36,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.65</v>
+        <v>14.7</v>
       </c>
       <c r="G36" s="18" t="str">
         <f>IF(VLOOKUP($B36,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B36,List!$A$1:$U$374,15,FALSE))</f>
@@ -64157,34 +64174,33 @@
       <c r="A37" s="19">
         <v>9</v>
       </c>
-      <c r="B37" s="1" t="str" cm="1">
+      <c r="B37" s="1" t="e" cm="1">
         <f t="array" ref="B37">INDEX(List!A:A,MATCH(LARGE(List!X:X,ROW(9:9)),List!X:X,0))</f>
-        <v>Imposter Syndrome</v>
-      </c>
-      <c r="C37" s="2" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="C37" s="2" t="e">
         <f>VLOOKUP($B37,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Sus, have three countries hostile to you (less than 0 opinion) after 
-they discovered your spy.</v>
-      </c>
-      <c r="D37" s="3">
+        <v>#NUM!</v>
+      </c>
+      <c r="D37" s="3" t="e">
         <f>VLOOKUP($B37,List!$A$1:$U$374,3,FALSE)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="E37" s="6" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="E37" s="6" t="e">
         <f>VLOOKUP($B37,List!$A$1:$U$374,4,FALSE)</f>
-        <v>VE</v>
-      </c>
-      <c r="F37" s="26">
+        <v>#NUM!</v>
+      </c>
+      <c r="F37" s="26" t="e">
         <f>IF(VLOOKUP($B37,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B37,List!$A$1:$U$374,5,FALSE))</f>
-        <v>14.7</v>
-      </c>
-      <c r="G37" s="4" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="G37" s="4" t="e">
         <f>IF(VLOOKUP($B37,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B37,List!$A$1:$U$374,15,FALSE))</f>
-        <v/>
-      </c>
-      <c r="H37" s="1" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="H37" s="1" t="e">
         <f>IF(VLOOKUP($B37,List!$A$1:$U$374,16,FALSE)="","",VLOOKUP($B37,List!$A$1:$U$374,16,FALSE))</f>
-        <v/>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BB83F2-FA0E-4154-B38E-F4C55DE77D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DCFC04-621C-4FDE-8693-2BD8753AD1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3857" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="2056">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -17583,27 +17583,32 @@
         <f t="shared" si="2"/>
         <v>6.4064000000000005E-3</v>
       </c>
-      <c r="J49" s="10" t="str">
+      <c r="J49" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K49" s="10">
+        <v>6.4064000000000005E-3</v>
+      </c>
+      <c r="K49" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>6.4064000000000005E-3</v>
+        <v/>
       </c>
       <c r="L49" s="9">
         <f t="shared" si="5"/>
         <v>3.9935936000000001</v>
       </c>
-      <c r="M49" s="9" t="str">
+      <c r="M49" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N49" s="9">
+        <v>3.9935936000000001</v>
+      </c>
+      <c r="N49" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>3.9935936000000001</v>
-      </c>
-      <c r="O49" s="4"/>
+        <v/>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>1860</v>
+      </c>
       <c r="Q49" s="7" t="s">
         <v>1551</v>
       </c>
@@ -17622,9 +17627,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W49">
+      <c r="W49" t="str">
         <f t="shared" si="10"/>
-        <v>6.4064000000000005E-3</v>
+        <v/>
       </c>
       <c r="X49" t="str">
         <f t="shared" si="11"/>
@@ -17668,27 +17673,32 @@
         <f t="shared" si="2"/>
         <v>6.4065000000000007E-3</v>
       </c>
-      <c r="J50" s="10" t="str">
+      <c r="J50" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K50" s="10">
+        <v>6.4065000000000007E-3</v>
+      </c>
+      <c r="K50" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>6.4065000000000007E-3</v>
+        <v/>
       </c>
       <c r="L50" s="9">
         <f t="shared" si="5"/>
         <v>3.9935934999999998</v>
       </c>
-      <c r="M50" s="9" t="str">
+      <c r="M50" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N50" s="9">
+        <v>3.9935934999999998</v>
+      </c>
+      <c r="N50" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>3.9935934999999998</v>
-      </c>
-      <c r="O50" s="4"/>
+        <v/>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>1916</v>
+      </c>
       <c r="Q50" s="7" t="s">
         <v>932</v>
       </c>
@@ -17707,9 +17717,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W50">
+      <c r="W50" t="str">
         <f t="shared" si="10"/>
-        <v>6.4065000000000007E-3</v>
+        <v/>
       </c>
       <c r="X50" t="str">
         <f t="shared" si="11"/>
@@ -18006,27 +18016,32 @@
         <f t="shared" si="2"/>
         <v>6.4069000000000001E-3</v>
       </c>
-      <c r="J54" s="10" t="str">
+      <c r="J54" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K54" s="10">
+        <v>6.4069000000000001E-3</v>
+      </c>
+      <c r="K54" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>6.4069000000000001E-3</v>
+        <v/>
       </c>
       <c r="L54" s="9">
         <f t="shared" si="5"/>
         <v>3.9935931</v>
       </c>
-      <c r="M54" s="9" t="str">
+      <c r="M54" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N54" s="9">
+        <v>3.9935931</v>
+      </c>
+      <c r="N54" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>3.9935931</v>
-      </c>
-      <c r="O54" s="4"/>
+        <v/>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>1704</v>
+      </c>
       <c r="Q54" s="7" t="s">
         <v>1373</v>
       </c>
@@ -18045,9 +18060,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W54">
+      <c r="W54" t="str">
         <f t="shared" si="10"/>
-        <v>6.4069000000000001E-3</v>
+        <v/>
       </c>
       <c r="X54" t="str">
         <f t="shared" si="11"/>
@@ -28558,27 +28573,32 @@
         <f t="shared" si="26"/>
         <v>1.33043E-2</v>
       </c>
-      <c r="J175" s="10" t="str">
+      <c r="J175" s="10">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="K175" s="10">
+        <v>1.33043E-2</v>
+      </c>
+      <c r="K175" s="10" t="str">
         <f t="shared" si="28"/>
-        <v>1.33043E-2</v>
+        <v/>
       </c>
       <c r="L175" s="9">
         <f t="shared" si="29"/>
         <v>2.9866956999999998</v>
       </c>
-      <c r="M175" s="9" t="str">
+      <c r="M175" s="9">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="N175" s="9">
+        <v>2.9866956999999998</v>
+      </c>
+      <c r="N175" s="9" t="str">
         <f t="shared" si="31"/>
-        <v>2.9866956999999998</v>
-      </c>
-      <c r="O175" s="4"/>
+        <v/>
+      </c>
+      <c r="O175" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P175" s="1" t="s">
+        <v>1916</v>
+      </c>
       <c r="Q175" s="7" t="s">
         <v>1118</v>
       </c>
@@ -28591,9 +28611,9 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="V175">
+      <c r="V175" t="str">
         <f t="shared" si="33"/>
-        <v>1.33043E-2</v>
+        <v/>
       </c>
       <c r="W175" t="str">
         <f t="shared" si="34"/>
@@ -33077,27 +33097,32 @@
         <f t="shared" si="38"/>
         <v>2.1400400000000003E-2</v>
       </c>
-      <c r="J226" s="10" t="str">
+      <c r="J226" s="10">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="K226" s="10">
+        <v>2.1400400000000003E-2</v>
+      </c>
+      <c r="K226" s="10" t="str">
         <f t="shared" si="40"/>
-        <v>2.1400400000000003E-2</v>
+        <v/>
       </c>
       <c r="L226" s="9">
         <f t="shared" si="41"/>
         <v>3.9785995999999999</v>
       </c>
-      <c r="M226" s="9" t="str">
+      <c r="M226" s="9">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="N226" s="9">
+        <v>3.9785995999999999</v>
+      </c>
+      <c r="N226" s="9" t="str">
         <f t="shared" si="43"/>
-        <v>3.9785995999999999</v>
-      </c>
-      <c r="O226" s="4"/>
+        <v/>
+      </c>
+      <c r="O226" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P226" s="1" t="s">
+        <v>2003</v>
+      </c>
       <c r="Q226" s="7" t="s">
         <v>1364</v>
       </c>
@@ -33116,9 +33141,9 @@
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="W226">
+      <c r="W226" t="str">
         <f t="shared" si="46"/>
-        <v>2.1400400000000003E-2</v>
+        <v/>
       </c>
       <c r="X226" t="str">
         <f t="shared" si="47"/>
@@ -33872,27 +33897,32 @@
         <f t="shared" si="38"/>
         <v>2.3304100000000001E-2</v>
       </c>
-      <c r="J235" s="10" t="str">
+      <c r="J235" s="10">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="K235" s="10">
+        <v>2.3304100000000001E-2</v>
+      </c>
+      <c r="K235" s="10" t="str">
         <f t="shared" si="40"/>
-        <v>2.3304100000000001E-2</v>
+        <v/>
       </c>
       <c r="L235" s="9">
         <f t="shared" si="41"/>
         <v>2.9766959000000002</v>
       </c>
-      <c r="M235" s="9" t="str">
+      <c r="M235" s="9">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="N235" s="9">
+        <v>2.9766959000000002</v>
+      </c>
+      <c r="N235" s="9" t="str">
         <f t="shared" si="43"/>
-        <v>2.9766959000000002</v>
-      </c>
-      <c r="O235" s="4"/>
+        <v/>
+      </c>
+      <c r="O235" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P235" s="1" t="s">
+        <v>1860</v>
+      </c>
       <c r="Q235" s="7"/>
       <c r="R235" s="8" t="s">
         <v>1091</v>
@@ -33905,9 +33935,9 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="V235">
+      <c r="V235" t="str">
         <f t="shared" si="45"/>
-        <v>2.3304100000000001E-2</v>
+        <v/>
       </c>
       <c r="W235" t="str">
         <f t="shared" si="46"/>
@@ -52030,7 +52060,7 @@
       </c>
       <c r="H63" s="64" t="str">
         <f>IF(VLOOKUP($G63,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G63,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I63" s="42" t="str">
         <f>VLOOKUP($G63,List!$A:$U,2,FALSE)</f>
@@ -52303,7 +52333,7 @@
       </c>
       <c r="H67" s="63" t="str">
         <f>IF(VLOOKUP($G67,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G67,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I67" s="47" t="str">
         <f>VLOOKUP($G67,List!$A:$U,2,FALSE)</f>
@@ -54981,7 +55011,7 @@
       </c>
       <c r="H107" s="63" t="str">
         <f>IF(VLOOKUP($G107,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G107,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I107" s="47" t="str">
         <f>VLOOKUP($G107,List!$A:$U,2,FALSE)</f>
@@ -55299,7 +55329,7 @@
       </c>
       <c r="H112" s="64" t="str">
         <f>IF(VLOOKUP($G112,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G112,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I112" s="42" t="str">
         <f>VLOOKUP($G112,List!$A:$U,2,FALSE)</f>
@@ -55364,7 +55394,7 @@
       </c>
       <c r="H113" s="63" t="str">
         <f>IF(VLOOKUP($G113,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G113,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I113" s="47" t="str">
         <f>VLOOKUP($G113,List!$A:$U,2,FALSE)</f>
@@ -59497,7 +59527,7 @@
     <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
       <c r="I2" s="29">
         <f>K2/J2</f>
-        <v>0.60700479628632753</v>
+        <v>0.62652267888687241</v>
       </c>
       <c r="J2" s="28">
         <f>SUM(List!E:E)</f>
@@ -59505,11 +59535,11 @@
       </c>
       <c r="K2" s="27">
         <f>SUMIFS(List!$E:$E,List!$O:$O,"Y")</f>
-        <v>22438.599999999995</v>
+        <v>23160.099999999995</v>
       </c>
       <c r="L2" s="1">
         <f>COUNTIFS(List!O:O,"Y")</f>
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -63450,15 +63480,15 @@
       </c>
       <c r="K18" s="1" t="str" cm="1">
         <f t="array" ref="K18">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(3:3)),List!W:W,0))</f>
-        <v>Luck of the Irish</v>
+        <v>A Hero’s Welcome</v>
       </c>
       <c r="L18" s="2" t="str">
         <f>VLOOKUP($K18,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Own and have cores on the British Isles as an Irish nation.</v>
+        <v>Starting as Karaman, form the Sultanate of Rum.</v>
       </c>
       <c r="M18" s="3">
         <f>VLOOKUP($K18,List!$A$1:$U$374,3,FALSE)</f>
-        <v>2.1000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="N18" s="6" t="str">
         <f>VLOOKUP($K18,List!$A$1:$U$374,4,FALSE)</f>
@@ -63466,7 +63496,7 @@
       </c>
       <c r="O18" s="26">
         <f>IF(VLOOKUP($K18,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($K18,List!$A$1:$U$374,5,FALSE))</f>
-        <v>139.5</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -63507,15 +63537,15 @@
       </c>
       <c r="K19" s="14" t="str" cm="1">
         <f t="array" ref="K19">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(4:4)),List!W:W,0))</f>
-        <v>A Hero’s Welcome</v>
+        <v>Lazarus</v>
       </c>
       <c r="L19" s="15" t="str">
         <f>VLOOKUP($K19,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as Karaman, form the Sultanate of Rum.</v>
+        <v>As Serbia, own the entire Balkans as core provinces.</v>
       </c>
       <c r="M19" s="16">
         <f>VLOOKUP($K19,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="N19" s="17" t="str">
         <f>VLOOKUP($K19,List!$A$1:$U$374,4,FALSE)</f>
@@ -63523,7 +63553,7 @@
       </c>
       <c r="O19" s="25">
         <f>IF(VLOOKUP($K19,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($K19,List!$A$1:$U$374,5,FALSE))</f>
-        <v>143.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -63532,15 +63562,16 @@
       </c>
       <c r="B20" s="1" t="str" cm="1">
         <f t="array" ref="B20">INDEX(List!A:A,MATCH(LARGE(List!V:V,ROW(5:5)),List!V:V,0))</f>
-        <v>Even Better than Piet Heyn</v>
+        <v>Spice Girls</v>
       </c>
       <c r="C20" s="2" t="str">
         <f>VLOOKUP($B20,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Gain over 100 gold from privateering a single treasure fleet.</v>
+        <v>Having a female ruler, have active trading bonuses for Cloves, Spices, 
+Salt and Sugar.</v>
       </c>
       <c r="D20" s="3">
         <f>VLOOKUP($B20,List!$A$1:$U$374,3,FALSE)</f>
-        <v>2.3E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E20" s="6" t="str">
         <f>VLOOKUP($B20,List!$A$1:$U$374,4,FALSE)</f>
@@ -63548,7 +63579,7 @@
       </c>
       <c r="F20" s="26">
         <f>IF(VLOOKUP($B20,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B20,List!$A$1:$U$374,5,FALSE))</f>
-        <v>69.25</v>
+        <v>70</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>IF(VLOOKUP($B20,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B20,List!$A$1:$U$374,15,FALSE))</f>
@@ -63563,11 +63594,11 @@
       </c>
       <c r="K20" s="1" t="str" cm="1">
         <f t="array" ref="K20">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(5:5)),List!W:W,0))</f>
-        <v>Lazarus</v>
+        <v>Rise of the White Sheep</v>
       </c>
       <c r="L20" s="2" t="str">
         <f>VLOOKUP($K20,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Serbia, own the entire Balkans as core provinces.</v>
+        <v>As Aq Qoyunlu, own Tabriz and have Qara Qoyunlu not exist by 1478.</v>
       </c>
       <c r="M20" s="3">
         <f>VLOOKUP($K20,List!$A$1:$U$374,3,FALSE)</f>
@@ -63588,16 +63619,15 @@
       </c>
       <c r="B21" s="14" t="str" cm="1">
         <f t="array" ref="B21">INDEX(List!A:A,MATCH(LARGE(List!V:V,ROW(6:6)),List!V:V,0))</f>
-        <v>Spice Girls</v>
+        <v>Sweet Home Qaraqorum</v>
       </c>
       <c r="C21" s="15" t="str">
         <f>VLOOKUP($B21,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Having a female ruler, have active trading bonuses for Cloves, Spices, 
-Salt and Sugar.</v>
+        <v>As the Mughals assimilate Mongolian culture.</v>
       </c>
       <c r="D21" s="16">
         <f>VLOOKUP($B21,List!$A$1:$U$374,3,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E21" s="17" t="str">
         <f>VLOOKUP($B21,List!$A$1:$U$374,4,FALSE)</f>
@@ -63605,7 +63635,7 @@
       </c>
       <c r="F21" s="25">
         <f>IF(VLOOKUP($B21,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B21,List!$A$1:$U$374,5,FALSE))</f>
-        <v>70</v>
+        <v>71.25</v>
       </c>
       <c r="G21" s="18" t="str">
         <f>IF(VLOOKUP($B21,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B21,List!$A$1:$U$374,15,FALSE))</f>
@@ -63620,15 +63650,16 @@
       </c>
       <c r="K21" s="14" t="str" cm="1">
         <f t="array" ref="K21">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(6:6)),List!W:W,0))</f>
-        <v>Rise of the White Sheep</v>
+        <v>Choson One</v>
       </c>
       <c r="L21" s="15" t="str">
         <f>VLOOKUP($K21,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Aq Qoyunlu, own Tabriz and have Qara Qoyunlu not exist by 1478.</v>
+        <v>As Korea, own or have a subject own all Shinto, Confucian and Buddhist 
+provinces in the world.</v>
       </c>
       <c r="M21" s="16">
         <f>VLOOKUP($K21,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.2E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="N21" s="17" t="str">
         <f>VLOOKUP($K21,List!$A$1:$U$374,4,FALSE)</f>
@@ -63636,7 +63667,7 @@
       </c>
       <c r="O21" s="25">
         <f>IF(VLOOKUP($K21,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($K21,List!$A$1:$U$374,5,FALSE))</f>
-        <v>144</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -63645,11 +63676,11 @@
       </c>
       <c r="B22" s="1" t="str" cm="1">
         <f t="array" ref="B22">INDEX(List!A:A,MATCH(LARGE(List!V:V,ROW(7:7)),List!V:V,0))</f>
-        <v>Sweet Home Qaraqorum</v>
+        <v>The Uncommonwealth</v>
       </c>
       <c r="C22" s="2" t="str">
         <f>VLOOKUP($B22,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As the Mughals assimilate Mongolian culture.</v>
+        <v>As Lithuania, become The Commonwealth.</v>
       </c>
       <c r="D22" s="3">
         <f>VLOOKUP($B22,List!$A$1:$U$374,3,FALSE)</f>
@@ -63676,16 +63707,15 @@
       </c>
       <c r="K22" s="1" t="str" cm="1">
         <f t="array" ref="K22">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(7:7)),List!W:W,0))</f>
-        <v>Choson One</v>
+        <v>Lucky Lucca</v>
       </c>
       <c r="L22" s="2" t="str">
         <f>VLOOKUP($K22,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Korea, own or have a subject own all Shinto, Confucian and Buddhist 
-provinces in the world.</v>
+        <v>As Lucca, own Lucknow!</v>
       </c>
       <c r="M22" s="3">
         <f>VLOOKUP($K22,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.0999999999999999E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="N22" s="6" t="str">
         <f>VLOOKUP($K22,List!$A$1:$U$374,4,FALSE)</f>
@@ -63693,7 +63723,7 @@
       </c>
       <c r="O22" s="26">
         <f>IF(VLOOKUP($K22,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($K22,List!$A$1:$U$374,5,FALSE))</f>
-        <v>144.5</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -63702,11 +63732,11 @@
       </c>
       <c r="B23" s="14" t="str" cm="1">
         <f t="array" ref="B23">INDEX(List!A:A,MATCH(LARGE(List!V:V,ROW(8:8)),List!V:V,0))</f>
-        <v>The Uncommonwealth</v>
+        <v>Bengal Tiger</v>
       </c>
       <c r="C23" s="15" t="str">
         <f>VLOOKUP($B23,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Lithuania, become The Commonwealth.</v>
+        <v>Start as Bengal and own Samarkand as a core province.</v>
       </c>
       <c r="D23" s="16">
         <f>VLOOKUP($B23,List!$A$1:$U$374,3,FALSE)</f>
@@ -63733,15 +63763,15 @@
       </c>
       <c r="K23" s="14" t="str" cm="1">
         <f t="array" ref="K23">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(8:8)),List!W:W,0))</f>
-        <v>Lucky Lucca</v>
+        <v>Meissner Porcelain</v>
       </c>
       <c r="L23" s="15" t="str">
         <f>VLOOKUP($K23,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Lucca, own Lucknow!</v>
+        <v>As Saxony, own or have a subject own all Chinaware provinces in the world.</v>
       </c>
       <c r="M23" s="16">
         <f>VLOOKUP($K23,List!$A$1:$U$374,3,FALSE)</f>
-        <v>8.9999999999999993E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="N23" s="17" t="str">
         <f>VLOOKUP($K23,List!$A$1:$U$374,4,FALSE)</f>
@@ -63749,7 +63779,7 @@
       </c>
       <c r="O23" s="25">
         <f>IF(VLOOKUP($K23,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($K23,List!$A$1:$U$374,5,FALSE))</f>
-        <v>145.5</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -63758,15 +63788,16 @@
       </c>
       <c r="B24" s="1" t="str" cm="1">
         <f t="array" ref="B24">INDEX(List!A:A,MATCH(LARGE(List!V:V,ROW(9:9)),List!V:V,0))</f>
-        <v>Bengal Tiger</v>
+        <v>Sons of Carthage</v>
       </c>
       <c r="C24" s="2" t="str">
         <f>VLOOKUP($B24,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Start as Bengal and own Samarkand as a core province.</v>
+        <v>As Tunisia, own and have cores on Sicily, Sardinia, the Balearic Islands, 
+the coast of Algiers and the southern coast of Spain.</v>
       </c>
       <c r="D24" s="3">
         <f>VLOOKUP($B24,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E24" s="6" t="str">
         <f>VLOOKUP($B24,List!$A$1:$U$374,4,FALSE)</f>
@@ -63774,7 +63805,7 @@
       </c>
       <c r="F24" s="26">
         <f>IF(VLOOKUP($B24,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B24,List!$A$1:$U$374,5,FALSE))</f>
-        <v>71.25</v>
+        <v>71.5</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>IF(VLOOKUP($B24,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B24,List!$A$1:$U$374,15,FALSE))</f>
@@ -63789,11 +63820,11 @@
       </c>
       <c r="K24" s="1" t="str" cm="1">
         <f t="array" ref="K24">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(9:9)),List!W:W,0))</f>
-        <v>Meissner Porcelain</v>
+        <v>Philippine Tiger</v>
       </c>
       <c r="L24" s="2" t="str">
         <f>VLOOKUP($K24,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Saxony, own or have a subject own all Chinaware provinces in the world.</v>
+        <v>As Cebu, recreate the Chola Empire.</v>
       </c>
       <c r="M24" s="3">
         <f>VLOOKUP($K24,List!$A$1:$U$374,3,FALSE)</f>
@@ -63814,16 +63845,15 @@
       </c>
       <c r="B25" s="14" t="str" cm="1">
         <f t="array" ref="B25">INDEX(List!A:A,MATCH(LARGE(List!V:V,ROW(10:10)),List!V:V,0))</f>
-        <v>Sons of Carthage</v>
+        <v>Parisian Pasha</v>
       </c>
       <c r="C25" s="15" t="str">
         <f>VLOOKUP($B25,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Tunisia, own and have cores on Sicily, Sardinia, the Balearic Islands, 
-the coast of Algiers and the southern coast of Spain.</v>
+        <v>Assign Pasha to Paris.</v>
       </c>
       <c r="D25" s="16">
         <f>VLOOKUP($B25,List!$A$1:$U$374,3,FALSE)</f>
-        <v>1.4E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="E25" s="17" t="str">
         <f>VLOOKUP($B25,List!$A$1:$U$374,4,FALSE)</f>
@@ -63831,7 +63861,7 @@
       </c>
       <c r="F25" s="25">
         <f>IF(VLOOKUP($B25,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B25,List!$A$1:$U$374,5,FALSE))</f>
-        <v>71.5</v>
+        <v>71.75</v>
       </c>
       <c r="G25" s="18" t="str">
         <f>IF(VLOOKUP($B25,List!$A$1:$U$374,15,FALSE)="","",VLOOKUP($B25,List!$A$1:$U$374,15,FALSE))</f>
@@ -63846,11 +63876,12 @@
       </c>
       <c r="K25" s="14" t="str" cm="1">
         <f t="array" ref="K25">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(10:10)),List!W:W,0))</f>
-        <v>Philippine Tiger</v>
+        <v>Holy Horder</v>
       </c>
       <c r="L25" s="15" t="str">
         <f>VLOOKUP($K25,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Cebu, recreate the Chola Empire.</v>
+        <v>Starting as the Teutonic Order, form the Mongol Empire while have the Holy 
+Horde government reform enacted.</v>
       </c>
       <c r="M25" s="16">
         <f>VLOOKUP($K25,List!$A$1:$U$374,3,FALSE)</f>

--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DCFC04-621C-4FDE-8693-2BD8753AD1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22706E8A-8D9E-4BC8-B0F2-EC154A9F50FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
+    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="17520" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="2056">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -19239,27 +19239,32 @@
         <f t="shared" si="14"/>
         <v>7.4048000000000004E-3</v>
       </c>
-      <c r="J68" s="10" t="str">
+      <c r="J68" s="10">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K68" s="10">
+        <v>7.4048000000000004E-3</v>
+      </c>
+      <c r="K68" s="10" t="str">
         <f t="shared" si="16"/>
-        <v>7.4048000000000004E-3</v>
+        <v/>
       </c>
       <c r="L68" s="9">
         <f t="shared" si="17"/>
         <v>3.9925951999999998</v>
       </c>
-      <c r="M68" s="9" t="str">
+      <c r="M68" s="9">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N68" s="9">
+        <v>3.9925951999999998</v>
+      </c>
+      <c r="N68" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>3.9925951999999998</v>
-      </c>
-      <c r="O68" s="4"/>
+        <v/>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>1892</v>
+      </c>
       <c r="Q68" s="7" t="s">
         <v>1444</v>
       </c>
@@ -19278,9 +19283,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="W68">
+      <c r="W68" t="str">
         <f t="shared" si="22"/>
-        <v>7.4048000000000004E-3</v>
+        <v/>
       </c>
       <c r="X68" t="str">
         <f t="shared" si="23"/>
@@ -20527,27 +20532,32 @@
         <f t="shared" si="14"/>
         <v>7.5053999999999997E-3</v>
       </c>
-      <c r="J83" s="10" t="str">
+      <c r="J83" s="10">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K83" s="10">
+        <v>7.5053999999999997E-3</v>
+      </c>
+      <c r="K83" s="10" t="str">
         <f t="shared" si="16"/>
-        <v>7.5053999999999997E-3</v>
+        <v/>
       </c>
       <c r="L83" s="9">
         <f t="shared" si="17"/>
         <v>4.9924945999999997</v>
       </c>
-      <c r="M83" s="9" t="str">
+      <c r="M83" s="9">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N83" s="9">
+        <v>4.9924945999999997</v>
+      </c>
+      <c r="N83" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>4.9924945999999997</v>
-      </c>
-      <c r="O83" s="4"/>
+        <v/>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>1897</v>
+      </c>
       <c r="Q83" s="7" t="s">
         <v>1542</v>
       </c>
@@ -53594,7 +53604,7 @@
       </c>
       <c r="H86" s="64" t="str">
         <f>IF(VLOOKUP($G86,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G86,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I86" s="42" t="str">
         <f>VLOOKUP($G86,List!$A:$U,2,FALSE)</f>
@@ -54051,7 +54061,7 @@
       </c>
       <c r="H93" s="63" t="str">
         <f>IF(VLOOKUP($G93,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G93,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I93" s="47" t="str">
         <f>VLOOKUP($G93,List!$A:$U,2,FALSE)</f>
@@ -59527,7 +59537,7 @@
     <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
       <c r="I2" s="29">
         <f>K2/J2</f>
-        <v>0.62652267888687241</v>
+        <v>0.63841195040861798</v>
       </c>
       <c r="J2" s="28">
         <f>SUM(List!E:E)</f>
@@ -59535,11 +59545,11 @@
       </c>
       <c r="K2" s="27">
         <f>SUMIFS(List!$E:$E,List!$O:$O,"Y")</f>
-        <v>23160.099999999995</v>
+        <v>23599.599999999995</v>
       </c>
       <c r="L2" s="1">
         <f>COUNTIFS(List!O:O,"Y")</f>
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -61893,15 +61903,15 @@
       </c>
       <c r="X26" s="1" t="str" cm="1">
         <f t="array" ref="X26">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(9:9)),List!N:N,0))</f>
-        <v>Spanish Fly</v>
+        <v>Raja of the Rajput Reich</v>
       </c>
       <c r="Y26" s="15" t="str">
         <f>VLOOKUP($X26,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as Offaly, secure a Personal Union over an Iberian nation.</v>
+        <v>Conquer all of Germany as Nagaur.</v>
       </c>
       <c r="Z26" s="16">
         <f>VLOOKUP($X26,List!$A$1:$U$374,3,FALSE)</f>
-        <v>7.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AA26" s="17" t="str">
         <f>VLOOKUP($X26,List!$A$1:$U$374,4,FALSE)</f>
@@ -62000,11 +62010,11 @@
       </c>
       <c r="X27" s="1" t="str" cm="1">
         <f t="array" ref="X27">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(10:10)),List!N:N,0))</f>
-        <v>Raja of the Rajput Reich</v>
+        <v>The Animal Kingdom</v>
       </c>
       <c r="Y27" s="2" t="str">
         <f>VLOOKUP($X27,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Conquer all of Germany as Nagaur.</v>
+        <v>As Manipur, unite the Bengal region and convert it to Animism.</v>
       </c>
       <c r="Z27" s="3">
         <f>VLOOKUP($X27,List!$A$1:$U$374,3,FALSE)</f>
@@ -62080,11 +62090,11 @@
       </c>
       <c r="O28" s="14" t="str" cm="1">
         <f t="array" ref="O28">INDEX(List!A:A,MATCH(LARGE(List!M:M,ROW(11:11)),List!M:M,0))</f>
-        <v>Where the heart is</v>
+        <v>Spanish Fly</v>
       </c>
       <c r="P28" s="15" t="str">
         <f>VLOOKUP($O28,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Dahomey, force all non-Fetishist nations out of Niger and Sahel by 1500.</v>
+        <v>Starting as Offaly, secure a Personal Union over an Iberian nation.</v>
       </c>
       <c r="Q28" s="16">
         <f>VLOOKUP($O28,List!$A$1:$U$374,3,FALSE)</f>
@@ -62104,18 +62114,18 @@
       </c>
       <c r="U28" s="14" t="str">
         <f>IF(VLOOKUP($O28,List!$A$1:$U$374,16,FALSE)="","",VLOOKUP($O28,List!$A$1:$U$374,16,FALSE))</f>
-        <v>Dahomey</v>
+        <v>Offaly</v>
       </c>
       <c r="W28" s="14">
         <v>10</v>
       </c>
       <c r="X28" s="1" t="str" cm="1">
         <f t="array" ref="X28">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(11:11)),List!N:N,0))</f>
-        <v>The Animal Kingdom</v>
+        <v>Academical</v>
       </c>
       <c r="Y28" s="15" t="str">
         <f>VLOOKUP($X28,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Manipur, unite the Bengal region and convert it to Animism.</v>
+        <v>As Athens, own 50 universities.</v>
       </c>
       <c r="Z28" s="16">
         <f>VLOOKUP($X28,List!$A$1:$U$374,3,FALSE)</f>

--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22706E8A-8D9E-4BC8-B0F2-EC154A9F50FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCC77F9-5212-4397-8E4D-6107F92CF115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="17520" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="2057">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -8538,6 +8538,9 @@
   </si>
   <si>
     <t>Imerina</t>
+  </si>
+  <si>
+    <t>Oda</t>
   </si>
 </sst>
 </file>
@@ -13351,28 +13354,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
   <dimension ref="A1:Y374"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="10" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="14" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="9.140625" style="5" collapsed="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="28.140625" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="60.140625" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="43.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="28.140625" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="11.140625" customWidth="1"/>
-    <col min="22" max="23" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="5" collapsed="1"/>
+    <col min="16" max="16" width="14.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="28.109375" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="60.109375" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="43.33203125" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="28.109375" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="11.109375" customWidth="1"/>
+    <col min="22" max="23" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="11.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -13449,7 +13452,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>568</v>
       </c>
@@ -13537,7 +13540,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>564</v>
       </c>
@@ -13627,7 +13630,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>621</v>
       </c>
@@ -13710,7 +13713,7 @@
         <v>Legacy of Saint George</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>619</v>
       </c>
@@ -13800,7 +13803,7 @@
         <v>From Frankfurt to the Andes</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>239</v>
       </c>
@@ -13885,7 +13888,7 @@
         <v>Timurizz</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>561</v>
       </c>
@@ -13975,7 +13978,7 @@
         <v>Ultimate Military</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>531</v>
       </c>
@@ -14063,7 +14066,7 @@
         <v>Triple the Rome</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>566</v>
       </c>
@@ -14146,7 +14149,7 @@
         <v>The Zoro-Austrians</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>522</v>
       </c>
@@ -14231,7 +14234,7 @@
         <v>The Freest Man in the World</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>569</v>
       </c>
@@ -14314,7 +14317,7 @@
         <v>Baborg</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>456</v>
       </c>
@@ -14399,7 +14402,7 @@
         <v>Australia-Hungary</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>633</v>
       </c>
@@ -14482,7 +14485,7 @@
         <v>Mehmet's Ambition</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>432</v>
       </c>
@@ -14572,7 +14575,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>426</v>
       </c>
@@ -14660,7 +14663,7 @@
         <v>It's all coming together</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>291</v>
       </c>
@@ -14750,7 +14753,7 @@
         <v>Hanukkah Mutapa</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>622</v>
       </c>
@@ -14838,7 +14841,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>599</v>
       </c>
@@ -14928,7 +14931,7 @@
         <v>Quizquiz Pro Quo</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>620</v>
       </c>
@@ -15018,7 +15021,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>585</v>
       </c>
@@ -15108,7 +15111,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>618</v>
       </c>
@@ -15198,7 +15201,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -15288,7 +15291,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -15376,7 +15379,7 @@
         <v>Breadbasket of the World</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>567</v>
       </c>
@@ -15466,7 +15469,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>433</v>
       </c>
@@ -15556,7 +15559,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>496</v>
       </c>
@@ -15639,7 +15642,7 @@
         <v>One nation to rule them all</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>553</v>
       </c>
@@ -15724,7 +15727,7 @@
         <v>New, New Deli</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>483</v>
       </c>
@@ -15814,7 +15817,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>440</v>
       </c>
@@ -15904,7 +15907,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>451</v>
       </c>
@@ -15987,7 +15990,7 @@
         <v>Almost Prussian Blue</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>383</v>
       </c>
@@ -16077,7 +16080,7 @@
         <v>Where are the penguins?</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>430</v>
       </c>
@@ -16165,7 +16168,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>413</v>
       </c>
@@ -16198,27 +16201,32 @@
         <f t="shared" si="2"/>
         <v>4.3122000000000004E-3</v>
       </c>
-      <c r="J33" s="10" t="str">
+      <c r="J33" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K33" s="10">
+        <v>4.3122000000000004E-3</v>
+      </c>
+      <c r="K33" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>4.3122000000000004E-3</v>
+        <v/>
       </c>
       <c r="L33" s="9">
         <f t="shared" si="5"/>
         <v>2.9956877999999998</v>
       </c>
-      <c r="M33" s="9" t="str">
+      <c r="M33" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N33" s="9">
+        <v>2.9956877999999998</v>
+      </c>
+      <c r="N33" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>2.9956877999999998</v>
-      </c>
-      <c r="O33" s="4"/>
+        <v/>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>2056</v>
+      </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="7" t="s">
         <v>1419</v>
@@ -16231,9 +16239,9 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="V33">
+      <c r="V33" t="str">
         <f t="shared" si="9"/>
-        <v>4.3122000000000004E-3</v>
+        <v/>
       </c>
       <c r="W33" t="str">
         <f t="shared" si="10"/>
@@ -16248,7 +16256,7 @@
         <v>Stardust Crusaders</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>288</v>
       </c>
@@ -16338,7 +16346,7 @@
         <v>Golden Wind</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>387</v>
       </c>
@@ -16428,7 +16436,7 @@
         <v>Copium Wars</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>592</v>
       </c>
@@ -16518,7 +16526,7 @@
         <v>Inner Turmoil</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>574</v>
       </c>
@@ -16603,7 +16611,7 @@
         <v>I don't like sand</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>200</v>
       </c>
@@ -16686,7 +16694,7 @@
         <v>To the Bone</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -16771,7 +16779,7 @@
         <v>Surfing USA</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>557</v>
       </c>
@@ -16856,7 +16864,7 @@
         <v>The Pheasant Strut</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>624</v>
       </c>
@@ -16941,7 +16949,7 @@
         <v>Eat your Greens</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>390</v>
       </c>
@@ -17031,7 +17039,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>338</v>
       </c>
@@ -17121,7 +17129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>389</v>
       </c>
@@ -17209,7 +17217,7 @@
         <v>No Country for Old Tercios</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>431</v>
       </c>
@@ -17297,7 +17305,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>428</v>
       </c>
@@ -17380,7 +17388,7 @@
         <v>Doge Coins</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>208</v>
       </c>
@@ -17467,7 +17475,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>528</v>
       </c>
@@ -17550,7 +17558,7 @@
         <v>Why is the Rûm gone!?</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>555</v>
       </c>
@@ -17640,7 +17648,7 @@
         <v>The Fezzan Corridors</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>513</v>
       </c>
@@ -17730,7 +17738,7 @@
         <v>Stiff Upper Lippe</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>511</v>
       </c>
@@ -17815,7 +17823,7 @@
         <v>Stern des Südens</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>503</v>
       </c>
@@ -17848,27 +17856,32 @@
         <f t="shared" si="2"/>
         <v>6.4068000000000007E-3</v>
       </c>
-      <c r="J52" s="10" t="str">
+      <c r="J52" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K52" s="10">
+        <v>6.4068000000000007E-3</v>
+      </c>
+      <c r="K52" s="10" t="str">
         <f t="shared" si="4"/>
-        <v>6.4068000000000007E-3</v>
+        <v/>
       </c>
       <c r="L52" s="9">
         <f t="shared" si="5"/>
         <v>3.9935931999999998</v>
       </c>
-      <c r="M52" s="9" t="str">
+      <c r="M52" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N52" s="9">
+        <v>3.9935931999999998</v>
+      </c>
+      <c r="N52" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>3.9935931999999998</v>
-      </c>
-      <c r="O52" s="4"/>
+        <v/>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>1886</v>
+      </c>
       <c r="Q52" s="7" t="s">
         <v>1392</v>
       </c>
@@ -17887,9 +17900,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W52">
+      <c r="W52" t="str">
         <f t="shared" si="10"/>
-        <v>6.4068000000000007E-3</v>
+        <v/>
       </c>
       <c r="X52" t="str">
         <f t="shared" si="11"/>
@@ -17900,7 +17913,7 @@
         <v>Pick Your Poison</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>499</v>
       </c>
@@ -17983,7 +17996,7 @@
         <v>Pandya Empire</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>491</v>
       </c>
@@ -18073,7 +18086,7 @@
         <v>Mass Production</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>468</v>
       </c>
@@ -18163,7 +18176,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>463</v>
       </c>
@@ -18246,7 +18259,7 @@
         <v>Dovmont's Own</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>348</v>
       </c>
@@ -18336,7 +18349,7 @@
         <v>That's No Mon</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>412</v>
       </c>
@@ -18424,7 +18437,7 @@
         <v>Sun Invasion</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>253</v>
       </c>
@@ -18512,7 +18525,7 @@
         <v>Shemot is Not</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -18602,7 +18615,7 @@
         <v>Mansa Musa</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>424</v>
       </c>
@@ -18688,7 +18701,7 @@
         <v>King of Kings</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>265</v>
       </c>
@@ -18776,7 +18789,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
@@ -18861,7 +18874,7 @@
         <v>Imposter Syndrome</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>586</v>
       </c>
@@ -18944,7 +18957,7 @@
         <v>Empire of Mann</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>583</v>
       </c>
@@ -19036,7 +19049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>530</v>
       </c>
@@ -19121,7 +19134,7 @@
         <v>With a little help..</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>525</v>
       </c>
@@ -19206,7 +19219,7 @@
         <v>Turkish Delight</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>523</v>
       </c>
@@ -19296,7 +19309,7 @@
         <v>Tiger of Mysore</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>520</v>
       </c>
@@ -19379,7 +19392,7 @@
         <v>The 52 Garhs</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>515</v>
       </c>
@@ -19469,7 +19482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>506</v>
       </c>
@@ -19554,7 +19567,7 @@
         <v>Protect the Secret</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>543</v>
       </c>
@@ -19637,7 +19650,7 @@
         <v>Foremost Servitor of Jagannath</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>437</v>
       </c>
@@ -19720,7 +19733,7 @@
         <v>Core-fu</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>461</v>
       </c>
@@ -19805,7 +19818,7 @@
         <v>Bunte Kuh</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>535</v>
       </c>
@@ -19888,7 +19901,7 @@
         <v>Avar Khaganate</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>355</v>
       </c>
@@ -19978,7 +19991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>309</v>
       </c>
@@ -20011,27 +20024,32 @@
         <f t="shared" si="14"/>
         <v>7.3029000000000002E-3</v>
       </c>
-      <c r="J77" s="10" t="str">
+      <c r="J77" s="10">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K77" s="10">
+        <v>7.3029000000000002E-3</v>
+      </c>
+      <c r="K77" s="10" t="str">
         <f t="shared" si="16"/>
-        <v>7.3029000000000002E-3</v>
+        <v/>
       </c>
       <c r="L77" s="9">
         <f t="shared" si="17"/>
         <v>2.9926971</v>
       </c>
-      <c r="M77" s="9" t="str">
+      <c r="M77" s="9">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N77" s="9">
+        <v>2.9926971</v>
+      </c>
+      <c r="N77" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>2.9926971</v>
-      </c>
-      <c r="O77" s="4"/>
+        <v/>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>1896</v>
+      </c>
       <c r="Q77" s="7" t="s">
         <v>1139</v>
       </c>
@@ -20046,9 +20064,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="V77">
+      <c r="V77" t="str">
         <f t="shared" si="21"/>
-        <v>7.3029000000000002E-3</v>
+        <v/>
       </c>
       <c r="W77" t="str">
         <f t="shared" si="22"/>
@@ -20063,7 +20081,7 @@
         <v>Kuban Cigars</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>283</v>
       </c>
@@ -20148,7 +20166,7 @@
         <v>Ganges Khan</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>386</v>
       </c>
@@ -20236,7 +20254,7 @@
         <v>Brentry!</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>397</v>
       </c>
@@ -20324,7 +20342,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>103</v>
       </c>
@@ -20409,7 +20427,7 @@
         <v>Truly Good Maaaaa-tch</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>614</v>
       </c>
@@ -20499,7 +20517,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>608</v>
       </c>
@@ -20589,7 +20607,7 @@
         <v>Spanish Fly</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>591</v>
       </c>
@@ -20672,7 +20690,7 @@
         <v>Great Perm</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>584</v>
       </c>
@@ -20760,7 +20778,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>139</v>
       </c>
@@ -20845,7 +20863,7 @@
         <v>Forgive me, for I have Sindh</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>509</v>
       </c>
@@ -20935,7 +20953,7 @@
         <v>Spaghetti Western</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>501</v>
       </c>
@@ -21016,7 +21034,7 @@
         <v>Philippine Tiger</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>551</v>
       </c>
@@ -21104,7 +21122,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>549</v>
       </c>
@@ -21189,7 +21207,7 @@
         <v>Meissner Porcelain</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>443</v>
       </c>
@@ -21274,7 +21292,7 @@
         <v>Kushite Restoration</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>477</v>
       </c>
@@ -21362,7 +21380,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>475</v>
       </c>
@@ -21447,7 +21465,7 @@
         <v>Holy Horder</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>541</v>
       </c>
@@ -21537,7 +21555,7 @@
         <v>Cotton Kandy</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>435</v>
       </c>
@@ -21625,7 +21643,7 @@
         <v>Breaking the Yoke</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>380</v>
       </c>
@@ -21710,7 +21728,7 @@
         <v>Victorian Three</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>337</v>
       </c>
@@ -21800,7 +21818,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>319</v>
       </c>
@@ -21890,7 +21908,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>297</v>
       </c>
@@ -21973,7 +21991,7 @@
         <v>Home and Away</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>277</v>
       </c>
@@ -22063,7 +22081,7 @@
         <v>Don’t be Cilli</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>248</v>
       </c>
@@ -22153,7 +22171,7 @@
         <v>Disciples of Enlightenment</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>613</v>
       </c>
@@ -22243,7 +22261,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>575</v>
       </c>
@@ -22328,7 +22346,7 @@
         <v>The Animal Kingdom</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>602</v>
       </c>
@@ -22413,7 +22431,7 @@
         <v>Raja of the Rajput Reich</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>597</v>
       </c>
@@ -22498,7 +22516,7 @@
         <v>Norwegian Wood</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>581</v>
       </c>
@@ -22588,7 +22606,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>577</v>
       </c>
@@ -22671,7 +22689,7 @@
         <v>Academical</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>186</v>
       </c>
@@ -22761,7 +22779,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>507</v>
       </c>
@@ -22851,7 +22869,7 @@
         <v>Sailor Mon</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>488</v>
       </c>
@@ -22936,7 +22954,7 @@
         <v>Lucky Lucca</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>547</v>
       </c>
@@ -23026,7 +23044,7 @@
         <v>Komnenoi Empire</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
@@ -23114,7 +23132,7 @@
         <v>Kinslayer</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>631</v>
       </c>
@@ -23199,7 +23217,7 @@
         <v>True Heir of Timur</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>629</v>
       </c>
@@ -23289,7 +23307,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>295</v>
       </c>
@@ -23374,7 +23392,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>404</v>
       </c>
@@ -23462,7 +23480,7 @@
         <v>For the Emperor!</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>571</v>
       </c>
@@ -23550,7 +23568,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>601</v>
       </c>
@@ -23635,7 +23653,7 @@
         <v>Rags and Riches</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>589</v>
       </c>
@@ -23720,7 +23738,7 @@
         <v>Gothic Invasion</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>170</v>
       </c>
@@ -23810,7 +23828,7 @@
         <v>On the Edge of Madness</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>215</v>
       </c>
@@ -23897,7 +23915,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>495</v>
       </c>
@@ -23985,7 +24003,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>420</v>
       </c>
@@ -24077,7 +24095,7 @@
         <v>Yarr Harr a Pirate's Life For Me</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>346</v>
       </c>
@@ -24165,7 +24183,7 @@
         <v>Tatarstan</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>334</v>
       </c>
@@ -24253,7 +24271,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -24340,7 +24358,7 @@
         <v>Rekindling the Flames</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>327</v>
       </c>
@@ -24423,7 +24441,7 @@
         <v>No Trail of Tears</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>423</v>
       </c>
@@ -24513,7 +24531,7 @@
         <v>First Come, First Serve</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>99</v>
       </c>
@@ -24600,7 +24618,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>611</v>
       </c>
@@ -24690,7 +24708,7 @@
         <v>The Buddhists Strike Back</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>595</v>
       </c>
@@ -24776,7 +24794,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>593</v>
       </c>
@@ -24866,7 +24884,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>588</v>
       </c>
@@ -24956,7 +24974,7 @@
         <v>Frozen Assets</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>579</v>
       </c>
@@ -25044,7 +25062,7 @@
         <v>Albania or Iberia</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>199</v>
       </c>
@@ -25129,7 +25147,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>235</v>
       </c>
@@ -25221,7 +25239,7 @@
         <v>Østindisk Kompagni Te</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>128</v>
       </c>
@@ -25306,7 +25324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>119</v>
       </c>
@@ -25394,7 +25412,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>527</v>
       </c>
@@ -25484,7 +25502,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>466</v>
       </c>
@@ -25574,7 +25592,7 @@
         <v>Emperor of Hindustan</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>540</v>
       </c>
@@ -25659,7 +25677,7 @@
         <v>Choson One</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>458</v>
       </c>
@@ -25747,7 +25765,7 @@
         <v>Back to the Piast</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>258</v>
       </c>
@@ -25830,7 +25848,7 @@
         <v>Turn the Table</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>366</v>
       </c>
@@ -25920,7 +25938,7 @@
         <v>The Sudanese Expedition</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>610</v>
       </c>
@@ -26010,7 +26028,7 @@
         <v>Sunset Invasion</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>604</v>
       </c>
@@ -26100,7 +26118,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>126</v>
       </c>
@@ -26192,7 +26210,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>121</v>
       </c>
@@ -26282,7 +26300,7 @@
         <v>Brick by Brick</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>565</v>
       </c>
@@ -26372,7 +26390,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>516</v>
       </c>
@@ -26460,7 +26478,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>445</v>
       </c>
@@ -26545,7 +26563,7 @@
         <v>Rise of the White Sheep</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>563</v>
       </c>
@@ -26633,7 +26651,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>444</v>
       </c>
@@ -26721,7 +26739,7 @@
         <v>Lessons of Hemmingstedt</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>484</v>
       </c>
@@ -26804,7 +26822,7 @@
         <v>Lazarus</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>479</v>
       </c>
@@ -26892,7 +26910,7 @@
         <v>Keep the Flame Burning</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -26980,7 +26998,7 @@
         <v>Auld Alliance Reversed</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>378</v>
       </c>
@@ -27070,7 +27088,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>362</v>
       </c>
@@ -27160,7 +27178,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>321</v>
       </c>
@@ -27248,7 +27266,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>289</v>
       </c>
@@ -27331,7 +27349,7 @@
         <v>Great Moravia</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>287</v>
       </c>
@@ -27416,7 +27434,7 @@
         <v>Golden Horn</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>83</v>
       </c>
@@ -27499,7 +27517,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>184</v>
       </c>
@@ -27584,7 +27602,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -27674,7 +27692,7 @@
         <v>Holy Trinity</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>471</v>
       </c>
@@ -27764,7 +27782,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>439</v>
       </c>
@@ -27856,7 +27874,7 @@
         <v>For Odin!</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>465</v>
       </c>
@@ -27946,7 +27964,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>533</v>
       </c>
@@ -28036,7 +28054,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>449</v>
       </c>
@@ -28121,7 +28139,7 @@
         <v>A Hero’s Welcome</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>627</v>
       </c>
@@ -28204,7 +28222,7 @@
         <v>One Faith</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>372</v>
       </c>
@@ -28287,7 +28305,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>418</v>
       </c>
@@ -28377,7 +28395,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>328</v>
       </c>
@@ -28460,7 +28478,7 @@
         <v>Parisian Pasha</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>317</v>
       </c>
@@ -28550,7 +28568,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>293</v>
       </c>
@@ -28638,7 +28656,7 @@
         <v>Hessian Mercenaries</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>267</v>
       </c>
@@ -28728,7 +28746,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>24</v>
       </c>
@@ -28815,7 +28833,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -28900,7 +28918,7 @@
         <v>Rozwi Empire</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
@@ -28990,7 +29008,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>154</v>
       </c>
@@ -29080,7 +29098,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>556</v>
       </c>
@@ -29170,7 +29188,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>419</v>
       </c>
@@ -29262,7 +29280,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>350</v>
       </c>
@@ -29350,7 +29368,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>336</v>
       </c>
@@ -29433,7 +29451,7 @@
         <v>Sons of Carthage</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>243</v>
       </c>
@@ -29523,7 +29541,7 @@
         <v>Abu Bakr II’s Ambition</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>214</v>
       </c>
@@ -29613,7 +29631,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -29698,7 +29716,7 @@
         <v>The Uncommonwealth</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>361</v>
       </c>
@@ -29788,7 +29806,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>357</v>
       </c>
@@ -29878,7 +29896,7 @@
         <v>The Levant Turnabout</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>352</v>
       </c>
@@ -29966,7 +29984,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>254</v>
       </c>
@@ -30049,7 +30067,7 @@
         <v>Sweet Home Qaraqorum</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>405</v>
       </c>
@@ -30139,7 +30157,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>299</v>
       </c>
@@ -30231,7 +30249,7 @@
         <v>Ideas Guy</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>269</v>
       </c>
@@ -30314,7 +30332,7 @@
         <v>Bengal Tiger</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>260</v>
       </c>
@@ -30406,7 +30424,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>161</v>
       </c>
@@ -30496,7 +30514,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>152</v>
       </c>
@@ -30586,7 +30604,7 @@
         <v>Kow-Tow</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>370</v>
       </c>
@@ -30674,7 +30692,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>422</v>
       </c>
@@ -30764,7 +30782,7 @@
         <v>A Sun God</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>469</v>
       </c>
@@ -30856,7 +30874,7 @@
         <v>Forever Golden</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>344</v>
       </c>
@@ -30946,7 +30964,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>342</v>
       </c>
@@ -31036,7 +31054,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>308</v>
       </c>
@@ -31126,7 +31144,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>398</v>
       </c>
@@ -31214,7 +31232,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>59</v>
       </c>
@@ -31299,7 +31317,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>221</v>
       </c>
@@ -31389,7 +31407,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>176</v>
       </c>
@@ -31472,7 +31490,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>157</v>
       </c>
@@ -31562,7 +31580,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>147</v>
       </c>
@@ -31652,7 +31670,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>117</v>
       </c>
@@ -31737,7 +31755,7 @@
         <v>Baa Baa Black Sheep</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>558</v>
       </c>
@@ -31827,7 +31845,7 @@
         <v>The Re-Reconquista</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>480</v>
       </c>
@@ -31917,7 +31935,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>545</v>
       </c>
@@ -32005,7 +32023,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>452</v>
       </c>
@@ -32097,7 +32115,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>359</v>
       </c>
@@ -32187,7 +32205,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>353</v>
       </c>
@@ -32275,7 +32293,7 @@
         <v>The Iron Price</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>36</v>
       </c>
@@ -32363,7 +32381,7 @@
         <v>Krabater</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>146</v>
       </c>
@@ -32453,7 +32471,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>560</v>
       </c>
@@ -32541,7 +32559,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>505</v>
       </c>
@@ -32631,7 +32649,7 @@
         <v>Prester John</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>460</v>
       </c>
@@ -32721,7 +32739,7 @@
         <v>Baltic Crusader</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>411</v>
       </c>
@@ -32806,7 +32824,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>333</v>
       </c>
@@ -32894,7 +32912,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>330</v>
       </c>
@@ -32984,7 +33002,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>402</v>
       </c>
@@ -33074,7 +33092,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>486</v>
       </c>
@@ -33164,7 +33182,7 @@
         <v>Luck of the Irish</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>441</v>
       </c>
@@ -33252,7 +33270,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>538</v>
       </c>
@@ -33342,7 +33360,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>93</v>
       </c>
@@ -33432,7 +33450,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>616</v>
       </c>
@@ -33522,7 +33540,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
@@ -33608,7 +33626,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>400</v>
       </c>
@@ -33696,7 +33714,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -33784,7 +33802,7 @@
         <v>A Blessed Nation</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>240</v>
       </c>
@@ -33874,7 +33892,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>279</v>
       </c>
@@ -33962,7 +33980,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>164</v>
       </c>
@@ -34050,7 +34068,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>312</v>
       </c>
@@ -34135,7 +34153,7 @@
         <v>Lion of the North</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>518</v>
       </c>
@@ -34223,7 +34241,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>310</v>
       </c>
@@ -34311,7 +34329,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>606</v>
       </c>
@@ -34401,7 +34419,7 @@
         <v>Shahanshah</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>473</v>
       </c>
@@ -34484,7 +34502,7 @@
         <v>Guarantor of Peace</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>409</v>
       </c>
@@ -34574,7 +34592,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>251</v>
       </c>
@@ -34664,7 +34682,7 @@
         <v>Relentless Push East</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>306</v>
       </c>
@@ -34752,7 +34770,7 @@
         <v>Kingdom of God</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>273</v>
       </c>
@@ -34840,7 +34858,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>97</v>
       </c>
@@ -34923,7 +34941,7 @@
         <v>Poland can into space</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>22</v>
       </c>
@@ -35015,7 +35033,7 @@
         <v>Foul Mouthed</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>143</v>
       </c>
@@ -35105,7 +35123,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>104</v>
       </c>
@@ -35195,7 +35213,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>263</v>
       </c>
@@ -35283,7 +35301,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>166</v>
       </c>
@@ -35371,7 +35389,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>112</v>
       </c>
@@ -35457,7 +35475,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>285</v>
       </c>
@@ -35547,7 +35565,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>168</v>
       </c>
@@ -35637,7 +35655,7 @@
         <v>Nobody wants to die</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>493</v>
       </c>
@@ -35722,7 +35740,7 @@
         <v>Master of India</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>231</v>
       </c>
@@ -35808,7 +35826,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>340</v>
       </c>
@@ -35896,7 +35914,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>202</v>
       </c>
@@ -35986,7 +36004,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>196</v>
       </c>
@@ -36074,7 +36092,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>364</v>
       </c>
@@ -36164,7 +36182,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>275</v>
       </c>
@@ -36247,7 +36265,7 @@
         <v>Definitely the Sultan of Rum</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>48</v>
       </c>
@@ -36335,7 +36353,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>497</v>
       </c>
@@ -36423,7 +36441,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>209</v>
       </c>
@@ -36506,7 +36524,7 @@
         <v>Winged Hussars</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>173</v>
       </c>
@@ -36589,7 +36607,7 @@
         <v>One King to Rule!</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>490</v>
       </c>
@@ -36679,7 +36697,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>256</v>
       </c>
@@ -36762,7 +36780,7 @@
         <v>The Spice Must Flow</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>259</v>
       </c>
@@ -36845,7 +36863,7 @@
         <v>A tale of two Families</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>129</v>
       </c>
@@ -36933,7 +36951,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>416</v>
       </c>
@@ -37021,7 +37039,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>393</v>
       </c>
@@ -37111,7 +37129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>34</v>
       </c>
@@ -37196,7 +37214,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>373</v>
       </c>
@@ -37284,7 +37302,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>325</v>
       </c>
@@ -37372,7 +37390,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>247</v>
       </c>
@@ -37460,7 +37478,7 @@
         <v>Black Jack</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>1677</v>
       </c>
@@ -37550,7 +37568,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>210</v>
       </c>
@@ -37640,7 +37658,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>190</v>
       </c>
@@ -37732,7 +37750,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>106</v>
       </c>
@@ -37822,7 +37840,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>130</v>
       </c>
@@ -37905,7 +37923,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>537</v>
       </c>
@@ -37993,7 +38011,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>381</v>
       </c>
@@ -38081,7 +38099,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>13</v>
       </c>
@@ -38171,7 +38189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>38</v>
       </c>
@@ -38259,7 +38277,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>148</v>
       </c>
@@ -38347,7 +38365,7 @@
         <v>Imperio español</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>384</v>
       </c>
@@ -38437,7 +38455,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>204</v>
       </c>
@@ -38525,7 +38543,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>300</v>
       </c>
@@ -38615,7 +38633,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>89</v>
       </c>
@@ -38703,7 +38721,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>376</v>
       </c>
@@ -38788,7 +38806,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>124</v>
       </c>
@@ -38876,7 +38894,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>144</v>
       </c>
@@ -38964,7 +38982,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>233</v>
       </c>
@@ -39052,7 +39070,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>229</v>
       </c>
@@ -39140,7 +39158,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>414</v>
       </c>
@@ -39230,7 +39248,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>391</v>
       </c>
@@ -39315,7 +39333,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>3</v>
       </c>
@@ -39403,7 +39421,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>63</v>
       </c>
@@ -39490,7 +39508,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>304</v>
       </c>
@@ -39580,7 +39598,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>281</v>
       </c>
@@ -39672,7 +39690,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>101</v>
       </c>
@@ -39757,7 +39775,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>25</v>
       </c>
@@ -39845,7 +39863,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>141</v>
       </c>
@@ -39933,7 +39951,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>133</v>
       </c>
@@ -40020,7 +40038,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>395</v>
       </c>
@@ -40106,7 +40124,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>40</v>
       </c>
@@ -40196,7 +40214,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>212</v>
       </c>
@@ -40284,7 +40302,7 @@
         <v>A Fine Goosestep</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>323</v>
       </c>
@@ -40374,7 +40392,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>137</v>
       </c>
@@ -40464,7 +40482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>250</v>
       </c>
@@ -40554,7 +40572,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>108</v>
       </c>
@@ -40642,7 +40660,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>223</v>
       </c>
@@ -40732,7 +40750,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>159</v>
       </c>
@@ -40820,7 +40838,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>175</v>
       </c>
@@ -40908,7 +40926,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>163</v>
       </c>
@@ -40998,7 +41016,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>262</v>
       </c>
@@ -41086,7 +41104,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>95</v>
       </c>
@@ -41174,7 +41192,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>49</v>
       </c>
@@ -41264,7 +41282,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>5</v>
       </c>
@@ -41354,7 +41372,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>313</v>
       </c>
@@ -41439,7 +41457,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>85</v>
       </c>
@@ -41527,7 +41545,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>271</v>
       </c>
@@ -41615,7 +41633,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>172</v>
       </c>
@@ -41703,7 +41721,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>75</v>
       </c>
@@ -41788,7 +41806,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>227</v>
       </c>
@@ -41878,7 +41896,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>42</v>
       </c>
@@ -41968,7 +41986,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>206</v>
       </c>
@@ -42056,7 +42074,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>203</v>
       </c>
@@ -42146,7 +42164,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>302</v>
       </c>
@@ -42234,7 +42252,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>135</v>
       </c>
@@ -42321,7 +42339,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>219</v>
       </c>
@@ -42409,7 +42427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>57</v>
       </c>
@@ -42497,7 +42515,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>110</v>
       </c>
@@ -42587,7 +42605,7 @@
         <v>All belongs to Mother Russia</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>87</v>
       </c>
@@ -42673,7 +42691,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>113</v>
       </c>
@@ -42763,7 +42781,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>18</v>
       </c>
@@ -42846,7 +42864,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>65</v>
       </c>
@@ -42934,7 +42952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>315</v>
       </c>
@@ -43022,7 +43040,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>192</v>
       </c>
@@ -43112,7 +43130,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>30</v>
       </c>
@@ -43202,7 +43220,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>61</v>
       </c>
@@ -43290,7 +43308,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>122</v>
       </c>
@@ -43379,7 +43397,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>194</v>
       </c>
@@ -43465,7 +43483,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>0</v>
       </c>
@@ -43552,7 +43570,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>81</v>
       </c>
@@ -43640,7 +43658,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>131</v>
       </c>
@@ -43728,7 +43746,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>225</v>
       </c>
@@ -43813,7 +43831,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>115</v>
       </c>
@@ -43903,7 +43921,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>245</v>
       </c>
@@ -43988,7 +44006,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>7</v>
       </c>
@@ -44073,7 +44091,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>217</v>
       </c>
@@ -44158,7 +44176,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>374</v>
       </c>
@@ -44241,7 +44259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>180</v>
       </c>
@@ -44326,7 +44344,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>16</v>
       </c>
@@ -44416,7 +44434,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>44</v>
       </c>
@@ -44499,7 +44517,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>27</v>
       </c>
@@ -44586,7 +44604,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>77</v>
       </c>
@@ -44671,7 +44689,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>69</v>
       </c>
@@ -44758,7 +44776,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -44845,7 +44863,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>150</v>
       </c>
@@ -44930,7 +44948,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>91</v>
       </c>
@@ -45015,7 +45033,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>198</v>
       </c>
@@ -45105,7 +45123,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>14</v>
       </c>
@@ -45192,7 +45210,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>32</v>
       </c>
@@ -45277,7 +45295,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>67</v>
       </c>
@@ -45364,7 +45382,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -45449,7 +45467,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>20</v>
       </c>
@@ -45534,7 +45552,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>55</v>
       </c>
@@ -45619,7 +45637,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>46</v>
       </c>
@@ -45702,7 +45720,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>79</v>
       </c>
@@ -45785,7 +45803,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>51</v>
       </c>
@@ -45868,7 +45886,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>53</v>
       </c>
@@ -45955,7 +45973,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>73</v>
       </c>
@@ -46040,7 +46058,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>71</v>
       </c>
@@ -46207,17 +46225,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16ACCB4E-C812-42E5-BA87-3FBA0B83A629}">
   <dimension ref="A1:F116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="125.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.44140625" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="125.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1747</v>
       </c>
@@ -46237,7 +46255,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>1713</v>
       </c>
@@ -46246,7 +46264,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>1714</v>
       </c>
@@ -46260,7 +46278,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
         <v>1715</v>
       </c>
@@ -46268,7 +46286,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
         <v>1748</v>
       </c>
@@ -46276,7 +46294,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
         <v>1716</v>
       </c>
@@ -46284,7 +46302,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
         <v>1749</v>
       </c>
@@ -46292,7 +46310,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
         <v>1717</v>
       </c>
@@ -46306,7 +46324,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
         <v>1675</v>
       </c>
@@ -46320,7 +46338,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="35" t="s">
         <v>1750</v>
       </c>
@@ -46334,7 +46352,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
         <v>1718</v>
       </c>
@@ -46342,7 +46360,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="35" t="s">
         <v>1719</v>
       </c>
@@ -46350,7 +46368,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
         <v>1751</v>
       </c>
@@ -46358,7 +46376,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
         <v>1752</v>
       </c>
@@ -46366,7 +46384,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
         <v>1689</v>
       </c>
@@ -46374,7 +46392,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>1720</v>
       </c>
@@ -46382,7 +46400,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="s">
         <v>1721</v>
       </c>
@@ -46396,7 +46414,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="35" t="s">
         <v>1753</v>
       </c>
@@ -46410,7 +46428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="35" t="s">
         <v>1754</v>
       </c>
@@ -46424,7 +46442,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
         <v>1755</v>
       </c>
@@ -46432,7 +46450,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
         <v>1756</v>
       </c>
@@ -46440,7 +46458,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="35" t="s">
         <v>1757</v>
       </c>
@@ -46454,7 +46472,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
         <v>1758</v>
       </c>
@@ -46468,7 +46486,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>1759</v>
       </c>
@@ -46476,7 +46494,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
         <v>1684</v>
       </c>
@@ -46490,7 +46508,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="35" t="s">
         <v>1722</v>
       </c>
@@ -46504,7 +46522,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
         <v>1826</v>
       </c>
@@ -46518,7 +46536,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
         <v>1676</v>
       </c>
@@ -46526,7 +46544,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="35" t="s">
         <v>1760</v>
       </c>
@@ -46534,7 +46552,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>756</v>
       </c>
@@ -46548,7 +46566,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
         <v>1723</v>
       </c>
@@ -46562,7 +46580,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="35" t="s">
         <v>1761</v>
       </c>
@@ -46570,7 +46588,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
         <v>1724</v>
       </c>
@@ -46578,7 +46596,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
         <v>289</v>
       </c>
@@ -46592,7 +46610,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="35" t="s">
         <v>1762</v>
       </c>
@@ -46600,7 +46618,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="35" t="s">
         <v>1763</v>
       </c>
@@ -46608,7 +46626,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
         <v>1764</v>
       </c>
@@ -46616,7 +46634,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>1765</v>
       </c>
@@ -46624,7 +46642,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
         <v>1725</v>
       </c>
@@ -46632,7 +46650,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="35" t="s">
         <v>1726</v>
       </c>
@@ -46640,7 +46658,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="35" t="s">
         <v>1710</v>
       </c>
@@ -46648,7 +46666,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
         <v>1766</v>
       </c>
@@ -46656,7 +46674,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
         <v>1767</v>
       </c>
@@ -46664,7 +46682,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
         <v>1768</v>
       </c>
@@ -46684,7 +46702,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
         <v>1769</v>
       </c>
@@ -46692,7 +46710,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
         <v>1770</v>
       </c>
@@ -46700,7 +46718,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>1727</v>
       </c>
@@ -46708,7 +46726,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
         <v>1728</v>
       </c>
@@ -46722,7 +46740,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
         <v>1771</v>
       </c>
@@ -46730,7 +46748,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="35" t="s">
         <v>1772</v>
       </c>
@@ -46738,7 +46756,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="35" t="s">
         <v>765</v>
       </c>
@@ -46746,7 +46764,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="35" t="s">
         <v>1773</v>
       </c>
@@ -46754,7 +46772,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
         <v>1777</v>
       </c>
@@ -46762,7 +46780,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
         <v>1774</v>
       </c>
@@ -46770,7 +46788,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
         <v>1775</v>
       </c>
@@ -46778,7 +46796,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>1776</v>
       </c>
@@ -46792,7 +46810,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>1729</v>
       </c>
@@ -46800,7 +46818,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="35" t="s">
         <v>1778</v>
       </c>
@@ -46808,7 +46826,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="35" t="s">
         <v>1779</v>
       </c>
@@ -46816,7 +46834,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="35" t="s">
         <v>1780</v>
       </c>
@@ -46830,7 +46848,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A61" s="35" t="s">
         <v>1781</v>
       </c>
@@ -46844,7 +46862,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="35" t="s">
         <v>1782</v>
       </c>
@@ -46864,7 +46882,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="35" t="s">
         <v>1783</v>
       </c>
@@ -46872,7 +46890,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="35" t="s">
         <v>1784</v>
       </c>
@@ -46880,7 +46898,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="35" t="s">
         <v>1785</v>
       </c>
@@ -46888,7 +46906,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="35" t="s">
         <v>1730</v>
       </c>
@@ -46902,7 +46920,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="35" t="s">
         <v>1731</v>
       </c>
@@ -46910,7 +46928,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="35" t="s">
         <v>1732</v>
       </c>
@@ -46924,7 +46942,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="35" t="s">
         <v>1786</v>
       </c>
@@ -46938,7 +46956,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="35" t="s">
         <v>1787</v>
       </c>
@@ -46946,7 +46964,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A71" s="35" t="s">
         <v>1733</v>
       </c>
@@ -46966,7 +46984,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="35" t="s">
         <v>1788</v>
       </c>
@@ -46974,7 +46992,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="35" t="s">
         <v>1789</v>
       </c>
@@ -46988,7 +47006,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="35" t="s">
         <v>1790</v>
       </c>
@@ -46996,7 +47014,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="35" t="s">
         <v>1791</v>
       </c>
@@ -47004,7 +47022,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="35" t="s">
         <v>1792</v>
       </c>
@@ -47012,7 +47030,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
         <v>1734</v>
       </c>
@@ -47032,7 +47050,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="35" t="s">
         <v>1735</v>
       </c>
@@ -47052,7 +47070,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A79" s="35" t="s">
         <v>1793</v>
       </c>
@@ -47066,7 +47084,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="35" t="s">
         <v>1794</v>
       </c>
@@ -47074,7 +47092,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A81" s="35" t="s">
         <v>1795</v>
       </c>
@@ -47088,7 +47106,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="35" t="s">
         <v>1796</v>
       </c>
@@ -47102,7 +47120,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="35" t="s">
         <v>1736</v>
       </c>
@@ -47110,7 +47128,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="35" t="s">
         <v>1797</v>
       </c>
@@ -47118,7 +47136,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="35" t="s">
         <v>1737</v>
       </c>
@@ -47126,7 +47144,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="35" t="s">
         <v>1798</v>
       </c>
@@ -47134,7 +47152,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="35" t="s">
         <v>182</v>
       </c>
@@ -47142,7 +47160,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A88" s="35" t="s">
         <v>1738</v>
       </c>
@@ -47162,7 +47180,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="35" t="s">
         <v>1739</v>
       </c>
@@ -47182,7 +47200,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="35" t="s">
         <v>1799</v>
       </c>
@@ -47190,7 +47208,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="35" t="s">
         <v>1800</v>
       </c>
@@ -47198,7 +47216,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="35" t="s">
         <v>1801</v>
       </c>
@@ -47206,7 +47224,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="35" t="s">
         <v>1740</v>
       </c>
@@ -47214,7 +47232,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="35" t="s">
         <v>1802</v>
       </c>
@@ -47228,7 +47246,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="35" t="s">
         <v>1803</v>
       </c>
@@ -47236,7 +47254,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="35" t="s">
         <v>1804</v>
       </c>
@@ -47244,7 +47262,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="35" t="s">
         <v>1805</v>
       </c>
@@ -47252,7 +47270,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
         <v>1806</v>
       </c>
@@ -47260,7 +47278,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="35" t="s">
         <v>1807</v>
       </c>
@@ -47268,7 +47286,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
         <v>1741</v>
       </c>
@@ -47282,7 +47300,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="35" t="s">
         <v>1808</v>
       </c>
@@ -47290,7 +47308,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="35" t="s">
         <v>764</v>
       </c>
@@ -47298,7 +47316,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="35" t="s">
         <v>1742</v>
       </c>
@@ -47306,7 +47324,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A104" s="35" t="s">
         <v>1743</v>
       </c>
@@ -47320,7 +47338,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="35" t="s">
         <v>1809</v>
       </c>
@@ -47328,7 +47346,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="35" t="s">
         <v>1810</v>
       </c>
@@ -47342,7 +47360,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="35" t="s">
         <v>1811</v>
       </c>
@@ -47350,7 +47368,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="35" t="s">
         <v>1812</v>
       </c>
@@ -47364,7 +47382,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="35" t="s">
         <v>1813</v>
       </c>
@@ -47372,7 +47390,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="35" t="s">
         <v>1814</v>
       </c>
@@ -47380,7 +47398,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="35" t="s">
         <v>1744</v>
       </c>
@@ -47396,7 +47414,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="35" t="s">
         <v>1815</v>
       </c>
@@ -47404,7 +47422,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="35" t="s">
         <v>1816</v>
       </c>
@@ -47412,7 +47430,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="35" t="s">
         <v>1817</v>
       </c>
@@ -47426,7 +47444,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="35" t="s">
         <v>1745</v>
       </c>
@@ -47434,7 +47452,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="35" t="s">
         <v>1746</v>
       </c>
@@ -47799,26 +47817,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB4F934-B5CD-4C00-8D57-A5021FDDF4F5}">
   <dimension ref="A1:P153"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" style="66" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="31.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="58" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="28.140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="34.42578125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="60.140625" customWidth="1"/>
-    <col min="16" max="16" width="63.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="58" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="28.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="34.44140625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="60.109375" customWidth="1"/>
+    <col min="16" max="16" width="63.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="37" t="s">
         <v>1856</v>
       </c>
@@ -47868,7 +47886,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
         <v>2044</v>
       </c>
@@ -47922,7 +47940,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>2031</v>
       </c>
@@ -47988,7 +48006,7 @@
 mission Ratify the Kalmar Union while having the reform Kalmar Union.</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48051,7 +48069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48115,7 +48133,7 @@
 Asia. Then form a claim in Ayutthaya or wait for Mingsplosion.</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48190,7 +48208,7 @@
 - Switching to play as a released vassal will invalidate the achievement.</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48291,7 +48309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48361,7 +48379,7 @@
 pretty easy without it.</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48432,7 +48450,7 @@
 the Siberian ports has already been cored or fully colonized.</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48493,7 +48511,7 @@
         <v>Easiest to do as Muscovy.</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48566,7 +48584,7 @@
 Sea ̦; it can be counterbalanced by building lots of light ships.</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48634,7 +48652,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48696,7 +48714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48760,7 +48778,7 @@
 modifier. This will deter nearby attackers as you expand opportunistically.</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48822,7 +48840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48896,7 +48914,7 @@
 Rekindling the Flames.</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="39" t="s">
         <v>2036</v>
       </c>
@@ -48968,7 +48986,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
         <v>2036</v>
       </c>
@@ -49039,7 +49057,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45" t="s">
         <v>2036</v>
       </c>
@@ -49106,7 +49124,7 @@
 scornfully insult 10 of Lithuania's 11 neighbours.</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49173,7 +49191,7 @@
 to that number later.</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49245,7 +49263,7 @@
 aspect.</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49318,7 +49336,7 @@
 colonize yourself.</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49385,7 +49403,7 @@
 possible to get the achievement without that DLC.</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49448,7 +49466,7 @@
 colonizing the NA lands may result in their capital being in NA.</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49512,7 +49530,7 @@
 partnered with The Buddhists Strike Back.</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49579,7 +49597,7 @@
 playing as Kandy, you'll likely also get the achievement Cotton Kandy.</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>2040</v>
       </c>
@@ -49643,7 +49661,7 @@
 be achieved even without the DLC.</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>2041</v>
       </c>
@@ -49708,7 +49726,7 @@
 these will immediately make you an empire.</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>2043</v>
       </c>
@@ -49773,7 +49791,7 @@
 Philippine islands are an excellent place to start forcing conversions.</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="39" t="s">
         <v>2042</v>
       </c>
@@ -49855,7 +49873,7 @@
 Emperor.</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="39" t="s">
         <v>1920</v>
       </c>
@@ -49918,7 +49936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="45" t="s">
         <v>1921</v>
       </c>
@@ -49990,7 +50008,7 @@
 Secretive personality which gives *+20%* foreign spy detection.</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39" t="s">
         <v>1922</v>
       </c>
@@ -50057,7 +50075,7 @@
 provinces by calling them to war as ally before subjugating them.</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="39" t="s">
         <v>1922</v>
       </c>
@@ -50122,7 +50140,7 @@
 the province sooner.</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50187,7 +50205,7 @@
 map which can't be earned by playing that custom nation.</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50255,7 +50273,7 @@
 to protect them while you improve relations.</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50321,7 +50339,7 @@
 releasing client states.</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50390,7 +50408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50452,7 +50470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50519,7 +50537,7 @@
 Aragon.</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50589,7 +50607,7 @@
 does not change your missions).</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50652,7 +50670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50722,7 +50740,7 @@
 animist) after hitting 95 doom will also not prevent the achievement.</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50794,7 +50812,7 @@
 take capitals without the need of conquering a lot of adjacent provinces.</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50865,7 +50883,7 @@
 you can finish, it may be easier to allow a colonial nation to form.</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50945,7 +50963,7 @@
 rapidly across the continent at the cost of diplomatic power.</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="45" t="s">
         <v>2047</v>
       </c>
@@ -51011,7 +51029,7 @@
 economy of Spain.</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="39" t="s">
         <v>1928</v>
       </c>
@@ -51083,7 +51101,7 @@
 country will count for the achievement.</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="45" t="s">
         <v>1929</v>
       </c>
@@ -51155,7 +51173,7 @@
 Ethiopia and nations lying in the way to the jewish provinces.</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51224,7 +51242,7 @@
 can culture convert their original provinces to a new culture.</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51289,7 +51307,7 @@
 in this way.</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="45" t="s">
         <v>1931</v>
       </c>
@@ -51355,7 +51373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="39" t="s">
         <v>2053</v>
       </c>
@@ -51422,7 +51440,7 @@
 due to the unique government reform.</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51486,7 +51504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51559,7 +51577,7 @@
 Sacraments” (*+2.5%*)</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51629,7 +51647,7 @@
 declines the PU is also a viable strategy.</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="45" t="s">
         <v>1933</v>
       </c>
@@ -51694,7 +51712,7 @@
 suffice.</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="39" t="s">
         <v>1934</v>
       </c>
@@ -51764,7 +51782,7 @@
 new capital.</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="45" t="s">
         <v>1935</v>
       </c>
@@ -51841,7 +51859,7 @@
 two are owned by Mali and one by Kong.</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51907,7 +51925,7 @@
 European majors for fighting the Turks.</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51970,7 +51988,7 @@
 religion by rebels.</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="45" t="s">
         <v>1937</v>
       </c>
@@ -52043,7 +52061,7 @@
 Africa. The provinces do not need to be cored.</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="39" t="s">
         <v>1938</v>
       </c>
@@ -52108,7 +52126,7 @@
 Valencia.</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="45" t="s">
         <v>1939</v>
       </c>
@@ -52174,7 +52192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="39" t="s">
         <v>1940</v>
       </c>
@@ -52236,7 +52254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="39" t="s">
         <v>2052</v>
       </c>
@@ -52316,7 +52334,7 @@
 gaining Azov early in the game.</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="45" t="s">
         <v>1941</v>
       </c>
@@ -52383,7 +52401,7 @@
 provinces with the correct trade goods.</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="39" t="s">
         <v>1942</v>
       </c>
@@ -52445,7 +52463,7 @@
         <v>Easiest as Malacca or Pasai.</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="45" t="s">
         <v>1943</v>
       </c>
@@ -52506,7 +52524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="39" t="s">
         <v>1944</v>
       </c>
@@ -52570,7 +52588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="45" t="s">
         <v>1945</v>
       </c>
@@ -52640,7 +52658,7 @@
 a quarter of HRE provinces under Anglican control.</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="39" t="s">
         <v>1946</v>
       </c>
@@ -52706,7 +52724,7 @@
 vassals in your home islands to achieve this.</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52769,7 +52787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52836,7 +52854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52905,7 +52923,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="39" t="s">
         <v>1948</v>
       </c>
@@ -52986,7 +53004,7 @@
 coast, and finally down to Werder.</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="45" t="s">
         <v>1949</v>
       </c>
@@ -53050,7 +53068,7 @@
 annexed all of Livonian Order and Riga</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="39" t="s">
         <v>1950</v>
       </c>
@@ -53124,7 +53142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="45" t="s">
         <v>1951</v>
       </c>
@@ -53191,7 +53209,7 @@
 necessary.</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="39" t="s">
         <v>1952</v>
       </c>
@@ -53254,7 +53272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="45" t="s">
         <v>1953</v>
       </c>
@@ -53281,7 +53299,7 @@
       </c>
       <c r="H81" s="63" t="str">
         <f>IF(VLOOKUP($G81,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G81,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I81" s="47" t="str">
         <f>VLOOKUP($G81,List!$A:$U,2,FALSE)</f>
@@ -53316,7 +53334,7 @@
         <v>Caffa is in the Pontic Steppe region, initially owned by Genoa.</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="39" t="s">
         <v>1954</v>
       </c>
@@ -53388,7 +53406,7 @@
 a lot of troops and declaring war on them once they form Prussia.</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="45" t="s">
         <v>1955</v>
       </c>
@@ -53450,7 +53468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="39" t="s">
         <v>1956</v>
       </c>
@@ -53512,7 +53530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="45" t="s">
         <v>1957</v>
       </c>
@@ -53577,7 +53595,7 @@
 this.</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="39" t="s">
         <v>1958</v>
       </c>
@@ -53641,7 +53659,7 @@
 southeast Asia</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="45" t="s">
         <v>1959</v>
       </c>
@@ -53704,7 +53722,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="39" t="s">
         <v>1960</v>
       </c>
@@ -53766,7 +53784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="45" t="s">
         <v>1961</v>
       </c>
@@ -53842,7 +53860,7 @@
 ideas are all helpful.</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="39" t="s">
         <v>1962</v>
       </c>
@@ -53906,7 +53924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="45" t="s">
         <v>1963</v>
       </c>
@@ -53969,7 +53987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="39" t="s">
         <v>1964</v>
       </c>
@@ -53996,7 +54014,7 @@
       </c>
       <c r="H92" s="64" t="str">
         <f>IF(VLOOKUP($G92,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G92,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I92" s="42" t="str">
         <f>VLOOKUP($G92,List!$A:$U,2,FALSE)</f>
@@ -54034,7 +54052,7 @@
 - Making the leading tobacco producer a tributary would count.</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="45" t="s">
         <v>1965</v>
       </c>
@@ -54107,7 +54125,7 @@
 (requires having the Emperor DLC activated and the Domination not active).</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="39" t="s">
         <v>1966</v>
       </c>
@@ -54178,7 +54196,7 @@
 province, this will convert you to Coptic and grant the achievement.</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="45" t="s">
         <v>1967</v>
       </c>
@@ -54242,7 +54260,7 @@
         <v>Chinaware appears in China, Japan, Korea and the East Indies.</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54308,7 +54326,7 @@
 and/or Bohemia to defeat Hungary for the important provinces.</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54374,7 +54392,7 @@
 then sail up next to Stockholm and move your cavalry onto it.</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="45" t="s">
         <v>1969</v>
       </c>
@@ -54437,7 +54455,7 @@
         <v>Lucknow is in northern India, initially owned by Jaunpur.</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="39" t="s">
         <v>1970</v>
       </c>
@@ -54505,7 +54523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="45" t="s">
         <v>2054</v>
       </c>
@@ -54602,7 +54620,7 @@
 a horde in this way is only possible as a migratory tribe.</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="39" t="s">
         <v>1971</v>
       </c>
@@ -54669,7 +54687,7 @@
 due to the event which spawns Kalmyk.</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54736,7 +54754,7 @@
 within a few days.</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54802,7 +54820,7 @@
 nations that can be released from Qara Qoyunlu's provinces.</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="39" t="s">
         <v>1973</v>
       </c>
@@ -54865,7 +54883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="45" t="s">
         <v>1974</v>
       </c>
@@ -54931,7 +54949,7 @@
 they produce wool.</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="39" t="s">
         <v>1975</v>
       </c>
@@ -54994,7 +55012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="45" t="s">
         <v>1976</v>
       </c>
@@ -55058,7 +55076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="39" t="s">
         <v>1977</v>
       </c>
@@ -55126,7 +55144,7 @@
 an army when Mutapa has started integrating you.</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="45" t="s">
         <v>1978</v>
       </c>
@@ -55187,7 +55205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="39" t="s">
         <v>2029</v>
       </c>
@@ -55249,7 +55267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="45" t="s">
         <v>1979</v>
       </c>
@@ -55312,7 +55330,7 @@
         <v>Has to be Protestant and lead the League.</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="39" t="s">
         <v>1980</v>
       </c>
@@ -55377,7 +55395,7 @@
 England until the time is right.</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="45" t="s">
         <v>1981</v>
       </c>
@@ -55447,7 +55465,7 @@
 then release and play as Lippe, earning you the achievement.</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55508,7 +55526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55573,7 +55591,7 @@
 Corfu will not count.</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="45" t="s">
         <v>1983</v>
       </c>
@@ -55648,7 +55666,7 @@
 which will increase your gold income, requiring less development.</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="39" t="s">
         <v>1984</v>
       </c>
@@ -55715,7 +55733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="45" t="s">
         <v>1985</v>
       </c>
@@ -55742,7 +55760,7 @@
       </c>
       <c r="H118" s="63" t="str">
         <f>IF(VLOOKUP($G118,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G118,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I118" s="47" t="str">
         <f>VLOOKUP($G118,List!$A:$U,2,FALSE)</f>
@@ -55781,7 +55799,7 @@
 get the open outcome in the incident Spread of Christianity.</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="39" t="s">
         <v>1986</v>
       </c>
@@ -55844,7 +55862,7 @@
         <v>Possible starts are Dongola, Alodia, and Makuria.</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="45" t="s">
         <v>1987</v>
       </c>
@@ -55909,7 +55927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="39" t="s">
         <v>1988</v>
       </c>
@@ -55979,7 +55997,7 @@
 Flame Burning.</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="45" t="s">
         <v>1989</v>
       </c>
@@ -56058,7 +56076,7 @@
 Moravia, which can be done by Bohemia.</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="39" t="s">
         <v>1990</v>
       </c>
@@ -56126,7 +56144,7 @@
 your former overlord.</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="45" t="s">
         <v>1991</v>
       </c>
@@ -56196,7 +56214,7 @@
 ahead-of-time penalty in 1820.</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="39" t="s">
         <v>1992</v>
       </c>
@@ -56275,7 +56293,7 @@
 Simply annexing a vassal in the region won't fire the achievement.</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="45" t="s">
         <v>1993</v>
       </c>
@@ -56385,7 +56403,7 @@
 is needed to complete it.</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="39" t="s">
         <v>1994</v>
       </c>
@@ -56448,7 +56466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="45" t="s">
         <v>1995</v>
       </c>
@@ -56519,7 +56537,7 @@
 to Germany.</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="39" t="s">
         <v>1996</v>
       </c>
@@ -56592,7 +56610,7 @@
 nation doesn't work, because it counts as playing as a released vassal.</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56666,7 +56684,7 @@
 more easily if necessary.</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56729,7 +56747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56800,7 +56818,7 @@
 use their bonuses and permanent claim on the mongol region.</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="39" t="s">
         <v>1998</v>
       </c>
@@ -56869,7 +56887,7 @@
 trust with allies grows slowly over time.</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="45" t="s">
         <v>1999</v>
       </c>
@@ -56942,7 +56960,7 @@
 especially for Trier which is not the primary tag of its culture.</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="39" t="s">
         <v>2000</v>
       </c>
@@ -57011,7 +57029,7 @@
 which stacks with "Hydraulic Rights"</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="45" t="s">
         <v>2001</v>
       </c>
@@ -57093,7 +57111,7 @@
 capital provinces.</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57157,7 +57175,7 @@
 still get the achievement without having to get Norway back on the map.</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57251,7 +57269,7 @@
 tick, you had the highest income.</v>
       </c>
     </row>
-    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57327,7 +57345,7 @@
 make conversions faster, especially against Islamic provinces.</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57413,7 +57431,7 @@
 - Tripura</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="39" t="s">
         <v>2012</v>
       </c>
@@ -57509,7 +57527,7 @@
 support from a rival.</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="45" t="s">
         <v>2007</v>
       </c>
@@ -57577,7 +57595,7 @@
 galley navy and block the straits.</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57641,7 +57659,7 @@
 Ottoman Government and Sultanate of Rûm</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57703,7 +57721,7 @@
         <v>Make sure to attack Muscovy ASAP to remove a future potential threat.</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57768,7 +57786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57839,7 +57857,7 @@
 provinces needed.</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57908,7 +57926,7 @@
 Coffee achievement. Do not form Arabia</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="45" t="s">
         <v>2009</v>
       </c>
@@ -57984,7 +58002,7 @@
 Sussex, and Kent in your first war and you should be off to a great start.</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="45" t="s">
         <v>2009</v>
       </c>
@@ -58049,7 +58067,7 @@
 Dulyn(373), Lleuddiniawn(248), Rhufain(118), Paris(183) and Llundain(236)</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58114,7 +58132,7 @@
 easily after unifying the HRE.</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58183,7 +58201,7 @@
 India.</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58259,7 +58277,7 @@
 with Jihad.</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
@@ -58388,19 +58406,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06764ED-1FD3-4368-8455-971DCC0423D8}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" customWidth="1"/>
-    <col min="8" max="8" width="60.140625" customWidth="1"/>
-    <col min="9" max="9" width="43.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="7" max="7" width="28.109375" customWidth="1"/>
+    <col min="8" max="8" width="60.109375" customWidth="1"/>
+    <col min="9" max="9" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -58429,7 +58447,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>531</v>
       </c>
@@ -58488,7 +58506,7 @@
       </c>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>251</v>
       </c>
@@ -58536,7 +58554,7 @@
       </c>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -58574,7 +58592,7 @@
       </c>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>482</v>
       </c>
@@ -58622,7 +58640,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
         <v>1702</v>
       </c>
@@ -58636,7 +58654,7 @@
       <c r="I6" s="75"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>435</v>
       </c>
@@ -58675,7 +58693,7 @@
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="76" t="s">
         <v>1703</v>
       </c>
@@ -58689,7 +58707,7 @@
       <c r="I8" s="76"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>463</v>
       </c>
@@ -58726,7 +58744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="77" t="s">
         <v>1704</v>
       </c>
@@ -58740,7 +58758,7 @@
       <c r="I10" s="77"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>491</v>
       </c>
@@ -58783,7 +58801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
         <v>1705</v>
       </c>
@@ -58797,7 +58815,7 @@
       <c r="I12" s="75"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>591</v>
       </c>
@@ -58842,7 +58860,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="78" t="s">
         <v>1706</v>
       </c>
@@ -58856,7 +58874,7 @@
       <c r="I14" s="78"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" ht="216.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>588</v>
       </c>
@@ -58905,30 +58923,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" s="2"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C22" s="2"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C26" s="2"/>
     </row>
   </sheetData>
@@ -59145,19 +59163,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5325864E-31AE-48F9-AD21-970E551229EF}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" customWidth="1"/>
-    <col min="7" max="7" width="60.140625" customWidth="1"/>
-    <col min="8" max="8" width="63.140625" customWidth="1"/>
+    <col min="6" max="6" width="28.109375" customWidth="1"/>
+    <col min="7" max="7" width="60.109375" customWidth="1"/>
+    <col min="8" max="8" width="63.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="C1" s="30" t="s">
         <v>1680</v>
       </c>
@@ -59170,7 +59188,7 @@
         <v>214.75</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>634</v>
       </c>
@@ -59196,7 +59214,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>299</v>
       </c>
@@ -59240,7 +59258,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="93" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>439</v>
       </c>
@@ -59283,7 +59301,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>601</v>
       </c>
@@ -59396,9 +59414,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1BBC31-09BA-43B6-86CD-7C2F847C46AC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>434</v>
       </c>
@@ -59409,7 +59427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>242</v>
       </c>
@@ -59420,7 +59438,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
@@ -59431,7 +59449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -59442,7 +59460,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>573</v>
       </c>
@@ -59453,7 +59471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>626</v>
       </c>
@@ -59464,7 +59482,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>1669</v>
       </c>
@@ -59497,30 +59515,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFB87DA-EA4E-493C-8327-11283D76496B}">
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="55.5703125" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="8" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-    <col min="12" max="12" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.42578125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="20" width="9.140625" style="1"/>
-    <col min="21" max="21" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.5703125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="55.5546875" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="8" max="9" width="9.109375" style="1"/>
+    <col min="10" max="10" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" style="1"/>
+    <col min="12" max="12" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="20" width="9.109375" style="1"/>
+    <col min="21" max="21" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.5546875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="I1" s="1" t="s">
         <v>1672</v>
       </c>
@@ -59534,10 +59552,10 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.3">
       <c r="I2" s="29">
         <f>K2/J2</f>
-        <v>0.63841195040861798</v>
+        <v>0.64637194618853544</v>
       </c>
       <c r="J2" s="28">
         <f>SUM(List!E:E)</f>
@@ -59545,20 +59563,20 @@
       </c>
       <c r="K2" s="27">
         <f>SUMIFS(List!$E:$E,List!$O:$O,"Y")</f>
-        <v>23599.599999999995</v>
+        <v>23893.850000000002</v>
       </c>
       <c r="L2" s="1">
         <f>COUNTIFS(List!O:O,"Y")</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="J3" s="67"/>
       <c r="L3" s="1">
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="79" t="s">
         <v>1638</v>
       </c>
@@ -59592,7 +59610,7 @@
       <c r="AA4" s="82"/>
       <c r="AB4" s="21"/>
     </row>
-    <row r="5" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>1640</v>
       </c>
@@ -59672,7 +59690,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -59791,7 +59809,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -59904,7 +59922,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -60047,7 +60065,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -60160,7 +60178,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -60274,7 +60292,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -60397,7 +60415,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -60483,12 +60501,11 @@
       </c>
       <c r="X12" s="1" t="str" cm="1">
         <f t="array" ref="X12">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(8:8)),List!K:K,0))</f>
-        <v>Stardust Crusaders</v>
+        <v>New, New Deli</v>
       </c>
       <c r="Y12" s="2" t="str">
         <f>VLOOKUP($X12,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Japan have the Land of the Christian Sun reform while Palestine and 
-Cairo are Christian under us.</v>
+        <v>As Deli, have your capital in the Delhi province.</v>
       </c>
       <c r="Z12" s="3">
         <f>VLOOKUP($X12,List!$A$1:$U$374,3,FALSE)</f>
@@ -60496,14 +60513,14 @@
       </c>
       <c r="AA12" s="6" t="str">
         <f>VLOOKUP($X12,List!$A$1:$U$374,4,FALSE)</f>
-        <v>M</v>
+        <v>H</v>
       </c>
       <c r="AB12" s="26">
         <f>IF(VLOOKUP($X12,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B12,List!$A$1:$U$374,5,FALSE))</f>
         <v>148.5</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -60608,11 +60625,12 @@
       </c>
       <c r="X13" s="1" t="str" cm="1">
         <f t="array" ref="X13">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(9:9)),List!K:K,0))</f>
-        <v>New, New Deli</v>
+        <v>One nation to rule them all</v>
       </c>
       <c r="Y13" s="15" t="str">
         <f>VLOOKUP($X13,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Deli, have your capital in the Delhi province.</v>
+        <v>As Saruhan, have at least 9 loyal vassals with at least 100 development 
+each.</v>
       </c>
       <c r="Z13" s="16">
         <f>VLOOKUP($X13,List!$A$1:$U$374,3,FALSE)</f>
@@ -60627,7 +60645,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -60715,12 +60733,12 @@
       </c>
       <c r="X14" s="1" t="str" cm="1">
         <f t="array" ref="X14">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(10:10)),List!K:K,0))</f>
-        <v>One nation to rule them all</v>
+        <v>Almost Prussian Blue</v>
       </c>
       <c r="Y14" s="2" t="str">
         <f>VLOOKUP($X14,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Saruhan, have at least 9 loyal vassals with at least 100 development 
-each.</v>
+        <v>Starting as the Livonian Order, form Livonia and own the territory of the 
+North German Confederation as core provinces.</v>
       </c>
       <c r="Z14" s="3">
         <f>VLOOKUP($X14,List!$A$1:$U$374,3,FALSE)</f>
@@ -60735,7 +60753,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -60826,12 +60844,12 @@
       </c>
       <c r="X15" s="1" t="str" cm="1">
         <f t="array" ref="X15">INDEX(List!A:A,MATCH(SMALL(List!K:K,ROW(11:11)),List!K:K,0))</f>
-        <v>Almost Prussian Blue</v>
+        <v>I don't like sand</v>
       </c>
       <c r="Y15" s="15" t="str">
         <f>VLOOKUP($X15,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as the Livonian Order, form Livonia and own the territory of the 
-North German Confederation as core provinces.</v>
+        <v>Have the most development while owning no province with terrain other than 
+desert or coastal desert.</v>
       </c>
       <c r="Z15" s="16">
         <f>VLOOKUP($X15,List!$A$1:$U$374,3,FALSE)</f>
@@ -60839,14 +60857,14 @@
       </c>
       <c r="AA15" s="17" t="str">
         <f>VLOOKUP($X15,List!$A$1:$U$374,4,FALSE)</f>
-        <v>H</v>
+        <v>VH</v>
       </c>
       <c r="AB15" s="25">
         <f>IF(VLOOKUP($X15,List!$A$1:$U$374,5,FALSE)="","",VLOOKUP($B15,List!$A$1:$U$374,5,FALSE))</f>
         <v>148.5</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="80" t="s">
         <v>1652</v>
       </c>
@@ -60880,7 +60898,7 @@
       <c r="AA17" s="84"/>
       <c r="AB17" s="22"/>
     </row>
-    <row r="18" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>1640</v>
       </c>
@@ -60960,7 +60978,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -61076,7 +61094,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>2</v>
       </c>
@@ -61194,7 +61212,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -61310,7 +61328,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>4</v>
       </c>
@@ -61429,7 +61447,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>5</v>
       </c>
@@ -61534,7 +61552,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>6</v>
       </c>
@@ -61677,7 +61695,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>7</v>
       </c>
@@ -61806,7 +61824,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>8</v>
       </c>
@@ -61922,7 +61940,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>9</v>
       </c>
@@ -62029,7 +62047,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>10</v>
       </c>
@@ -62631,21 +62649,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70671CC-FD1D-40C3-A5F7-A316733B30A0}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="9.109375" style="1"/>
+    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.44140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="86" t="s">
         <v>1658</v>
       </c>
@@ -62665,7 +62683,7 @@
       <c r="N1" s="88"/>
       <c r="O1" s="88"/>
     </row>
-    <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>1640</v>
       </c>
@@ -62709,7 +62727,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -62767,7 +62785,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20">
         <v>2</v>
       </c>
@@ -62823,7 +62841,7 @@
         <v>13.15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -62881,7 +62899,7 @@
         <v>66.25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20">
         <v>4</v>
       </c>
@@ -62937,7 +62955,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -62993,7 +63011,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>6</v>
       </c>
@@ -63050,7 +63068,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -63106,7 +63124,7 @@
         <v>67.25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20">
         <v>8</v>
       </c>
@@ -63163,7 +63181,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -63220,7 +63238,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20">
         <v>10</v>
       </c>
@@ -63276,7 +63294,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="87" t="s">
         <v>1659</v>
       </c>
@@ -63296,7 +63314,7 @@
       <c r="N14" s="89"/>
       <c r="O14" s="89"/>
     </row>
-    <row r="15" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63340,7 +63358,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>1</v>
       </c>
@@ -63397,7 +63415,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20">
         <v>2</v>
       </c>
@@ -63453,7 +63471,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
         <v>3</v>
       </c>
@@ -63509,7 +63527,7 @@
         <v>143.5</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>4</v>
       </c>
@@ -63566,7 +63584,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
         <v>5</v>
       </c>
@@ -63623,7 +63641,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>6</v>
       </c>
@@ -63680,7 +63698,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
         <v>7</v>
       </c>
@@ -63736,7 +63754,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
         <v>8</v>
       </c>
@@ -63792,7 +63810,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
         <v>9</v>
       </c>
@@ -63849,7 +63867,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20">
         <v>10</v>
       </c>
@@ -63906,7 +63924,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="85" t="s">
         <v>1673</v>
       </c>
@@ -63918,7 +63936,7 @@
       <c r="G27" s="85"/>
       <c r="H27" s="85"/>
     </row>
-    <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63944,7 +63962,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
         <v>1</v>
       </c>
@@ -63977,7 +63995,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20">
         <v>2</v>
       </c>
@@ -64010,7 +64028,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
         <v>3</v>
       </c>
@@ -64043,7 +64061,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
         <v>4</v>
       </c>
@@ -64077,7 +64095,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
         <v>5</v>
       </c>
@@ -64110,7 +64128,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>6</v>
       </c>
@@ -64143,7 +64161,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
         <v>7</v>
       </c>
@@ -64177,7 +64195,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>8</v>
       </c>
@@ -64211,7 +64229,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
         <v>9</v>
       </c>
@@ -64244,7 +64262,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20">
         <v>10</v>
       </c>

--- a/EU4_Achievements.xlsx
+++ b/EU4_Achievements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklein2\Documents\Personal\eu4_achievements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCC77F9-5212-4397-8E4D-6107F92CF115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48022142-6871-40C4-8DD9-24061013E5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
+    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="17520" tabRatio="783" xr2:uid="{198BA5B9-B19A-430E-889E-D7F965E5A24F}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="2057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3883" uniqueCount="2057">
   <si>
     <t>A Golden Empire</t>
   </si>
@@ -13353,29 +13353,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y374"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="10" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="14" width="8" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="9.109375" style="5" collapsed="1"/>
-    <col min="16" max="16" width="14.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="28.109375" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="60.109375" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="43.33203125" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="28.109375" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="11.109375" customWidth="1"/>
-    <col min="22" max="23" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="5" collapsed="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="28.140625" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="60.140625" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="43.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="28.140625" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="11.140625" customWidth="1"/>
+    <col min="22" max="23" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -13452,7 +13453,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>568</v>
       </c>
@@ -13540,7 +13541,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>564</v>
       </c>
@@ -13630,7 +13631,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>621</v>
       </c>
@@ -13713,7 +13714,7 @@
         <v>Legacy of Saint George</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>619</v>
       </c>
@@ -13803,7 +13804,7 @@
         <v>From Frankfurt to the Andes</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>239</v>
       </c>
@@ -13888,7 +13889,7 @@
         <v>Timurizz</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>561</v>
       </c>
@@ -13978,7 +13979,7 @@
         <v>Ultimate Military</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>531</v>
       </c>
@@ -14066,7 +14067,7 @@
         <v>Triple the Rome</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>566</v>
       </c>
@@ -14149,7 +14150,7 @@
         <v>The Zoro-Austrians</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>522</v>
       </c>
@@ -14234,7 +14235,7 @@
         <v>The Freest Man in the World</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>569</v>
       </c>
@@ -14317,7 +14318,7 @@
         <v>Baborg</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>456</v>
       </c>
@@ -14402,7 +14403,7 @@
         <v>Australia-Hungary</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>633</v>
       </c>
@@ -14485,7 +14486,7 @@
         <v>Mehmet's Ambition</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>432</v>
       </c>
@@ -14575,7 +14576,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>426</v>
       </c>
@@ -14663,7 +14664,7 @@
         <v>It's all coming together</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>291</v>
       </c>
@@ -14753,7 +14754,7 @@
         <v>Hanukkah Mutapa</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>622</v>
       </c>
@@ -14841,7 +14842,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>599</v>
       </c>
@@ -14931,7 +14932,7 @@
         <v>Quizquiz Pro Quo</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>620</v>
       </c>
@@ -15021,7 +15022,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>585</v>
       </c>
@@ -15111,7 +15112,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>618</v>
       </c>
@@ -15201,7 +15202,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -15291,7 +15292,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -15379,7 +15380,7 @@
         <v>Breadbasket of the World</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>567</v>
       </c>
@@ -15469,7 +15470,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>433</v>
       </c>
@@ -15559,7 +15560,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>496</v>
       </c>
@@ -15642,7 +15643,7 @@
         <v>One nation to rule them all</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>553</v>
       </c>
@@ -15727,7 +15728,7 @@
         <v>New, New Deli</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>483</v>
       </c>
@@ -15817,7 +15818,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>440</v>
       </c>
@@ -15907,7 +15908,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>451</v>
       </c>
@@ -15990,7 +15991,7 @@
         <v>Almost Prussian Blue</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>383</v>
       </c>
@@ -16080,7 +16081,7 @@
         <v>Where are the penguins?</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>430</v>
       </c>
@@ -16168,7 +16169,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>413</v>
       </c>
@@ -16256,7 +16257,7 @@
         <v>Stardust Crusaders</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>288</v>
       </c>
@@ -16346,7 +16347,7 @@
         <v>Golden Wind</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>387</v>
       </c>
@@ -16436,7 +16437,7 @@
         <v>Copium Wars</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>592</v>
       </c>
@@ -16526,7 +16527,7 @@
         <v>Inner Turmoil</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>574</v>
       </c>
@@ -16611,7 +16612,7 @@
         <v>I don't like sand</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>200</v>
       </c>
@@ -16694,7 +16695,7 @@
         <v>To the Bone</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>188</v>
       </c>
@@ -16779,7 +16780,7 @@
         <v>Surfing USA</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>557</v>
       </c>
@@ -16864,7 +16865,7 @@
         <v>The Pheasant Strut</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>624</v>
       </c>
@@ -16949,7 +16950,7 @@
         <v>Eat your Greens</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>390</v>
       </c>
@@ -17039,7 +17040,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>338</v>
       </c>
@@ -17129,7 +17130,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>389</v>
       </c>
@@ -17217,7 +17218,7 @@
         <v>No Country for Old Tercios</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>431</v>
       </c>
@@ -17305,7 +17306,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>428</v>
       </c>
@@ -17388,7 +17389,7 @@
         <v>Doge Coins</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>208</v>
       </c>
@@ -17475,7 +17476,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>528</v>
       </c>
@@ -17558,7 +17559,7 @@
         <v>Why is the Rûm gone!?</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>555</v>
       </c>
@@ -17648,7 +17649,7 @@
         <v>The Fezzan Corridors</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>513</v>
       </c>
@@ -17738,7 +17739,7 @@
         <v>Stiff Upper Lippe</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>511</v>
       </c>
@@ -17823,7 +17824,7 @@
         <v>Stern des Südens</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>503</v>
       </c>
@@ -17913,7 +17914,7 @@
         <v>Pick Your Poison</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>499</v>
       </c>
@@ -17996,7 +17997,7 @@
         <v>Pandya Empire</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>491</v>
       </c>
@@ -18086,7 +18087,7 @@
         <v>Mass Production</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>468</v>
       </c>
@@ -18176,7 +18177,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>463</v>
       </c>
@@ -18259,7 +18260,7 @@
         <v>Dovmont's Own</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>348</v>
       </c>
@@ -18349,7 +18350,7 @@
         <v>That's No Mon</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>412</v>
       </c>
@@ -18437,7 +18438,7 @@
         <v>Sun Invasion</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>253</v>
       </c>
@@ -18525,7 +18526,7 @@
         <v>Shemot is Not</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -18615,7 +18616,7 @@
         <v>Mansa Musa</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>424</v>
       </c>
@@ -18701,7 +18702,7 @@
         <v>King of Kings</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>265</v>
       </c>
@@ -18789,7 +18790,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
@@ -18874,7 +18875,7 @@
         <v>Imposter Syndrome</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>586</v>
       </c>
@@ -18957,7 +18958,7 @@
         <v>Empire of Mann</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>583</v>
       </c>
@@ -19049,7 +19050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>530</v>
       </c>
@@ -19134,7 +19135,7 @@
         <v>With a little help..</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>525</v>
       </c>
@@ -19219,7 +19220,7 @@
         <v>Turkish Delight</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>523</v>
       </c>
@@ -19309,7 +19310,7 @@
         <v>Tiger of Mysore</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>520</v>
       </c>
@@ -19392,7 +19393,7 @@
         <v>The 52 Garhs</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>515</v>
       </c>
@@ -19482,7 +19483,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>506</v>
       </c>
@@ -19567,7 +19568,7 @@
         <v>Protect the Secret</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>543</v>
       </c>
@@ -19650,7 +19651,7 @@
         <v>Foremost Servitor of Jagannath</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>437</v>
       </c>
@@ -19733,7 +19734,7 @@
         <v>Core-fu</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>461</v>
       </c>
@@ -19818,7 +19819,7 @@
         <v>Bunte Kuh</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>535</v>
       </c>
@@ -19901,7 +19902,7 @@
         <v>Avar Khaganate</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>355</v>
       </c>
@@ -19991,7 +19992,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>309</v>
       </c>
@@ -20081,7 +20082,7 @@
         <v>Kuban Cigars</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>283</v>
       </c>
@@ -20166,7 +20167,7 @@
         <v>Ganges Khan</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>386</v>
       </c>
@@ -20254,7 +20255,7 @@
         <v>Brentry!</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>397</v>
       </c>
@@ -20342,7 +20343,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>103</v>
       </c>
@@ -20427,7 +20428,7 @@
         <v>Truly Good Maaaaa-tch</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>614</v>
       </c>
@@ -20517,7 +20518,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>608</v>
       </c>
@@ -20607,7 +20608,7 @@
         <v>Spanish Fly</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>591</v>
       </c>
@@ -20690,7 +20691,7 @@
         <v>Great Perm</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>584</v>
       </c>
@@ -20778,7 +20779,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>139</v>
       </c>
@@ -20863,7 +20864,7 @@
         <v>Forgive me, for I have Sindh</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>509</v>
       </c>
@@ -20953,7 +20954,7 @@
         <v>Spaghetti Western</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>501</v>
       </c>
@@ -21034,7 +21035,7 @@
         <v>Philippine Tiger</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>551</v>
       </c>
@@ -21122,7 +21123,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>549</v>
       </c>
@@ -21207,7 +21208,7 @@
         <v>Meissner Porcelain</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>443</v>
       </c>
@@ -21292,7 +21293,7 @@
         <v>Kushite Restoration</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>477</v>
       </c>
@@ -21380,7 +21381,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>475</v>
       </c>
@@ -21413,27 +21414,32 @@
         <f t="shared" si="14"/>
         <v>8.4069000000000001E-3</v>
       </c>
-      <c r="J93" s="10" t="str">
+      <c r="J93" s="10">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K93" s="10">
+        <v>8.4069000000000001E-3</v>
+      </c>
+      <c r="K93" s="10" t="str">
         <f t="shared" si="16"/>
-        <v>8.4069000000000001E-3</v>
+        <v/>
       </c>
       <c r="L93" s="9">
         <f t="shared" si="17"/>
         <v>3.9915930999999998</v>
       </c>
-      <c r="M93" s="9" t="str">
+      <c r="M93" s="9">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N93" s="9">
+        <v>3.9915930999999998</v>
+      </c>
+      <c r="N93" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>3.9915930999999998</v>
-      </c>
-      <c r="O93" s="4"/>
+        <v/>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P93" s="1" t="s">
+        <v>1875</v>
+      </c>
       <c r="Q93" s="7" t="s">
         <v>1343</v>
       </c>
@@ -21452,9 +21458,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="W93">
+      <c r="W93" t="str">
         <f t="shared" si="22"/>
-        <v>8.4069000000000001E-3</v>
+        <v/>
       </c>
       <c r="X93" t="str">
         <f t="shared" si="23"/>
@@ -21465,7 +21471,7 @@
         <v>Holy Horder</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>541</v>
       </c>
@@ -21555,7 +21561,7 @@
         <v>Cotton Kandy</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>435</v>
       </c>
@@ -21643,7 +21649,7 @@
         <v>Breaking the Yoke</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>380</v>
       </c>
@@ -21728,7 +21734,7 @@
         <v>Victorian Three</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>337</v>
       </c>
@@ -21818,7 +21824,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>319</v>
       </c>
@@ -21908,7 +21914,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>297</v>
       </c>
@@ -21991,7 +21997,7 @@
         <v>Home and Away</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>277</v>
       </c>
@@ -22081,7 +22087,7 @@
         <v>Don’t be Cilli</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>248</v>
       </c>
@@ -22171,7 +22177,7 @@
         <v>Disciples of Enlightenment</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>613</v>
       </c>
@@ -22261,7 +22267,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>575</v>
       </c>
@@ -22346,7 +22352,7 @@
         <v>The Animal Kingdom</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>602</v>
       </c>
@@ -22431,7 +22437,7 @@
         <v>Raja of the Rajput Reich</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>597</v>
       </c>
@@ -22516,7 +22522,7 @@
         <v>Norwegian Wood</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>581</v>
       </c>
@@ -22606,7 +22612,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>577</v>
       </c>
@@ -22639,27 +22645,32 @@
         <f t="shared" si="14"/>
         <v>8.5039E-3</v>
       </c>
-      <c r="J107" s="10" t="str">
+      <c r="J107" s="10">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K107" s="10">
+        <v>8.5039E-3</v>
+      </c>
+      <c r="K107" s="10" t="str">
         <f t="shared" si="16"/>
-        <v>8.5039E-3</v>
+        <v/>
       </c>
       <c r="L107" s="9">
         <f t="shared" si="17"/>
         <v>4.9914961</v>
       </c>
-      <c r="M107" s="9" t="str">
+      <c r="M107" s="9">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N107" s="9">
+        <v>4.9914961</v>
+      </c>
+      <c r="N107" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>4.9914961</v>
-      </c>
-      <c r="O107" s="4"/>
+        <v/>
+      </c>
+      <c r="O107" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="P107" s="1" t="s">
+        <v>1903</v>
+      </c>
       <c r="Q107" s="7" t="s">
         <v>1464</v>
       </c>
@@ -22689,7 +22700,7 @@
         <v>Academical</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>186</v>
       </c>
@@ -22779,7 +22790,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>507</v>
       </c>
@@ -22869,7 +22880,7 @@
         <v>Sailor Mon</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>488</v>
       </c>
@@ -22954,7 +22965,7 @@
         <v>Lucky Lucca</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>547</v>
       </c>
@@ -23044,7 +23055,7 @@
         <v>Komnenoi Empire</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
@@ -23132,7 +23143,7 @@
         <v>Kinslayer</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>631</v>
       </c>
@@ -23217,7 +23228,7 @@
         <v>True Heir of Timur</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>629</v>
       </c>
@@ -23307,7 +23318,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>295</v>
       </c>
@@ -23392,7 +23403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>404</v>
       </c>
@@ -23480,7 +23491,7 @@
         <v>For the Emperor!</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>571</v>
       </c>
@@ -23568,7 +23579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>601</v>
       </c>
@@ -23653,7 +23664,7 @@
         <v>Rags and Riches</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>589</v>
       </c>
@@ -23738,7 +23749,7 @@
         <v>Gothic Invasion</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>170</v>
       </c>
@@ -23828,7 +23839,7 @@
         <v>On the Edge of Madness</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>215</v>
       </c>
@@ -23915,7 +23926,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>495</v>
       </c>
@@ -24003,7 +24014,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>420</v>
       </c>
@@ -24095,7 +24106,7 @@
         <v>Yarr Harr a Pirate's Life For Me</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>346</v>
       </c>
@@ -24183,7 +24194,7 @@
         <v>Tatarstan</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>334</v>
       </c>
@@ -24271,7 +24282,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -24358,7 +24369,7 @@
         <v>Rekindling the Flames</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>327</v>
       </c>
@@ -24441,7 +24452,7 @@
         <v>No Trail of Tears</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>423</v>
       </c>
@@ -24531,7 +24542,7 @@
         <v>First Come, First Serve</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>99</v>
       </c>
@@ -24618,7 +24629,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>611</v>
       </c>
@@ -24708,7 +24719,7 @@
         <v>The Buddhists Strike Back</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>595</v>
       </c>
@@ -24794,7 +24805,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>593</v>
       </c>
@@ -24884,7 +24895,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>588</v>
       </c>
@@ -24974,7 +24985,7 @@
         <v>Frozen Assets</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>579</v>
       </c>
@@ -25062,7 +25073,7 @@
         <v>Albania or Iberia</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>199</v>
       </c>
@@ -25147,7 +25158,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>235</v>
       </c>
@@ -25239,7 +25250,7 @@
         <v>Østindisk Kompagni Te</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>128</v>
       </c>
@@ -25324,7 +25335,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>119</v>
       </c>
@@ -25412,7 +25423,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>527</v>
       </c>
@@ -25502,7 +25513,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>466</v>
       </c>
@@ -25592,7 +25603,7 @@
         <v>Emperor of Hindustan</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>540</v>
       </c>
@@ -25677,7 +25688,7 @@
         <v>Choson One</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>458</v>
       </c>
@@ -25765,7 +25776,7 @@
         <v>Back to the Piast</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>258</v>
       </c>
@@ -25848,7 +25859,7 @@
         <v>Turn the Table</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>366</v>
       </c>
@@ -25938,7 +25949,7 @@
         <v>The Sudanese Expedition</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>610</v>
       </c>
@@ -26028,7 +26039,7 @@
         <v>Sunset Invasion</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>604</v>
       </c>
@@ -26118,7 +26129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>126</v>
       </c>
@@ -26210,7 +26221,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>121</v>
       </c>
@@ -26300,7 +26311,7 @@
         <v>Brick by Brick</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>565</v>
       </c>
@@ -26390,7 +26401,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>516</v>
       </c>
@@ -26478,7 +26489,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>445</v>
       </c>
@@ -26563,7 +26574,7 @@
         <v>Rise of the White Sheep</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>563</v>
       </c>
@@ -26651,7 +26662,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>444</v>
       </c>
@@ -26739,7 +26750,7 @@
         <v>Lessons of Hemmingstedt</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>484</v>
       </c>
@@ -26822,7 +26833,7 @@
         <v>Lazarus</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>479</v>
       </c>
@@ -26910,7 +26921,7 @@
         <v>Keep the Flame Burning</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -26998,7 +27009,7 @@
         <v>Auld Alliance Reversed</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>378</v>
       </c>
@@ -27088,7 +27099,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>362</v>
       </c>
@@ -27178,7 +27189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>321</v>
       </c>
@@ -27266,7 +27277,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>289</v>
       </c>
@@ -27349,7 +27360,7 @@
         <v>Great Moravia</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>287</v>
       </c>
@@ -27434,7 +27445,7 @@
         <v>Golden Horn</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>83</v>
       </c>
@@ -27517,7 +27528,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>184</v>
       </c>
@@ -27602,7 +27613,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -27692,7 +27703,7 @@
         <v>Holy Trinity</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>471</v>
       </c>
@@ -27782,7 +27793,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>439</v>
       </c>
@@ -27874,7 +27885,7 @@
         <v>For Odin!</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>465</v>
       </c>
@@ -27964,7 +27975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>533</v>
       </c>
@@ -28054,7 +28065,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>449</v>
       </c>
@@ -28139,7 +28150,7 @@
         <v>A Hero’s Welcome</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>627</v>
       </c>
@@ -28222,7 +28233,7 @@
         <v>One Faith</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>372</v>
       </c>
@@ -28305,7 +28316,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>418</v>
       </c>
@@ -28395,7 +28406,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>328</v>
       </c>
@@ -28478,7 +28489,7 @@
         <v>Parisian Pasha</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>317</v>
       </c>
@@ -28568,7 +28579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>293</v>
       </c>
@@ -28656,7 +28667,7 @@
         <v>Hessian Mercenaries</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>267</v>
       </c>
@@ -28746,7 +28757,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>24</v>
       </c>
@@ -28833,7 +28844,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -28918,7 +28929,7 @@
         <v>Rozwi Empire</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
@@ -29008,7 +29019,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>154</v>
       </c>
@@ -29098,7 +29109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>556</v>
       </c>
@@ -29188,7 +29199,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>419</v>
       </c>
@@ -29280,7 +29291,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>350</v>
       </c>
@@ -29368,7 +29379,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>336</v>
       </c>
@@ -29451,7 +29462,7 @@
         <v>Sons of Carthage</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>243</v>
       </c>
@@ -29541,7 +29552,7 @@
         <v>Abu Bakr II’s Ambition</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>214</v>
       </c>
@@ -29631,7 +29642,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -29716,7 +29727,7 @@
         <v>The Uncommonwealth</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>361</v>
       </c>
@@ -29806,7 +29817,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>357</v>
       </c>
@@ -29896,7 +29907,7 @@
         <v>The Levant Turnabout</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>352</v>
       </c>
@@ -29984,7 +29995,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>254</v>
       </c>
@@ -30067,7 +30078,7 @@
         <v>Sweet Home Qaraqorum</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>405</v>
       </c>
@@ -30157,7 +30168,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>299</v>
       </c>
@@ -30249,7 +30260,7 @@
         <v>Ideas Guy</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>269</v>
       </c>
@@ -30332,7 +30343,7 @@
         <v>Bengal Tiger</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>260</v>
       </c>
@@ -30424,7 +30435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>161</v>
       </c>
@@ -30514,7 +30525,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>152</v>
       </c>
@@ -30604,7 +30615,7 @@
         <v>Kow-Tow</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>370</v>
       </c>
@@ -30692,7 +30703,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>422</v>
       </c>
@@ -30782,7 +30793,7 @@
         <v>A Sun God</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>469</v>
       </c>
@@ -30874,7 +30885,7 @@
         <v>Forever Golden</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>344</v>
       </c>
@@ -30964,7 +30975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>342</v>
       </c>
@@ -31054,7 +31065,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>308</v>
       </c>
@@ -31144,7 +31155,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>398</v>
       </c>
@@ -31232,7 +31243,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>59</v>
       </c>
@@ -31317,7 +31328,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>221</v>
       </c>
@@ -31407,7 +31418,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>176</v>
       </c>
@@ -31490,7 +31501,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>157</v>
       </c>
@@ -31580,7 +31591,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>147</v>
       </c>
@@ -31670,7 +31681,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>117</v>
       </c>
@@ -31755,7 +31766,7 @@
         <v>Baa Baa Black Sheep</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>558</v>
       </c>
@@ -31845,7 +31856,7 @@
         <v>The Re-Reconquista</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>480</v>
       </c>
@@ -31935,7 +31946,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>545</v>
       </c>
@@ -32023,7 +32034,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>452</v>
       </c>
@@ -32115,7 +32126,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>359</v>
       </c>
@@ -32205,7 +32216,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>353</v>
       </c>
@@ -32293,7 +32304,7 @@
         <v>The Iron Price</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>36</v>
       </c>
@@ -32381,7 +32392,7 @@
         <v>Krabater</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>146</v>
       </c>
@@ -32471,7 +32482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>560</v>
       </c>
@@ -32559,7 +32570,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>505</v>
       </c>
@@ -32649,7 +32660,7 @@
         <v>Prester John</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>460</v>
       </c>
@@ -32739,7 +32750,7 @@
         <v>Baltic Crusader</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>411</v>
       </c>
@@ -32824,7 +32835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>333</v>
       </c>
@@ -32912,7 +32923,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>330</v>
       </c>
@@ -33002,7 +33013,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>402</v>
       </c>
@@ -33092,7 +33103,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>486</v>
       </c>
@@ -33182,7 +33193,7 @@
         <v>Luck of the Irish</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>441</v>
       </c>
@@ -33270,7 +33281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>538</v>
       </c>
@@ -33360,7 +33371,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>93</v>
       </c>
@@ -33450,7 +33461,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>616</v>
       </c>
@@ -33540,7 +33551,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
@@ -33626,7 +33637,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>400</v>
       </c>
@@ -33714,7 +33725,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -33802,7 +33813,7 @@
         <v>A Blessed Nation</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>240</v>
       </c>
@@ -33892,7 +33903,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>279</v>
       </c>
@@ -33980,7 +33991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>164</v>
       </c>
@@ -34068,7 +34079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>312</v>
       </c>
@@ -34153,7 +34164,7 @@
         <v>Lion of the North</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>518</v>
       </c>
@@ -34241,7 +34252,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>310</v>
       </c>
@@ -34329,7 +34340,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>606</v>
       </c>
@@ -34419,7 +34430,7 @@
         <v>Shahanshah</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>473</v>
       </c>
@@ -34502,7 +34513,7 @@
         <v>Guarantor of Peace</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>409</v>
       </c>
@@ -34592,7 +34603,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>251</v>
       </c>
@@ -34682,7 +34693,7 @@
         <v>Relentless Push East</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>306</v>
       </c>
@@ -34770,7 +34781,7 @@
         <v>Kingdom of God</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>273</v>
       </c>
@@ -34858,7 +34869,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>97</v>
       </c>
@@ -34941,7 +34952,7 @@
         <v>Poland can into space</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>22</v>
       </c>
@@ -35033,7 +35044,7 @@
         <v>Foul Mouthed</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>143</v>
       </c>
@@ -35123,7 +35134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>104</v>
       </c>
@@ -35213,7 +35224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>263</v>
       </c>
@@ -35301,7 +35312,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>166</v>
       </c>
@@ -35389,7 +35400,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>112</v>
       </c>
@@ -35475,7 +35486,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>285</v>
       </c>
@@ -35565,7 +35576,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>168</v>
       </c>
@@ -35655,7 +35666,7 @@
         <v>Nobody wants to die</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>493</v>
       </c>
@@ -35740,7 +35751,7 @@
         <v>Master of India</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>231</v>
       </c>
@@ -35826,7 +35837,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>340</v>
       </c>
@@ -35914,7 +35925,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>202</v>
       </c>
@@ -36004,7 +36015,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>196</v>
       </c>
@@ -36092,7 +36103,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>364</v>
       </c>
@@ -36182,7 +36193,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>275</v>
       </c>
@@ -36265,7 +36276,7 @@
         <v>Definitely the Sultan of Rum</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>48</v>
       </c>
@@ -36353,7 +36364,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>497</v>
       </c>
@@ -36441,7 +36452,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>209</v>
       </c>
@@ -36524,7 +36535,7 @@
         <v>Winged Hussars</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>173</v>
       </c>
@@ -36607,7 +36618,7 @@
         <v>One King to Rule!</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>490</v>
       </c>
@@ -36697,7 +36708,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>256</v>
       </c>
@@ -36780,7 +36791,7 @@
         <v>The Spice Must Flow</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>259</v>
       </c>
@@ -36863,7 +36874,7 @@
         <v>A tale of two Families</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>129</v>
       </c>
@@ -36951,7 +36962,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>416</v>
       </c>
@@ -37039,7 +37050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>393</v>
       </c>
@@ -37129,7 +37140,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>34</v>
       </c>
@@ -37214,7 +37225,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>373</v>
       </c>
@@ -37302,7 +37313,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>325</v>
       </c>
@@ -37390,7 +37401,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>247</v>
       </c>
@@ -37478,7 +37489,7 @@
         <v>Black Jack</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1677</v>
       </c>
@@ -37568,7 +37579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>210</v>
       </c>
@@ -37658,7 +37669,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>190</v>
       </c>
@@ -37750,7 +37761,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>106</v>
       </c>
@@ -37840,7 +37851,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>130</v>
       </c>
@@ -37923,7 +37934,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>537</v>
       </c>
@@ -38011,7 +38022,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>381</v>
       </c>
@@ -38099,7 +38110,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>13</v>
       </c>
@@ -38189,7 +38200,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>38</v>
       </c>
@@ -38277,7 +38288,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>148</v>
       </c>
@@ -38365,7 +38376,7 @@
         <v>Imperio español</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>384</v>
       </c>
@@ -38455,7 +38466,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>204</v>
       </c>
@@ -38543,7 +38554,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>300</v>
       </c>
@@ -38633,7 +38644,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>89</v>
       </c>
@@ -38721,7 +38732,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>376</v>
       </c>
@@ -38806,7 +38817,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>124</v>
       </c>
@@ -38894,7 +38905,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>144</v>
       </c>
@@ -38982,7 +38993,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>233</v>
       </c>
@@ -39070,7 +39081,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>229</v>
       </c>
@@ -39158,7 +39169,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>414</v>
       </c>
@@ -39248,7 +39259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>391</v>
       </c>
@@ -39333,7 +39344,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>3</v>
       </c>
@@ -39421,7 +39432,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>63</v>
       </c>
@@ -39508,7 +39519,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>304</v>
       </c>
@@ -39598,7 +39609,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>281</v>
       </c>
@@ -39690,7 +39701,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>101</v>
       </c>
@@ -39775,7 +39786,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>25</v>
       </c>
@@ -39863,7 +39874,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>141</v>
       </c>
@@ -39951,7 +39962,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>133</v>
       </c>
@@ -40038,7 +40049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>395</v>
       </c>
@@ -40124,7 +40135,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>40</v>
       </c>
@@ -40214,7 +40225,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>212</v>
       </c>
@@ -40302,7 +40313,7 @@
         <v>A Fine Goosestep</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>323</v>
       </c>
@@ -40392,7 +40403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>137</v>
       </c>
@@ -40482,7 +40493,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>250</v>
       </c>
@@ -40572,7 +40583,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>108</v>
       </c>
@@ -40660,7 +40671,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>223</v>
       </c>
@@ -40750,7 +40761,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>159</v>
       </c>
@@ -40838,7 +40849,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>175</v>
       </c>
@@ -40926,7 +40937,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>163</v>
       </c>
@@ -41016,7 +41027,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>262</v>
       </c>
@@ -41104,7 +41115,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>95</v>
       </c>
@@ -41192,7 +41203,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>49</v>
       </c>
@@ -41282,7 +41293,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>5</v>
       </c>
@@ -41372,7 +41383,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>313</v>
       </c>
@@ -41457,7 +41468,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>85</v>
       </c>
@@ -41545,7 +41556,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>271</v>
       </c>
@@ -41633,7 +41644,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>172</v>
       </c>
@@ -41721,7 +41732,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>75</v>
       </c>
@@ -41806,7 +41817,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>227</v>
       </c>
@@ -41896,7 +41907,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>42</v>
       </c>
@@ -41986,7 +41997,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>206</v>
       </c>
@@ -42074,7 +42085,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>203</v>
       </c>
@@ -42164,7 +42175,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>302</v>
       </c>
@@ -42252,7 +42263,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>135</v>
       </c>
@@ -42339,7 +42350,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>219</v>
       </c>
@@ -42427,7 +42438,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>57</v>
       </c>
@@ -42515,7 +42526,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>110</v>
       </c>
@@ -42605,7 +42616,7 @@
         <v>All belongs to Mother Russia</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>87</v>
       </c>
@@ -42691,7 +42702,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>113</v>
       </c>
@@ -42781,7 +42792,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>18</v>
       </c>
@@ -42864,7 +42875,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>65</v>
       </c>
@@ -42952,7 +42963,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>315</v>
       </c>
@@ -43040,7 +43051,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>192</v>
       </c>
@@ -43130,7 +43141,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>30</v>
       </c>
@@ -43220,7 +43231,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>61</v>
       </c>
@@ -43308,7 +43319,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>122</v>
       </c>
@@ -43397,7 +43408,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>194</v>
       </c>
@@ -43483,7 +43494,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>0</v>
       </c>
@@ -43570,7 +43581,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>81</v>
       </c>
@@ -43658,7 +43669,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>131</v>
       </c>
@@ -43746,7 +43757,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>225</v>
       </c>
@@ -43831,7 +43842,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>115</v>
       </c>
@@ -43921,7 +43932,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>245</v>
       </c>
@@ -44006,7 +44017,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>7</v>
       </c>
@@ -44091,7 +44102,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>217</v>
       </c>
@@ -44176,7 +44187,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>374</v>
       </c>
@@ -44259,7 +44270,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>180</v>
       </c>
@@ -44344,7 +44355,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>16</v>
       </c>
@@ -44434,7 +44445,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>44</v>
       </c>
@@ -44517,7 +44528,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>27</v>
       </c>
@@ -44604,7 +44615,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>77</v>
       </c>
@@ -44689,7 +44700,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>69</v>
       </c>
@@ -44776,7 +44787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -44863,7 +44874,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>150</v>
       </c>
@@ -44948,7 +44959,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>91</v>
       </c>
@@ -45033,7 +45044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>198</v>
       </c>
@@ -45123,7 +45134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>14</v>
       </c>
@@ -45210,7 +45221,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>32</v>
       </c>
@@ -45295,7 +45306,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>67</v>
       </c>
@@ -45382,7 +45393,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>9</v>
       </c>
@@ -45467,7 +45478,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>20</v>
       </c>
@@ -45552,7 +45563,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>55</v>
       </c>
@@ -45637,7 +45648,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>46</v>
       </c>
@@ -45720,7 +45731,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>79</v>
       </c>
@@ -45803,7 +45814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>51</v>
       </c>
@@ -45886,7 +45897,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>53</v>
       </c>
@@ -45973,7 +45984,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>73</v>
       </c>
@@ -46058,7 +46069,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>71</v>
       </c>
@@ -46146,7 +46157,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y374" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}"/>
+  <autoFilter ref="A1:Y374" xr:uid="{12CD01ED-E44C-4881-8F38-D7195B5D6C0E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Holy Horder"/>
+        <filter val="Holy Trinity"/>
+        <filter val="Neither Holy, Nor German"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="393" priority="379">
@@ -46225,17 +46244,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16ACCB4E-C812-42E5-BA87-3FBA0B83A629}">
   <dimension ref="A1:F116"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.44140625" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="6" width="125.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="125.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>1747</v>
       </c>
@@ -46255,7 +46274,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>1713</v>
       </c>
@@ -46264,7 +46283,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>1714</v>
       </c>
@@ -46278,7 +46297,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>1715</v>
       </c>
@@ -46286,7 +46305,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>1748</v>
       </c>
@@ -46294,7 +46313,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>1716</v>
       </c>
@@ -46302,7 +46321,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>1749</v>
       </c>
@@ -46310,7 +46329,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>1717</v>
       </c>
@@ -46324,7 +46343,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
         <v>1675</v>
       </c>
@@ -46338,7 +46357,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>1750</v>
       </c>
@@ -46352,7 +46371,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>1718</v>
       </c>
@@ -46360,7 +46379,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
         <v>1719</v>
       </c>
@@ -46368,7 +46387,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
         <v>1751</v>
       </c>
@@ -46376,7 +46395,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
         <v>1752</v>
       </c>
@@ -46384,7 +46403,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
         <v>1689</v>
       </c>
@@ -46392,7 +46411,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>1720</v>
       </c>
@@ -46400,7 +46419,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
         <v>1721</v>
       </c>
@@ -46414,7 +46433,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>1753</v>
       </c>
@@ -46428,7 +46447,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>1754</v>
       </c>
@@ -46442,7 +46461,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>1755</v>
       </c>
@@ -46450,7 +46469,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>1756</v>
       </c>
@@ -46458,7 +46477,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
         <v>1757</v>
       </c>
@@ -46472,7 +46491,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35" t="s">
         <v>1758</v>
       </c>
@@ -46486,7 +46505,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>1759</v>
       </c>
@@ -46494,7 +46513,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>1684</v>
       </c>
@@ -46508,7 +46527,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
         <v>1722</v>
       </c>
@@ -46522,7 +46541,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="35" t="s">
         <v>1826</v>
       </c>
@@ -46536,7 +46555,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
         <v>1676</v>
       </c>
@@ -46544,7 +46563,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
         <v>1760</v>
       </c>
@@ -46552,7 +46571,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
         <v>756</v>
       </c>
@@ -46566,7 +46585,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
         <v>1723</v>
       </c>
@@ -46580,7 +46599,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
         <v>1761</v>
       </c>
@@ -46588,7 +46607,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="35" t="s">
         <v>1724</v>
       </c>
@@ -46596,7 +46615,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
         <v>289</v>
       </c>
@@ -46610,7 +46629,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
         <v>1762</v>
       </c>
@@ -46618,7 +46637,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="35" t="s">
         <v>1763</v>
       </c>
@@ -46626,7 +46645,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="35" t="s">
         <v>1764</v>
       </c>
@@ -46634,7 +46653,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>1765</v>
       </c>
@@ -46642,7 +46661,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
         <v>1725</v>
       </c>
@@ -46650,7 +46669,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="35" t="s">
         <v>1726</v>
       </c>
@@ -46658,7 +46677,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="35" t="s">
         <v>1710</v>
       </c>
@@ -46666,7 +46685,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
         <v>1766</v>
       </c>
@@ -46674,7 +46693,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="35" t="s">
         <v>1767</v>
       </c>
@@ -46682,7 +46701,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="35" t="s">
         <v>1768</v>
       </c>
@@ -46702,7 +46721,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
         <v>1769</v>
       </c>
@@ -46710,7 +46729,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="35" t="s">
         <v>1770</v>
       </c>
@@ -46718,7 +46737,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="35" t="s">
         <v>1727</v>
       </c>
@@ -46726,7 +46745,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
         <v>1728</v>
       </c>
@@ -46740,7 +46759,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="35" t="s">
         <v>1771</v>
       </c>
@@ -46748,7 +46767,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="35" t="s">
         <v>1772</v>
       </c>
@@ -46756,7 +46775,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="35" t="s">
         <v>765</v>
       </c>
@@ -46764,7 +46783,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="35" t="s">
         <v>1773</v>
       </c>
@@ -46772,7 +46791,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="35" t="s">
         <v>1777</v>
       </c>
@@ -46780,7 +46799,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
         <v>1774</v>
       </c>
@@ -46788,7 +46807,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="35" t="s">
         <v>1775</v>
       </c>
@@ -46796,7 +46815,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="35" t="s">
         <v>1776</v>
       </c>
@@ -46810,7 +46829,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="35" t="s">
         <v>1729</v>
       </c>
@@ -46818,7 +46837,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
         <v>1778</v>
       </c>
@@ -46826,7 +46845,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="35" t="s">
         <v>1779</v>
       </c>
@@ -46834,7 +46853,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="35" t="s">
         <v>1780</v>
       </c>
@@ -46848,7 +46867,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A61" s="35" t="s">
         <v>1781</v>
       </c>
@@ -46862,7 +46881,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="35" t="s">
         <v>1782</v>
       </c>
@@ -46882,7 +46901,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="35" t="s">
         <v>1783</v>
       </c>
@@ -46890,7 +46909,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="35" t="s">
         <v>1784</v>
       </c>
@@ -46898,7 +46917,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="35" t="s">
         <v>1785</v>
       </c>
@@ -46906,7 +46925,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="35" t="s">
         <v>1730</v>
       </c>
@@ -46920,7 +46939,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="35" t="s">
         <v>1731</v>
       </c>
@@ -46928,7 +46947,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="35" t="s">
         <v>1732</v>
       </c>
@@ -46942,7 +46961,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="35" t="s">
         <v>1786</v>
       </c>
@@ -46956,7 +46975,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="35" t="s">
         <v>1787</v>
       </c>
@@ -46964,7 +46983,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A71" s="35" t="s">
         <v>1733</v>
       </c>
@@ -46984,7 +47003,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="35" t="s">
         <v>1788</v>
       </c>
@@ -46992,7 +47011,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
         <v>1789</v>
       </c>
@@ -47006,7 +47025,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
         <v>1790</v>
       </c>
@@ -47014,7 +47033,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
         <v>1791</v>
       </c>
@@ -47022,7 +47041,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
         <v>1792</v>
       </c>
@@ -47030,7 +47049,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>1734</v>
       </c>
@@ -47050,7 +47069,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
         <v>1735</v>
       </c>
@@ -47070,7 +47089,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
         <v>1793</v>
       </c>
@@ -47084,7 +47103,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
         <v>1794</v>
       </c>
@@ -47092,7 +47111,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
         <v>1795</v>
       </c>
@@ -47106,7 +47125,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
         <v>1796</v>
       </c>
@@ -47120,7 +47139,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
         <v>1736</v>
       </c>
@@ -47128,7 +47147,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
         <v>1797</v>
       </c>
@@ -47136,7 +47155,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="35" t="s">
         <v>1737</v>
       </c>
@@ -47144,7 +47163,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
         <v>1798</v>
       </c>
@@ -47152,7 +47171,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="35" t="s">
         <v>182</v>
       </c>
@@ -47160,7 +47179,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
         <v>1738</v>
       </c>
@@ -47180,7 +47199,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
         <v>1739</v>
       </c>
@@ -47200,7 +47219,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
         <v>1799</v>
       </c>
@@ -47208,7 +47227,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
         <v>1800</v>
       </c>
@@ -47216,7 +47235,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="35" t="s">
         <v>1801</v>
       </c>
@@ -47224,7 +47243,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
         <v>1740</v>
       </c>
@@ -47232,7 +47251,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="35" t="s">
         <v>1802</v>
       </c>
@@ -47246,7 +47265,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="35" t="s">
         <v>1803</v>
       </c>
@@ -47254,7 +47273,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="35" t="s">
         <v>1804</v>
       </c>
@@ -47262,7 +47281,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="35" t="s">
         <v>1805</v>
       </c>
@@ -47270,7 +47289,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="35" t="s">
         <v>1806</v>
       </c>
@@ -47278,7 +47297,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="35" t="s">
         <v>1807</v>
       </c>
@@ -47286,7 +47305,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="35" t="s">
         <v>1741</v>
       </c>
@@ -47300,7 +47319,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="35" t="s">
         <v>1808</v>
       </c>
@@ -47308,7 +47327,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="35" t="s">
         <v>764</v>
       </c>
@@ -47316,7 +47335,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="35" t="s">
         <v>1742</v>
       </c>
@@ -47324,7 +47343,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A104" s="35" t="s">
         <v>1743</v>
       </c>
@@ -47338,7 +47357,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="35" t="s">
         <v>1809</v>
       </c>
@@ -47346,7 +47365,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="35" t="s">
         <v>1810</v>
       </c>
@@ -47360,7 +47379,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="35" t="s">
         <v>1811</v>
       </c>
@@ -47368,7 +47387,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="35" t="s">
         <v>1812</v>
       </c>
@@ -47382,7 +47401,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="35" t="s">
         <v>1813</v>
       </c>
@@ -47390,7 +47409,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="35" t="s">
         <v>1814</v>
       </c>
@@ -47398,7 +47417,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="35" t="s">
         <v>1744</v>
       </c>
@@ -47414,7 +47433,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="35" t="s">
         <v>1815</v>
       </c>
@@ -47422,7 +47441,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="35" t="s">
         <v>1816</v>
       </c>
@@ -47430,7 +47449,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="35" t="s">
         <v>1817</v>
       </c>
@@ -47444,7 +47463,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="35" t="s">
         <v>1745</v>
       </c>
@@ -47452,7 +47471,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="35" t="s">
         <v>1746</v>
       </c>
@@ -47817,26 +47836,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB4F934-B5CD-4C00-8D57-A5021FDDF4F5}">
   <dimension ref="A1:P153"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="66" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="31.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="58" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="28.109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="34.44140625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="60.109375" customWidth="1"/>
-    <col min="16" max="16" width="63.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="66" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="58" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="28.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="34.42578125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="60.140625" customWidth="1"/>
+    <col min="16" max="16" width="63.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>1856</v>
       </c>
@@ -47886,7 +47905,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
         <v>2044</v>
       </c>
@@ -47940,7 +47959,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48006,7 +48025,7 @@
 mission Ratify the Kalmar Union while having the reform Kalmar Union.</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48069,7 +48088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
         <v>2031</v>
       </c>
@@ -48133,7 +48152,7 @@
 Asia. Then form a claim in Ayutthaya or wait for Mingsplosion.</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48208,7 +48227,7 @@
 - Switching to play as a released vassal will invalidate the achievement.</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48309,7 +48328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
         <v>2032</v>
       </c>
@@ -48379,7 +48398,7 @@
 pretty easy without it.</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48450,7 +48469,7 @@
 the Siberian ports has already been cored or fully colonized.</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48511,7 +48530,7 @@
         <v>Easiest to do as Muscovy.</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
         <v>2033</v>
       </c>
@@ -48584,7 +48603,7 @@
 Sea ̦; it can be counterbalanced by building lots of light ships.</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48652,7 +48671,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
         <v>2034</v>
       </c>
@@ -48714,7 +48733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48778,7 +48797,7 @@
 modifier. This will deter nearby attackers as you expand opportunistically.</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48840,7 +48859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
         <v>2035</v>
       </c>
@@ -48914,7 +48933,7 @@
 Rekindling the Flames.</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>2036</v>
       </c>
@@ -48986,7 +49005,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
         <v>2036</v>
       </c>
@@ -49057,7 +49076,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
         <v>2036</v>
       </c>
@@ -49124,7 +49143,7 @@
 scornfully insult 10 of Lithuania's 11 neighbours.</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49191,7 +49210,7 @@
 to that number later.</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49263,7 +49282,7 @@
 aspect.</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="s">
         <v>2037</v>
       </c>
@@ -49336,7 +49355,7 @@
 colonize yourself.</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49403,7 +49422,7 @@
 possible to get the achievement without that DLC.</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>2038</v>
       </c>
@@ -49466,7 +49485,7 @@
 colonizing the NA lands may result in their capital being in NA.</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49530,7 +49549,7 @@
 partnered with The Buddhists Strike Back.</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>2039</v>
       </c>
@@ -49597,7 +49616,7 @@
 playing as Kandy, you'll likely also get the achievement Cotton Kandy.</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
         <v>2040</v>
       </c>
@@ -49661,7 +49680,7 @@
 be achieved even without the DLC.</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
         <v>2041</v>
       </c>
@@ -49726,7 +49745,7 @@
 these will immediately make you an empire.</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="39" t="s">
         <v>2043</v>
       </c>
@@ -49791,7 +49810,7 @@
 Philippine islands are an excellent place to start forcing conversions.</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="39" t="s">
         <v>2042</v>
       </c>
@@ -49873,7 +49892,7 @@
 Emperor.</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39" t="s">
         <v>1920</v>
       </c>
@@ -49936,7 +49955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="45" t="s">
         <v>1921</v>
       </c>
@@ -50008,7 +50027,7 @@
 Secretive personality which gives *+20%* foreign spy detection.</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="39" t="s">
         <v>1922</v>
       </c>
@@ -50075,7 +50094,7 @@
 provinces by calling them to war as ally before subjugating them.</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
         <v>1922</v>
       </c>
@@ -50140,7 +50159,7 @@
 the province sooner.</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50205,7 +50224,7 @@
 map which can't be earned by playing that custom nation.</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50273,7 +50292,7 @@
 to protect them while you improve relations.</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45" t="s">
         <v>1923</v>
       </c>
@@ -50339,7 +50358,7 @@
 releasing client states.</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50408,7 +50427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="39" t="s">
         <v>1924</v>
       </c>
@@ -50470,7 +50489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50537,7 +50556,7 @@
 Aragon.</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50607,7 +50626,7 @@
 does not change your missions).</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
         <v>1925</v>
       </c>
@@ -50670,7 +50689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50740,7 +50759,7 @@
 animist) after hitting 95 doom will also not prevent the achievement.</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
         <v>1926</v>
       </c>
@@ -50812,7 +50831,7 @@
 take capitals without the need of conquering a lot of adjacent provinces.</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50883,7 +50902,7 @@
 you can finish, it may be easier to allow a colonial nation to form.</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39" t="s">
         <v>1927</v>
       </c>
@@ -50963,7 +50982,7 @@
 rapidly across the continent at the cost of diplomatic power.</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45" t="s">
         <v>2047</v>
       </c>
@@ -51029,7 +51048,7 @@
 economy of Spain.</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
         <v>1928</v>
       </c>
@@ -51101,7 +51120,7 @@
 country will count for the achievement.</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45" t="s">
         <v>1929</v>
       </c>
@@ -51173,7 +51192,7 @@
 Ethiopia and nations lying in the way to the jewish provinces.</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51242,7 +51261,7 @@
 can culture convert their original provinces to a new culture.</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="39" t="s">
         <v>1930</v>
       </c>
@@ -51307,7 +51326,7 @@
 in this way.</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="45" t="s">
         <v>1931</v>
       </c>
@@ -51373,7 +51392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="39" t="s">
         <v>2053</v>
       </c>
@@ -51400,7 +51419,7 @@
       </c>
       <c r="H53" s="64" t="str">
         <f>IF(VLOOKUP($G53,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G53,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I53" s="42" t="str">
         <f>VLOOKUP($G53,List!$A:$U,2,FALSE)</f>
@@ -51440,7 +51459,7 @@
 due to the unique government reform.</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51504,7 +51523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51577,7 +51596,7 @@
 Sacraments” (*+2.5%*)</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39" t="s">
         <v>1932</v>
       </c>
@@ -51647,7 +51666,7 @@
 declines the PU is also a viable strategy.</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="45" t="s">
         <v>1933</v>
       </c>
@@ -51712,7 +51731,7 @@
 suffice.</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39" t="s">
         <v>1934</v>
       </c>
@@ -51782,7 +51801,7 @@
 new capital.</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45" t="s">
         <v>1935</v>
       </c>
@@ -51859,7 +51878,7 @@
 two are owned by Mali and one by Kong.</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51925,7 +51944,7 @@
 European majors for fighting the Turks.</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="39" t="s">
         <v>1936</v>
       </c>
@@ -51988,7 +52007,7 @@
 religion by rebels.</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45" t="s">
         <v>1937</v>
       </c>
@@ -52061,7 +52080,7 @@
 Africa. The provinces do not need to be cored.</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="39" t="s">
         <v>1938</v>
       </c>
@@ -52126,7 +52145,7 @@
 Valencia.</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="45" t="s">
         <v>1939</v>
       </c>
@@ -52192,7 +52211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="39" t="s">
         <v>1940</v>
       </c>
@@ -52254,7 +52273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="39" t="s">
         <v>2052</v>
       </c>
@@ -52334,7 +52353,7 @@
 gaining Azov early in the game.</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45" t="s">
         <v>1941</v>
       </c>
@@ -52401,7 +52420,7 @@
 provinces with the correct trade goods.</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="39" t="s">
         <v>1942</v>
       </c>
@@ -52463,7 +52482,7 @@
         <v>Easiest as Malacca or Pasai.</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45" t="s">
         <v>1943</v>
       </c>
@@ -52524,7 +52543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="39" t="s">
         <v>1944</v>
       </c>
@@ -52588,7 +52607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45" t="s">
         <v>1945</v>
       </c>
@@ -52658,7 +52677,7 @@
 a quarter of HRE provinces under Anglican control.</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="39" t="s">
         <v>1946</v>
       </c>
@@ -52724,7 +52743,7 @@
 vassals in your home islands to achieve this.</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52787,7 +52806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52854,7 +52873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="45" t="s">
         <v>1947</v>
       </c>
@@ -52923,7 +52942,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="39" t="s">
         <v>1948</v>
       </c>
@@ -53004,7 +53023,7 @@
 coast, and finally down to Werder.</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="45" t="s">
         <v>1949</v>
       </c>
@@ -53068,7 +53087,7 @@
 annexed all of Livonian Order and Riga</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="39" t="s">
         <v>1950</v>
       </c>
@@ -53142,7 +53161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="45" t="s">
         <v>1951</v>
       </c>
@@ -53209,7 +53228,7 @@
 necessary.</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="39" t="s">
         <v>1952</v>
       </c>
@@ -53272,7 +53291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="45" t="s">
         <v>1953</v>
       </c>
@@ -53334,7 +53353,7 @@
         <v>Caffa is in the Pontic Steppe region, initially owned by Genoa.</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="39" t="s">
         <v>1954</v>
       </c>
@@ -53406,7 +53425,7 @@
 a lot of troops and declaring war on them once they form Prussia.</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="45" t="s">
         <v>1955</v>
       </c>
@@ -53468,7 +53487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="39" t="s">
         <v>1956</v>
       </c>
@@ -53530,7 +53549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="45" t="s">
         <v>1957</v>
       </c>
@@ -53595,7 +53614,7 @@
 this.</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="39" t="s">
         <v>1958</v>
       </c>
@@ -53659,7 +53678,7 @@
 southeast Asia</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="45" t="s">
         <v>1959</v>
       </c>
@@ -53722,7 +53741,7 @@
 achievement.</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="39" t="s">
         <v>1960</v>
       </c>
@@ -53784,7 +53803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="45" t="s">
         <v>1961</v>
       </c>
@@ -53860,7 +53879,7 @@
 ideas are all helpful.</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="39" t="s">
         <v>1962</v>
       </c>
@@ -53924,7 +53943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="45" t="s">
         <v>1963</v>
       </c>
@@ -53987,7 +54006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="39" t="s">
         <v>1964</v>
       </c>
@@ -54052,7 +54071,7 @@
 - Making the leading tobacco producer a tributary would count.</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="45" t="s">
         <v>1965</v>
       </c>
@@ -54125,7 +54144,7 @@
 (requires having the Emperor DLC activated and the Domination not active).</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="39" t="s">
         <v>1966</v>
       </c>
@@ -54196,7 +54215,7 @@
 province, this will convert you to Coptic and grant the achievement.</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="45" t="s">
         <v>1967</v>
       </c>
@@ -54260,7 +54279,7 @@
         <v>Chinaware appears in China, Japan, Korea and the East Indies.</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54326,7 +54345,7 @@
 and/or Bohemia to defeat Hungary for the important provinces.</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="39" t="s">
         <v>1968</v>
       </c>
@@ -54392,7 +54411,7 @@
 then sail up next to Stockholm and move your cavalry onto it.</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="45" t="s">
         <v>1969</v>
       </c>
@@ -54455,7 +54474,7 @@
         <v>Lucknow is in northern India, initially owned by Jaunpur.</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="39" t="s">
         <v>1970</v>
       </c>
@@ -54523,7 +54542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="45" t="s">
         <v>2054</v>
       </c>
@@ -54620,7 +54639,7 @@
 a horde in this way is only possible as a migratory tribe.</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="39" t="s">
         <v>1971</v>
       </c>
@@ -54687,7 +54706,7 @@
 due to the event which spawns Kalmyk.</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54754,7 +54773,7 @@
 within a few days.</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="45" t="s">
         <v>1972</v>
       </c>
@@ -54820,7 +54839,7 @@
 nations that can be released from Qara Qoyunlu's provinces.</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="39" t="s">
         <v>1973</v>
       </c>
@@ -54883,7 +54902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="45" t="s">
         <v>1974</v>
       </c>
@@ -54949,7 +54968,7 @@
 they produce wool.</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="39" t="s">
         <v>1975</v>
       </c>
@@ -55012,7 +55031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="45" t="s">
         <v>1976</v>
       </c>
@@ -55076,7 +55095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="39" t="s">
         <v>1977</v>
       </c>
@@ -55144,7 +55163,7 @@
 an army when Mutapa has started integrating you.</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="45" t="s">
         <v>1978</v>
       </c>
@@ -55205,7 +55224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="39" t="s">
         <v>2029</v>
       </c>
@@ -55267,7 +55286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="45" t="s">
         <v>1979</v>
       </c>
@@ -55330,7 +55349,7 @@
         <v>Has to be Protestant and lead the League.</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="39" t="s">
         <v>1980</v>
       </c>
@@ -55395,7 +55414,7 @@
 England until the time is right.</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="45" t="s">
         <v>1981</v>
       </c>
@@ -55465,7 +55484,7 @@
 then release and play as Lippe, earning you the achievement.</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55526,7 +55545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="39" t="s">
         <v>1982</v>
       </c>
@@ -55591,7 +55610,7 @@
 Corfu will not count.</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="45" t="s">
         <v>1983</v>
       </c>
@@ -55666,7 +55685,7 @@
 which will increase your gold income, requiring less development.</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="39" t="s">
         <v>1984</v>
       </c>
@@ -55733,7 +55752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="45" t="s">
         <v>1985</v>
       </c>
@@ -55799,7 +55818,7 @@
 get the open outcome in the incident Spread of Christianity.</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="39" t="s">
         <v>1986</v>
       </c>
@@ -55862,7 +55881,7 @@
         <v>Possible starts are Dongola, Alodia, and Makuria.</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="45" t="s">
         <v>1987</v>
       </c>
@@ -55927,7 +55946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="39" t="s">
         <v>1988</v>
       </c>
@@ -55997,7 +56016,7 @@
 Flame Burning.</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="45" t="s">
         <v>1989</v>
       </c>
@@ -56076,7 +56095,7 @@
 Moravia, which can be done by Bohemia.</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="39" t="s">
         <v>1990</v>
       </c>
@@ -56144,7 +56163,7 @@
 your former overlord.</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="45" t="s">
         <v>1991</v>
       </c>
@@ -56214,7 +56233,7 @@
 ahead-of-time penalty in 1820.</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="39" t="s">
         <v>1992</v>
       </c>
@@ -56293,7 +56312,7 @@
 Simply annexing a vassal in the region won't fire the achievement.</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="45" t="s">
         <v>1993</v>
       </c>
@@ -56403,7 +56422,7 @@
 is needed to complete it.</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="39" t="s">
         <v>1994</v>
       </c>
@@ -56430,7 +56449,7 @@
       </c>
       <c r="H127" s="64" t="str">
         <f>IF(VLOOKUP($G127,List!$A:$O,15,FALSE)=0,"",VLOOKUP($G127,List!$A:$O,15,FALSE))</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="I127" s="42" t="str">
         <f>VLOOKUP($G127,List!$A:$U,2,FALSE)</f>
@@ -56466,7 +56485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="45" t="s">
         <v>1995</v>
       </c>
@@ -56537,7 +56556,7 @@
 to Germany.</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="39" t="s">
         <v>1996</v>
       </c>
@@ -56610,7 +56629,7 @@
 nation doesn't work, because it counts as playing as a released vassal.</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56684,7 +56703,7 @@
 more easily if necessary.</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56747,7 +56766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="45" t="s">
         <v>1997</v>
       </c>
@@ -56818,7 +56837,7 @@
 use their bonuses and permanent claim on the mongol region.</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="39" t="s">
         <v>1998</v>
       </c>
@@ -56887,7 +56906,7 @@
 trust with allies grows slowly over time.</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="45" t="s">
         <v>1999</v>
       </c>
@@ -56960,7 +56979,7 @@
 especially for Trier which is not the primary tag of its culture.</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="39" t="s">
         <v>2000</v>
       </c>
@@ -57029,7 +57048,7 @@
 which stacks with "Hydraulic Rights"</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="45" t="s">
         <v>2001</v>
       </c>
@@ -57111,7 +57130,7 @@
 capital provinces.</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57175,7 +57194,7 @@
 still get the achievement without having to get Norway back on the map.</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="39" t="s">
         <v>2030</v>
       </c>
@@ -57269,7 +57288,7 @@
 tick, you had the highest income.</v>
       </c>
     </row>
-    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57345,7 +57364,7 @@
 make conversions faster, especially against Islamic provinces.</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="45" t="s">
         <v>2002</v>
       </c>
@@ -57431,7 +57450,7 @@
 - Tripura</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="39" t="s">
         <v>2012</v>
       </c>
@@ -57527,7 +57546,7 @@
 support from a rival.</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="45" t="s">
         <v>2007</v>
       </c>
@@ -57595,7 +57614,7 @@
 galley navy and block the straits.</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57659,7 +57678,7 @@
 Ottoman Government and Sultanate of Rûm</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57721,7 +57740,7 @@
         <v>Make sure to attack Muscovy ASAP to remove a future potential threat.</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57786,7 +57805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57857,7 +57876,7 @@
 provinces needed.</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="39" t="s">
         <v>2008</v>
       </c>
@@ -57926,7 +57945,7 @@
 Coffee achievement. Do not form Arabia</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="45" t="s">
         <v>2009</v>
       </c>
@@ -58002,7 +58021,7 @@
 Sussex, and Kent in your first war and you should be off to a great start.</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="45" t="s">
         <v>2009</v>
       </c>
@@ -58067,7 +58086,7 @@
 Dulyn(373), Lleuddiniawn(248), Rhufain(118), Paris(183) and Llundain(236)</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58132,7 +58151,7 @@
 easily after unifying the HRE.</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58201,7 +58220,7 @@
 India.</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="39" t="s">
         <v>2010</v>
       </c>
@@ -58277,7 +58296,7 @@
 with Jihad.</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
@@ -58406,19 +58425,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06764ED-1FD3-4368-8455-971DCC0423D8}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
-    <col min="7" max="7" width="28.109375" customWidth="1"/>
-    <col min="8" max="8" width="60.109375" customWidth="1"/>
-    <col min="9" max="9" width="43.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" customWidth="1"/>
+    <col min="8" max="8" width="60.140625" customWidth="1"/>
+    <col min="9" max="9" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>634</v>
       </c>
@@ -58447,7 +58466,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>531</v>
       </c>
@@ -58506,7 +58525,7 @@
       </c>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>251</v>
       </c>
@@ -58554,7 +58573,7 @@
       </c>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -58592,7 +58611,7 @@
       </c>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>482</v>
       </c>
@@ -58640,7 +58659,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="75" t="s">
         <v>1702</v>
       </c>
@@ -58654,7 +58673,7 @@
       <c r="I6" s="75"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>435</v>
       </c>
@@ -58693,7 +58712,7 @@
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="76" t="s">
         <v>1703</v>
       </c>
@@ -58707,7 +58726,7 @@
       <c r="I8" s="76"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>463</v>
       </c>
@@ -58744,7 +58763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="77" t="s">
         <v>1704</v>
       </c>
@@ -58758,7 +58777,7 @@
       <c r="I10" s="77"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>491</v>
       </c>
@@ -58801,7 +58820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="75" t="s">
         <v>1705</v>
       </c>
@@ -58815,7 +58834,7 @@
       <c r="I12" s="75"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>591</v>
       </c>
@@ -58860,7 +58879,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="78" t="s">
         <v>1706</v>
       </c>
@@ -58874,7 +58893,7 @@
       <c r="I14" s="78"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" ht="224.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>588</v>
       </c>
@@ -58923,30 +58942,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C19" s="2"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C22" s="2"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
     </row>
   </sheetData>
@@ -59163,19 +59182,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5325864E-31AE-48F9-AD21-970E551229EF}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="28.109375" customWidth="1"/>
-    <col min="7" max="7" width="60.109375" customWidth="1"/>
-    <col min="8" max="8" width="63.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="60.140625" customWidth="1"/>
+    <col min="8" max="8" width="63.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="C1" s="30" t="s">
         <v>1680</v>
       </c>
@@ -59188,7 +59207,7 @@
         <v>214.75</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>634</v>
       </c>
@@ -59214,7 +59233,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>299</v>
       </c>
@@ -59258,7 +59277,7 @@
 Can also be paired with For Odin! and From Humble Origins</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="93" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>439</v>
       </c>
@@ -59301,7 +59320,7 @@
         <v>Can also be paired with From Humble Origins and Ideas Guy</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="200.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>601</v>
       </c>
@@ -59414,9 +59433,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1BBC31-09BA-43B6-86CD-7C2F847C46AC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>434</v>
       </c>
@@ -59427,7 +59446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>242</v>
       </c>
@@ -59438,7 +59457,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
@@ -59449,7 +59468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -59460,7 +59479,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>573</v>
       </c>
@@ -59471,7 +59490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>626</v>
       </c>
@@ -59482,7 +59501,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>1669</v>
       </c>
@@ -59515,30 +59534,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFB87DA-EA4E-493C-8327-11283D76496B}">
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="55.5546875" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="8" max="9" width="9.109375" style="1"/>
-    <col min="10" max="10" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="1"/>
-    <col min="12" max="12" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.44140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="20" width="9.109375" style="1"/>
-    <col min="21" max="21" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.5546875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="55.5703125" style="1" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="8" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="20" width="9.140625" style="1"/>
+    <col min="21" max="21" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.5703125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
         <v>1672</v>
       </c>
@@ -59552,10 +59571,10 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="21" x14ac:dyDescent="0.25">
       <c r="I2" s="29">
         <f>K2/J2</f>
-        <v>0.64637194618853544</v>
+        <v>0.65822063999177682</v>
       </c>
       <c r="J2" s="28">
         <f>SUM(List!E:E)</f>
@@ -59563,20 +59582,20 @@
       </c>
       <c r="K2" s="27">
         <f>SUMIFS(List!$E:$E,List!$O:$O,"Y")</f>
-        <v>23893.850000000002</v>
+        <v>24331.850000000002</v>
       </c>
       <c r="L2" s="1">
         <f>COUNTIFS(List!O:O,"Y")</f>
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="J3" s="67"/>
       <c r="L3" s="1">
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="79" t="s">
         <v>1638</v>
       </c>
@@ -59610,7 +59629,7 @@
       <c r="AA4" s="82"/>
       <c r="AB4" s="21"/>
     </row>
-    <row r="5" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>1640</v>
       </c>
@@ -59690,7 +59709,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -59809,7 +59828,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -59922,7 +59941,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -60065,7 +60084,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -60178,7 +60197,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -60292,7 +60311,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -60415,7 +60434,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -60520,7 +60539,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -60645,7 +60664,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -60753,7 +60772,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -60864,7 +60883,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="80" t="s">
         <v>1652</v>
       </c>
@@ -60898,7 +60917,7 @@
       <c r="AA17" s="84"/>
       <c r="AB17" s="22"/>
     </row>
-    <row r="18" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>1640</v>
       </c>
@@ -60978,7 +60997,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -61094,7 +61113,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>2</v>
       </c>
@@ -61212,7 +61231,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -61328,7 +61347,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>4</v>
       </c>
@@ -61447,7 +61466,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>5</v>
       </c>
@@ -61552,7 +61571,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>6</v>
       </c>
@@ -61695,7 +61714,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>7</v>
       </c>
@@ -61824,7 +61843,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>8</v>
       </c>
@@ -61940,7 +61959,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>9</v>
       </c>
@@ -62047,7 +62066,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>10</v>
       </c>
@@ -62139,11 +62158,11 @@
       </c>
       <c r="X28" s="1" t="str" cm="1">
         <f t="array" ref="X28">INDEX(List!A:A,MATCH(LARGE(List!N:N,ROW(11:11)),List!N:N,0))</f>
-        <v>Academical</v>
+        <v>Norwegian Wood</v>
       </c>
       <c r="Y28" s="15" t="str">
         <f>VLOOKUP($X28,List!$A$1:$U$374,2,FALSE)</f>
-        <v>As Athens, own 50 universities.</v>
+        <v>Own or have a subject own all naval supplies provinces as Norway.</v>
       </c>
       <c r="Z28" s="16">
         <f>VLOOKUP($X28,List!$A$1:$U$374,3,FALSE)</f>
@@ -62649,21 +62668,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70671CC-FD1D-40C3-A5F7-A316733B30A0}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="7" width="9.109375" style="1"/>
-    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.42578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="3" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="67.33203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="11" max="11" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="86" t="s">
         <v>1658</v>
       </c>
@@ -62683,7 +62702,7 @@
       <c r="N1" s="88"/>
       <c r="O1" s="88"/>
     </row>
-    <row r="2" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>1640</v>
       </c>
@@ -62727,7 +62746,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -62785,7 +62804,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>2</v>
       </c>
@@ -62841,7 +62860,7 @@
         <v>13.15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -62899,7 +62918,7 @@
         <v>66.25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>4</v>
       </c>
@@ -62955,7 +62974,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -63011,7 +63030,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>6</v>
       </c>
@@ -63068,7 +63087,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -63124,7 +63143,7 @@
         <v>67.25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>8</v>
       </c>
@@ -63181,7 +63200,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -63238,7 +63257,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>10</v>
       </c>
@@ -63294,7 +63313,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="87" t="s">
         <v>1659</v>
       </c>
@@ -63314,7 +63333,7 @@
       <c r="N14" s="89"/>
       <c r="O14" s="89"/>
     </row>
-    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63358,7 +63377,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>1</v>
       </c>
@@ -63415,7 +63434,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>2</v>
       </c>
@@ -63471,7 +63490,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>3</v>
       </c>
@@ -63527,7 +63546,7 @@
         <v>143.5</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>4</v>
       </c>
@@ -63584,7 +63603,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>5</v>
       </c>
@@ -63641,7 +63660,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>6</v>
       </c>
@@ -63698,7 +63717,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>7</v>
       </c>
@@ -63754,7 +63773,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20">
         <v>8</v>
       </c>
@@ -63810,7 +63829,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9</v>
       </c>
@@ -63867,7 +63886,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20">
         <v>10</v>
       </c>
@@ -63904,12 +63923,12 @@
       </c>
       <c r="K25" s="14" t="str" cm="1">
         <f t="array" ref="K25">INDEX(List!A:A,MATCH(LARGE(List!W:W,ROW(10:10)),List!W:W,0))</f>
-        <v>Holy Horder</v>
+        <v>Kushite Restoration</v>
       </c>
       <c r="L25" s="15" t="str">
         <f>VLOOKUP($K25,List!$A$1:$U$374,2,FALSE)</f>
-        <v>Starting as the Teutonic Order, form the Mongol Empire while have the Holy 
-Horde government reform enacted.</v>
+        <v>As a Nubian culture nation, own or have a non-Tributary subject own the 
+entire Egyptian region.</v>
       </c>
       <c r="M25" s="16">
         <f>VLOOKUP($K25,List!$A$1:$U$374,3,FALSE)</f>
@@ -63924,7 +63943,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="85" t="s">
         <v>1673</v>
       </c>
@@ -63936,7 +63955,7 @@
       <c r="G27" s="85"/>
       <c r="H27" s="85"/>
     </row>
-    <row r="28" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>1640</v>
       </c>
@@ -63962,7 +63981,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>1</v>
       </c>
@@ -63995,7 +64014,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="20">
         <v>2</v>
       </c>
@@ -64028,7 +64047,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>3</v>
       </c>
@@ -64061,7 +64080,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>4</v>
       </c>
@@ -64095,7 +64114,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>5</v>
       </c>
@@ -64128,7 +64147,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>6</v>
       </c>
@@ -64161,7 +64180,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <v>7</v>
       </c>
@@ -64195,7 +64214,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>8</v>
       </c>
@@ -64229,7 +64248,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>9</v>
       </c>
@@ -64262,7 +64281,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>10</v>
       </c>
